--- a/examples/NCC-1701_pdmout_BOM.xlsx
+++ b/examples/NCC-1701_pdmout_BOM.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BOM" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="BOM" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'BOM'!$G$17:$O$66</definedName>

--- a/examples/NCC-1701_pdmout_BOM.xlsx
+++ b/examples/NCC-1701_pdmout_BOM.xlsx
@@ -19,13 +19,18 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Aptos Narrow"/>
+      <color rgb="007A4E00"/>
+      <sz val="11"/>
     </font>
     <font>
       <name val="Aptos Narrow"/>
@@ -47,20 +52,108 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF3C4"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="3">
+  <borders count="11">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00B98900"/>
+      </left>
+      <right style="thin">
+        <color rgb="00B98900"/>
+      </right>
+      <top style="thin">
+        <color rgb="00B98900"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00B98900"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00B98900"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00B98900"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00B98900"/>
+      </right>
+      <top style="thin">
+        <color rgb="00B98900"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00B98900"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00B98900"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00B98900"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00B98900"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00B98900"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00B98900"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -77,24 +170,34 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -460,7 +563,7 @@
     <outlinePr summaryBelow="0" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B6:O66"/>
+  <dimension ref="B2:O66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5.3" customWidth="1" min="2" max="2"/>
@@ -479,2104 +582,2151 @@
     <col width="14" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
+    <row r="2" ht="20.75" customHeight="1">
+      <c r="B2" s="1" t="inlineStr">
+        <is>
+          <t>⚠ DATA QUALITY WARNINGS — verify before use:
+• V7: column 'Mass': 4 row(s) hold an unresolved SolidWorks property expression (e.g. 'SW-Mass@.SLDPRT'), not a value — rebuild and save those files in CAD so PDM exports the evaluated number
+• V5: COTS column 'COTS' not in input; COTS will be blank (per design D1 — add the variable in PDM or edit the CSV)
+• R1: row 31: duplicate path '2.1' reinterpreted as '2.10' (Excel float-mangling; export direct from PDM to avoid)</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="n"/>
+      <c r="D2" s="2" t="n"/>
+      <c r="E2" s="2" t="n"/>
+      <c r="F2" s="2" t="n"/>
+      <c r="G2" s="2" t="n"/>
+      <c r="H2" s="2" t="n"/>
+      <c r="I2" s="2" t="n"/>
+      <c r="J2" s="2" t="n"/>
+      <c r="K2" s="2" t="n"/>
+      <c r="L2" s="2" t="n"/>
+      <c r="M2" s="2" t="n"/>
+      <c r="N2" s="2" t="n"/>
+      <c r="O2" s="3" t="n"/>
+    </row>
+    <row r="3" ht="20.75" customHeight="1">
+      <c r="B3" s="4" t="n"/>
+      <c r="O3" s="5" t="n"/>
+    </row>
+    <row r="4" ht="20.75" customHeight="1">
+      <c r="B4" s="4" t="n"/>
+      <c r="O4" s="5" t="n"/>
+    </row>
+    <row r="5" ht="20.75" customHeight="1">
+      <c r="B5" s="6" t="n"/>
+      <c r="C5" s="7" t="n"/>
+      <c r="D5" s="7" t="n"/>
+      <c r="E5" s="7" t="n"/>
+      <c r="F5" s="7" t="n"/>
+      <c r="G5" s="7" t="n"/>
+      <c r="H5" s="7" t="n"/>
+      <c r="I5" s="7" t="n"/>
+      <c r="J5" s="7" t="n"/>
+      <c r="K5" s="7" t="n"/>
+      <c r="L5" s="7" t="n"/>
+      <c r="M5" s="7" t="n"/>
+      <c r="N5" s="7" t="n"/>
+      <c r="O5" s="8" t="n"/>
+    </row>
     <row r="6">
-      <c r="B6" s="1" t="inlineStr">
+      <c r="B6" s="9" t="inlineStr">
         <is>
           <t>Bill of Materials (BOM)</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="B7" s="2" t="inlineStr">
+      <c r="B7" s="10" t="inlineStr">
         <is>
           <t>NCC-1701 BOM DRAFT, 7/12/26</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="B9" s="2" t="inlineStr">
+      <c r="B9" s="10" t="inlineStr">
         <is>
           <t>PROJECT NAME AND TITLE BOX</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="B10" s="2" t="inlineStr">
+      <c r="B10" s="10" t="inlineStr">
         <is>
           <t>System Name: USS Enterprise Deflector Subsystem</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="B11" s="2" t="inlineStr">
+      <c r="B11" s="10" t="inlineStr">
         <is>
           <t>Assembly Name NCC-FA001-00</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="B12" s="2" t="inlineStr">
+      <c r="B12" s="10" t="inlineStr">
         <is>
           <t>Montgomery Scott</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="B13" s="2" t="inlineStr">
+      <c r="B13" s="10" t="inlineStr">
         <is>
           <t>scotty@starfleet.example</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="B16" s="3" t="inlineStr">
+      <c r="B16" s="11" t="inlineStr">
         <is>
           <t>Assembly Level</t>
         </is>
       </c>
-      <c r="C16" s="4" t="n"/>
-      <c r="D16" s="4" t="n"/>
-      <c r="E16" s="4" t="n"/>
-      <c r="F16" s="4" t="n"/>
-      <c r="G16" s="4" t="n"/>
-      <c r="H16" s="4" t="n"/>
-      <c r="I16" s="4" t="n"/>
-      <c r="J16" s="4" t="n"/>
-      <c r="K16" s="4" t="n"/>
-      <c r="L16" s="5" t="inlineStr">
+      <c r="C16" s="12" t="n"/>
+      <c r="D16" s="12" t="n"/>
+      <c r="E16" s="12" t="n"/>
+      <c r="F16" s="12" t="n"/>
+      <c r="G16" s="12" t="n"/>
+      <c r="H16" s="12" t="n"/>
+      <c r="I16" s="12" t="n"/>
+      <c r="J16" s="12" t="n"/>
+      <c r="K16" s="12" t="n"/>
+      <c r="L16" s="13" t="inlineStr">
         <is>
           <t>Quantity Required</t>
         </is>
       </c>
-      <c r="M16" s="4" t="n"/>
-      <c r="N16" s="4" t="n"/>
-      <c r="O16" s="4" t="n"/>
+      <c r="M16" s="12" t="n"/>
+      <c r="N16" s="12" t="n"/>
+      <c r="O16" s="12" t="n"/>
     </row>
     <row r="17">
-      <c r="B17" s="6" t="inlineStr">
+      <c r="B17" s="14" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="C17" s="6" t="inlineStr">
+      <c r="C17" s="14" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D17" s="6" t="inlineStr">
+      <c r="D17" s="14" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E17" s="6" t="inlineStr">
+      <c r="E17" s="14" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="F17" s="6" t="inlineStr">
+      <c r="F17" s="14" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="G17" s="5" t="inlineStr">
+      <c r="G17" s="13" t="inlineStr">
         <is>
           <t>Level</t>
         </is>
       </c>
-      <c r="H17" s="5" t="inlineStr">
+      <c r="H17" s="13" t="inlineStr">
         <is>
           <t>Abbreviated Part Number</t>
         </is>
       </c>
-      <c r="I17" s="5" t="inlineStr">
+      <c r="I17" s="13" t="inlineStr">
         <is>
           <t>Part Name</t>
         </is>
       </c>
-      <c r="J17" s="5" t="inlineStr">
+      <c r="J17" s="13" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
-      <c r="K17" s="5" t="inlineStr">
+      <c r="K17" s="13" t="inlineStr">
         <is>
           <t>COTS</t>
         </is>
       </c>
-      <c r="L17" s="5" t="inlineStr">
+      <c r="L17" s="13" t="inlineStr">
         <is>
           <t>Qty (Assembly)</t>
         </is>
       </c>
-      <c r="M17" s="5" t="inlineStr">
+      <c r="M17" s="13" t="inlineStr">
         <is>
           <t>Qty (Total)</t>
         </is>
       </c>
-      <c r="N17" s="5" t="inlineStr">
+      <c r="N17" s="13" t="inlineStr">
         <is>
           <t>Material</t>
         </is>
       </c>
-      <c r="O17" s="5" t="inlineStr">
+      <c r="O17" s="13" t="inlineStr">
         <is>
           <t>Mass</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="B18" s="7" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="C18" s="7" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="D18" s="7" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="E18" s="7" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="F18" s="7" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="n">
+      <c r="B18" s="15" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="C18" s="15" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="D18" s="15" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E18" s="15" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F18" s="15" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="G18" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="H18" s="2" t="inlineStr">
+      <c r="H18" s="10" t="inlineStr">
         <is>
           <t>NCC-FA001-00</t>
         </is>
       </c>
-      <c r="I18" s="2" t="inlineStr">
+      <c r="I18" s="10" t="inlineStr">
         <is>
           <t>Enterprise Deflector Final Assy (NCC-FA001.SLDASM)</t>
         </is>
       </c>
-      <c r="J18" s="2" t="inlineStr">
+      <c r="J18" s="10" t="inlineStr">
         <is>
           <t>Final Deflector Top Level Assembly</t>
         </is>
       </c>
-      <c r="K18" s="2" t="inlineStr"/>
-      <c r="L18" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="M18" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="N18" s="2" t="inlineStr"/>
-      <c r="O18" s="2" t="inlineStr"/>
+      <c r="K18" s="10" t="inlineStr"/>
+      <c r="L18" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="M18" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="N18" s="10" t="inlineStr"/>
+      <c r="O18" s="10" t="inlineStr"/>
     </row>
     <row r="19" outlineLevel="1">
-      <c r="B19" s="8" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="C19" s="8" t="n"/>
-      <c r="D19" s="8" t="n"/>
-      <c r="E19" s="8" t="n"/>
-      <c r="F19" s="8" t="n"/>
-      <c r="G19" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="H19" s="9" t="inlineStr">
+      <c r="B19" s="16" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="C19" s="16" t="n"/>
+      <c r="D19" s="16" t="n"/>
+      <c r="E19" s="16" t="n"/>
+      <c r="F19" s="16" t="n"/>
+      <c r="G19" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="H19" s="17" t="inlineStr">
         <is>
           <t>NCC-FA014-00</t>
         </is>
       </c>
-      <c r="I19" s="9" t="inlineStr">
+      <c r="I19" s="17" t="inlineStr">
         <is>
           <t>1in Cell Mounted Plasma Injector 5-DOF Mount Port With Coil (NCC-FA014.SLDASM)</t>
         </is>
       </c>
-      <c r="J19" s="9" t="inlineStr">
+      <c r="J19" s="17" t="inlineStr">
         <is>
           <t>1in Cell Mounted Plasma Injector 5-DOF Mount Port With Coil</t>
         </is>
       </c>
-      <c r="K19" s="9" t="inlineStr"/>
-      <c r="L19" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="M19" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="N19" s="9" t="inlineStr"/>
-      <c r="O19" s="9" t="inlineStr"/>
+      <c r="K19" s="17" t="inlineStr"/>
+      <c r="L19" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="M19" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="N19" s="17" t="inlineStr"/>
+      <c r="O19" s="17" t="inlineStr"/>
     </row>
     <row r="20" outlineLevel="2">
-      <c r="B20" s="8" t="n"/>
-      <c r="C20" s="8" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="D20" s="8" t="n"/>
-      <c r="E20" s="8" t="n"/>
-      <c r="F20" s="8" t="n"/>
-      <c r="G20" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="H20" s="9" t="inlineStr">
+      <c r="B20" s="16" t="n"/>
+      <c r="C20" s="16" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="D20" s="16" t="n"/>
+      <c r="E20" s="16" t="n"/>
+      <c r="F20" s="16" t="n"/>
+      <c r="G20" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="H20" s="17" t="inlineStr">
         <is>
           <t>NCC-FA004-00</t>
         </is>
       </c>
-      <c r="I20" s="9" t="inlineStr">
+      <c r="I20" s="17" t="inlineStr">
         <is>
           <t>Injector Mount Assembly Port No Coil (NCC-FA004.SLDASM)</t>
         </is>
       </c>
-      <c r="J20" s="9" t="inlineStr">
+      <c r="J20" s="17" t="inlineStr">
         <is>
           <t>1in Cell Mounted Plasma Injector 5-DOF Mount Port No Coil</t>
         </is>
       </c>
-      <c r="K20" s="9" t="inlineStr"/>
-      <c r="L20" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="M20" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="N20" s="9" t="inlineStr"/>
-      <c r="O20" s="9" t="inlineStr"/>
+      <c r="K20" s="17" t="inlineStr"/>
+      <c r="L20" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="M20" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="N20" s="17" t="inlineStr"/>
+      <c r="O20" s="17" t="inlineStr"/>
     </row>
     <row r="21" outlineLevel="3">
-      <c r="B21" s="8" t="n"/>
-      <c r="C21" s="8" t="n"/>
-      <c r="D21" s="8" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="E21" s="8" t="n"/>
-      <c r="F21" s="8" t="n"/>
-      <c r="G21" s="10" t="n">
-        <v>3</v>
-      </c>
-      <c r="H21" s="10" t="inlineStr">
+      <c r="B21" s="16" t="n"/>
+      <c r="C21" s="16" t="n"/>
+      <c r="D21" s="16" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E21" s="16" t="n"/>
+      <c r="F21" s="16" t="n"/>
+      <c r="G21" s="18" t="n">
+        <v>3</v>
+      </c>
+      <c r="H21" s="18" t="inlineStr">
         <is>
           <t>NCC-FP005-02</t>
         </is>
       </c>
-      <c r="I21" s="10" t="inlineStr">
+      <c r="I21" s="18" t="inlineStr">
         <is>
           <t>Injector Base Port (NCC-FP005.SLDPRT)</t>
         </is>
       </c>
-      <c r="J21" s="10" t="inlineStr">
+      <c r="J21" s="18" t="inlineStr">
         <is>
           <t>INJECTOR BASE, 1" COIL</t>
         </is>
       </c>
-      <c r="K21" s="10" t="inlineStr"/>
-      <c r="L21" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="M21" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="N21" s="10" t="inlineStr"/>
-      <c r="O21" s="10" t="inlineStr"/>
+      <c r="K21" s="18" t="inlineStr"/>
+      <c r="L21" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="M21" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="N21" s="18" t="inlineStr"/>
+      <c r="O21" s="18" t="inlineStr"/>
     </row>
     <row r="22" outlineLevel="3">
-      <c r="B22" s="8" t="n"/>
-      <c r="C22" s="8" t="n"/>
-      <c r="D22" s="8" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="E22" s="8" t="n"/>
-      <c r="F22" s="8" t="n"/>
-      <c r="G22" s="10" t="n">
-        <v>3</v>
-      </c>
-      <c r="H22" s="10" t="inlineStr">
+      <c r="B22" s="16" t="n"/>
+      <c r="C22" s="16" t="n"/>
+      <c r="D22" s="16" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E22" s="16" t="n"/>
+      <c r="F22" s="16" t="n"/>
+      <c r="G22" s="18" t="n">
+        <v>3</v>
+      </c>
+      <c r="H22" s="18" t="inlineStr">
         <is>
           <t>96246A088_Duranium Helical Insert_WRP</t>
         </is>
       </c>
-      <c r="I22" s="10" t="inlineStr">
+      <c r="I22" s="18" t="inlineStr">
         <is>
           <t>Duranium Helical Insert (96246A088_Duranium Helical Insert_WRP.SLDPRT)</t>
         </is>
       </c>
-      <c r="J22" s="10" t="inlineStr">
+      <c r="J22" s="18" t="inlineStr">
         <is>
           <t>Duranium Helical Insert</t>
         </is>
       </c>
-      <c r="K22" s="10" t="inlineStr"/>
-      <c r="L22" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="M22" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="N22" s="10" t="inlineStr">
+      <c r="K22" s="18" t="inlineStr"/>
+      <c r="L22" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="M22" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="N22" s="18" t="inlineStr">
         <is>
           <t>Nitronium 60 Duranium Alloy</t>
         </is>
       </c>
-      <c r="O22" s="10" t="inlineStr"/>
+      <c r="O22" s="18" t="inlineStr"/>
     </row>
     <row r="23" outlineLevel="3">
-      <c r="B23" s="8" t="n"/>
-      <c r="C23" s="8" t="n"/>
-      <c r="D23" s="8" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="E23" s="8" t="n"/>
-      <c r="F23" s="8" t="n"/>
-      <c r="G23" s="10" t="n">
-        <v>3</v>
-      </c>
-      <c r="H23" s="10" t="inlineStr">
+      <c r="B23" s="16" t="n"/>
+      <c r="C23" s="16" t="n"/>
+      <c r="D23" s="16" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E23" s="16" t="n"/>
+      <c r="F23" s="16" t="n"/>
+      <c r="G23" s="18" t="n">
+        <v>3</v>
+      </c>
+      <c r="H23" s="18" t="inlineStr">
         <is>
           <t>90945A715_Tritanium Fleet Spec. Washer_WRP</t>
         </is>
       </c>
-      <c r="I23" s="10" t="inlineStr">
+      <c r="I23" s="18" t="inlineStr">
         <is>
           <t>Tritanium Fleet Spec. Washer (90945A715_Tritanium Fleet Spec. Washer_WRP.SLDPRT)</t>
         </is>
       </c>
-      <c r="J23" s="10" t="inlineStr">
+      <c r="J23" s="18" t="inlineStr">
         <is>
           <t>Tritanium Fleet Spec. Washer</t>
         </is>
       </c>
-      <c r="K23" s="10" t="inlineStr"/>
-      <c r="L23" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="M23" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="N23" s="10" t="inlineStr">
+      <c r="K23" s="18" t="inlineStr"/>
+      <c r="L23" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="M23" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="N23" s="18" t="inlineStr">
         <is>
           <t>Tritanium 18-8</t>
         </is>
       </c>
-      <c r="O23" s="10" t="inlineStr"/>
+      <c r="O23" s="18" t="inlineStr"/>
     </row>
     <row r="24" outlineLevel="3">
-      <c r="B24" s="8" t="n"/>
-      <c r="C24" s="8" t="n"/>
-      <c r="D24" s="8" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="E24" s="8" t="n"/>
-      <c r="F24" s="8" t="n"/>
-      <c r="G24" s="10" t="n">
-        <v>3</v>
-      </c>
-      <c r="H24" s="10" t="inlineStr">
+      <c r="B24" s="16" t="n"/>
+      <c r="C24" s="16" t="n"/>
+      <c r="D24" s="16" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E24" s="16" t="n"/>
+      <c r="F24" s="16" t="n"/>
+      <c r="G24" s="18" t="n">
+        <v>3</v>
+      </c>
+      <c r="H24" s="18" t="inlineStr">
         <is>
           <t>92423A458_High-Strength Duranium Socket Head Screw_WRP</t>
         </is>
       </c>
-      <c r="I24" s="10" t="inlineStr">
+      <c r="I24" s="18" t="inlineStr">
         <is>
           <t>High-Strength Duranium Socket Head Screw (92423A458_High-Strength Duranium Socket Head Screw_WRP.SLDPRT)</t>
         </is>
       </c>
-      <c r="J24" s="10" t="inlineStr">
+      <c r="J24" s="18" t="inlineStr">
         <is>
           <t>High-Strength Duranium Socket Head Screw</t>
         </is>
       </c>
-      <c r="K24" s="10" t="inlineStr"/>
-      <c r="L24" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="M24" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="N24" s="10" t="inlineStr">
+      <c r="K24" s="18" t="inlineStr"/>
+      <c r="L24" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="M24" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="N24" s="18" t="inlineStr">
         <is>
           <t>Duranium A286 Alloy</t>
         </is>
       </c>
-      <c r="O24" s="10" t="inlineStr"/>
+      <c r="O24" s="18" t="inlineStr"/>
     </row>
     <row r="25" outlineLevel="3">
-      <c r="B25" s="8" t="n"/>
-      <c r="C25" s="8" t="n"/>
-      <c r="D25" s="8" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="E25" s="8" t="n"/>
-      <c r="F25" s="8" t="n"/>
-      <c r="G25" s="10" t="n">
-        <v>3</v>
-      </c>
-      <c r="H25" s="10" t="inlineStr">
+      <c r="B25" s="16" t="n"/>
+      <c r="C25" s="16" t="n"/>
+      <c r="D25" s="16" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E25" s="16" t="n"/>
+      <c r="F25" s="16" t="n"/>
+      <c r="G25" s="18" t="n">
+        <v>3</v>
+      </c>
+      <c r="H25" s="18" t="inlineStr">
         <is>
           <t>Custom Injector Shim_WRP</t>
         </is>
       </c>
-      <c r="I25" s="10" t="inlineStr">
+      <c r="I25" s="18" t="inlineStr">
         <is>
           <t>Custom Injector Shim WRP (Custom Injector Shim_WRP.SLDPRT)</t>
         </is>
       </c>
-      <c r="J25" s="10" t="inlineStr"/>
-      <c r="K25" s="10" t="inlineStr"/>
-      <c r="L25" s="10" t="n">
-        <v>3</v>
-      </c>
-      <c r="M25" s="10" t="n">
-        <v>3</v>
-      </c>
-      <c r="N25" s="10" t="inlineStr"/>
-      <c r="O25" s="10" t="inlineStr"/>
+      <c r="J25" s="18" t="inlineStr"/>
+      <c r="K25" s="18" t="inlineStr"/>
+      <c r="L25" s="18" t="n">
+        <v>3</v>
+      </c>
+      <c r="M25" s="18" t="n">
+        <v>3</v>
+      </c>
+      <c r="N25" s="18" t="inlineStr"/>
+      <c r="O25" s="18" t="inlineStr"/>
     </row>
     <row r="26" outlineLevel="3">
-      <c r="B26" s="8" t="n"/>
-      <c r="C26" s="8" t="n"/>
-      <c r="D26" s="8" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="E26" s="8" t="n"/>
-      <c r="F26" s="8" t="n"/>
-      <c r="G26" s="10" t="n">
-        <v>3</v>
-      </c>
-      <c r="H26" s="10" t="inlineStr">
+      <c r="B26" s="16" t="n"/>
+      <c r="C26" s="16" t="n"/>
+      <c r="D26" s="16" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E26" s="16" t="n"/>
+      <c r="F26" s="16" t="n"/>
+      <c r="G26" s="18" t="n">
+        <v>3</v>
+      </c>
+      <c r="H26" s="18" t="inlineStr">
         <is>
           <t>NCC-FP006-02</t>
         </is>
       </c>
-      <c r="I26" s="10" t="inlineStr">
+      <c r="I26" s="18" t="inlineStr">
         <is>
           <t>1in Injector Stage Port (NCC-FP006.SLDPRT)</t>
         </is>
       </c>
-      <c r="J26" s="10" t="inlineStr">
+      <c r="J26" s="18" t="inlineStr">
         <is>
           <t>INJECTOR STAGE, 1" COIL</t>
         </is>
       </c>
-      <c r="K26" s="10" t="inlineStr"/>
-      <c r="L26" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="M26" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="N26" s="10" t="inlineStr"/>
-      <c r="O26" s="10" t="inlineStr"/>
+      <c r="K26" s="18" t="inlineStr"/>
+      <c r="L26" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="M26" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="N26" s="18" t="inlineStr"/>
+      <c r="O26" s="18" t="inlineStr"/>
     </row>
     <row r="27" outlineLevel="3">
-      <c r="B27" s="8" t="n"/>
-      <c r="C27" s="8" t="n"/>
-      <c r="D27" s="8" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="E27" s="8" t="n"/>
-      <c r="F27" s="8" t="n"/>
-      <c r="G27" s="10" t="n">
-        <v>3</v>
-      </c>
-      <c r="H27" s="10" t="inlineStr">
+      <c r="B27" s="16" t="n"/>
+      <c r="C27" s="16" t="n"/>
+      <c r="D27" s="16" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E27" s="16" t="n"/>
+      <c r="F27" s="16" t="n"/>
+      <c r="G27" s="18" t="n">
+        <v>3</v>
+      </c>
+      <c r="H27" s="18" t="inlineStr">
         <is>
           <t>90945A725_Tritanium Fleet Spec. Washer_WRP</t>
         </is>
       </c>
-      <c r="I27" s="10" t="inlineStr">
+      <c r="I27" s="18" t="inlineStr">
         <is>
           <t>Tritanium Fleet Spec. Washer (90945A725_Tritanium Fleet Spec. Washer_WRP.SLDPRT)</t>
         </is>
       </c>
-      <c r="J27" s="10" t="inlineStr">
+      <c r="J27" s="18" t="inlineStr">
         <is>
           <t>Tritanium Fleet Spec. Washer</t>
         </is>
       </c>
-      <c r="K27" s="10" t="inlineStr"/>
-      <c r="L27" s="10" t="n">
-        <v>3</v>
-      </c>
-      <c r="M27" s="10" t="n">
-        <v>3</v>
-      </c>
-      <c r="N27" s="10" t="inlineStr">
+      <c r="K27" s="18" t="inlineStr"/>
+      <c r="L27" s="18" t="n">
+        <v>3</v>
+      </c>
+      <c r="M27" s="18" t="n">
+        <v>3</v>
+      </c>
+      <c r="N27" s="18" t="inlineStr">
         <is>
           <t>Tritanium 18-8</t>
         </is>
       </c>
-      <c r="O27" s="10" t="inlineStr"/>
+      <c r="O27" s="18" t="inlineStr"/>
     </row>
     <row r="28" outlineLevel="3">
-      <c r="B28" s="8" t="n"/>
-      <c r="C28" s="8" t="n"/>
-      <c r="D28" s="8" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="E28" s="8" t="n"/>
-      <c r="F28" s="8" t="n"/>
-      <c r="G28" s="10" t="n">
-        <v>3</v>
-      </c>
-      <c r="H28" s="10" t="inlineStr">
+      <c r="B28" s="16" t="n"/>
+      <c r="C28" s="16" t="n"/>
+      <c r="D28" s="16" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E28" s="16" t="n"/>
+      <c r="F28" s="16" t="n"/>
+      <c r="G28" s="18" t="n">
+        <v>3</v>
+      </c>
+      <c r="H28" s="18" t="inlineStr">
         <is>
           <t>96246A046_Duranium Helical Insert_WRP</t>
         </is>
       </c>
-      <c r="I28" s="10" t="inlineStr">
+      <c r="I28" s="18" t="inlineStr">
         <is>
           <t>Duranium Helical Insert (96246A046_Duranium Helical Insert_WRP.SLDPRT)</t>
         </is>
       </c>
-      <c r="J28" s="10" t="inlineStr">
+      <c r="J28" s="18" t="inlineStr">
         <is>
           <t>Duranium Helical Insert</t>
         </is>
       </c>
-      <c r="K28" s="10" t="inlineStr"/>
-      <c r="L28" s="10" t="n">
+      <c r="K28" s="18" t="inlineStr"/>
+      <c r="L28" s="18" t="n">
         <v>7</v>
       </c>
-      <c r="M28" s="10" t="n">
+      <c r="M28" s="18" t="n">
         <v>7</v>
       </c>
-      <c r="N28" s="10" t="inlineStr">
+      <c r="N28" s="18" t="inlineStr">
         <is>
           <t>Nitronium 60 Duranium Alloy</t>
         </is>
       </c>
-      <c r="O28" s="10" t="inlineStr"/>
+      <c r="O28" s="18" t="inlineStr"/>
     </row>
     <row r="29" outlineLevel="3">
-      <c r="B29" s="8" t="n"/>
-      <c r="C29" s="8" t="n"/>
-      <c r="D29" s="8" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="E29" s="8" t="n"/>
-      <c r="F29" s="8" t="n"/>
-      <c r="G29" s="10" t="n">
-        <v>3</v>
-      </c>
-      <c r="H29" s="10" t="inlineStr">
+      <c r="B29" s="16" t="n"/>
+      <c r="C29" s="16" t="n"/>
+      <c r="D29" s="16" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E29" s="16" t="n"/>
+      <c r="F29" s="16" t="n"/>
+      <c r="G29" s="18" t="n">
+        <v>3</v>
+      </c>
+      <c r="H29" s="18" t="inlineStr">
         <is>
           <t>NCC-FP007-00</t>
         </is>
       </c>
-      <c r="I29" s="10" t="inlineStr">
+      <c r="I29" s="18" t="inlineStr">
         <is>
           <t>Coil Glue Bond (NCC-FP007.SLDPRT)</t>
         </is>
       </c>
-      <c r="J29" s="10" t="inlineStr">
+      <c r="J29" s="18" t="inlineStr">
         <is>
           <t>Sinlge 2216 bond for 1in coil.</t>
         </is>
       </c>
-      <c r="K29" s="10" t="inlineStr"/>
-      <c r="L29" s="10" t="n">
-        <v>3</v>
-      </c>
-      <c r="M29" s="10" t="n">
-        <v>3</v>
-      </c>
-      <c r="N29" s="10" t="inlineStr"/>
-      <c r="O29" s="10" t="inlineStr"/>
+      <c r="K29" s="18" t="inlineStr"/>
+      <c r="L29" s="18" t="n">
+        <v>3</v>
+      </c>
+      <c r="M29" s="18" t="n">
+        <v>3</v>
+      </c>
+      <c r="N29" s="18" t="inlineStr"/>
+      <c r="O29" s="18" t="inlineStr"/>
     </row>
     <row r="30" outlineLevel="3">
-      <c r="B30" s="8" t="n"/>
-      <c r="C30" s="8" t="n"/>
-      <c r="D30" s="8" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="E30" s="8" t="n"/>
-      <c r="F30" s="8" t="n"/>
-      <c r="G30" s="10" t="n">
-        <v>3</v>
-      </c>
-      <c r="H30" s="10" t="inlineStr">
+      <c r="B30" s="16" t="n"/>
+      <c r="C30" s="16" t="n"/>
+      <c r="D30" s="16" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E30" s="16" t="n"/>
+      <c r="F30" s="16" t="n"/>
+      <c r="G30" s="18" t="n">
+        <v>3</v>
+      </c>
+      <c r="H30" s="18" t="inlineStr">
         <is>
           <t>NCC-FP004-B</t>
         </is>
       </c>
-      <c r="I30" s="10" t="inlineStr">
+      <c r="I30" s="18" t="inlineStr">
         <is>
           <t>1in Injector Radial Cell (NCC-FP004.SLDPRT)</t>
         </is>
       </c>
-      <c r="J30" s="10" t="inlineStr">
+      <c r="J30" s="18" t="inlineStr">
         <is>
           <t>Radial Cell of Injector 3DOF or 5DOF Coil Mount</t>
         </is>
       </c>
-      <c r="K30" s="10" t="inlineStr"/>
-      <c r="L30" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="M30" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="N30" s="10" t="inlineStr">
+      <c r="K30" s="18" t="inlineStr"/>
+      <c r="L30" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="M30" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="N30" s="18" t="inlineStr">
         <is>
           <t>Tritanium-36 Plate</t>
         </is>
       </c>
-      <c r="O30" s="10" t="inlineStr">
+      <c r="O30" s="18" t="inlineStr">
         <is>
           <t>0.064</t>
         </is>
       </c>
     </row>
     <row r="31" outlineLevel="3">
-      <c r="B31" s="8" t="n"/>
-      <c r="C31" s="8" t="n"/>
-      <c r="D31" s="8" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="E31" s="8" t="n"/>
-      <c r="F31" s="8" t="n"/>
-      <c r="G31" s="10" t="n">
-        <v>3</v>
-      </c>
-      <c r="H31" s="10" t="inlineStr">
+      <c r="B31" s="16" t="n"/>
+      <c r="C31" s="16" t="n"/>
+      <c r="D31" s="16" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E31" s="16" t="n"/>
+      <c r="F31" s="16" t="n"/>
+      <c r="G31" s="18" t="n">
+        <v>3</v>
+      </c>
+      <c r="H31" s="18" t="inlineStr">
         <is>
           <t>92423A491_High-Strength Duranium Socket Head Screw_WRP</t>
         </is>
       </c>
-      <c r="I31" s="10" t="inlineStr">
+      <c r="I31" s="18" t="inlineStr">
         <is>
           <t>High-Strength Duranium Socket Head Screw (92423A491_High-Strength Duranium Socket Head Screw_WRP.SLDPRT)</t>
         </is>
       </c>
-      <c r="J31" s="10" t="inlineStr">
+      <c r="J31" s="18" t="inlineStr">
         <is>
           <t>High-Strength Duranium Socket Head Screw</t>
         </is>
       </c>
-      <c r="K31" s="10" t="inlineStr"/>
-      <c r="L31" s="10" t="n">
-        <v>3</v>
-      </c>
-      <c r="M31" s="10" t="n">
-        <v>3</v>
-      </c>
-      <c r="N31" s="10" t="inlineStr">
+      <c r="K31" s="18" t="inlineStr"/>
+      <c r="L31" s="18" t="n">
+        <v>3</v>
+      </c>
+      <c r="M31" s="18" t="n">
+        <v>3</v>
+      </c>
+      <c r="N31" s="18" t="inlineStr">
         <is>
           <t>Duranium A286 Alloy</t>
         </is>
       </c>
-      <c r="O31" s="10" t="inlineStr"/>
+      <c r="O31" s="18" t="inlineStr"/>
     </row>
     <row r="32" outlineLevel="3">
-      <c r="B32" s="8" t="n"/>
-      <c r="C32" s="8" t="n"/>
-      <c r="D32" s="8" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="E32" s="8" t="n"/>
-      <c r="F32" s="8" t="n"/>
-      <c r="G32" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="H32" s="9" t="inlineStr">
+      <c r="B32" s="16" t="n"/>
+      <c r="C32" s="16" t="n"/>
+      <c r="D32" s="16" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E32" s="16" t="n"/>
+      <c r="F32" s="16" t="n"/>
+      <c r="G32" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="H32" s="17" t="inlineStr">
         <is>
           <t>AK000007S_WRP</t>
         </is>
       </c>
-      <c r="I32" s="9" t="inlineStr">
+      <c r="I32" s="17" t="inlineStr">
         <is>
           <t>AK000007S WRP (AK000007S_WRP.SLDASM)</t>
         </is>
       </c>
-      <c r="J32" s="9" t="inlineStr"/>
-      <c r="K32" s="9" t="inlineStr"/>
-      <c r="L32" s="9" t="n">
+      <c r="J32" s="17" t="inlineStr"/>
+      <c r="K32" s="17" t="inlineStr"/>
+      <c r="L32" s="17" t="n">
         <v>6</v>
       </c>
-      <c r="M32" s="9" t="n">
+      <c r="M32" s="17" t="n">
         <v>6</v>
       </c>
-      <c r="N32" s="9" t="inlineStr"/>
-      <c r="O32" s="9" t="inlineStr"/>
+      <c r="N32" s="17" t="inlineStr"/>
+      <c r="O32" s="17" t="inlineStr"/>
     </row>
     <row r="33" outlineLevel="4">
-      <c r="B33" s="8" t="n"/>
-      <c r="C33" s="8" t="n"/>
-      <c r="D33" s="8" t="n"/>
-      <c r="E33" s="8" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="F33" s="8" t="n"/>
-      <c r="G33" s="10" t="n">
+      <c r="B33" s="16" t="n"/>
+      <c r="C33" s="16" t="n"/>
+      <c r="D33" s="16" t="n"/>
+      <c r="E33" s="16" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F33" s="16" t="n"/>
+      <c r="G33" s="18" t="n">
         <v>4</v>
       </c>
-      <c r="H33" s="10" t="inlineStr">
+      <c r="H33" s="18" t="inlineStr">
         <is>
           <t>AK020004 EPS Tap Rev A_WRP</t>
         </is>
       </c>
-      <c r="I33" s="10" t="inlineStr">
+      <c r="I33" s="18" t="inlineStr">
         <is>
           <t>AK020004 EPS Tap Rev A WRP (AK020004 EPS Tap Rev A_WRP.SLDPRT)</t>
         </is>
       </c>
-      <c r="J33" s="10" t="inlineStr"/>
-      <c r="K33" s="10" t="inlineStr"/>
-      <c r="L33" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="M33" s="10" t="n">
+      <c r="J33" s="18" t="inlineStr"/>
+      <c r="K33" s="18" t="inlineStr"/>
+      <c r="L33" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="M33" s="18" t="n">
         <v>6</v>
       </c>
-      <c r="N33" s="10" t="inlineStr"/>
-      <c r="O33" s="10" t="inlineStr"/>
+      <c r="N33" s="18" t="inlineStr"/>
+      <c r="O33" s="18" t="inlineStr"/>
     </row>
     <row r="34" outlineLevel="4">
-      <c r="B34" s="8" t="n"/>
-      <c r="C34" s="8" t="n"/>
-      <c r="D34" s="8" t="n"/>
-      <c r="E34" s="8" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="F34" s="8" t="n"/>
-      <c r="G34" s="10" t="n">
+      <c r="B34" s="16" t="n"/>
+      <c r="C34" s="16" t="n"/>
+      <c r="D34" s="16" t="n"/>
+      <c r="E34" s="16" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F34" s="16" t="n"/>
+      <c r="G34" s="18" t="n">
         <v>4</v>
       </c>
-      <c r="H34" s="10" t="inlineStr">
+      <c r="H34" s="18" t="inlineStr">
         <is>
           <t>HD301004 SBS 92196A108_Tritanium Socket Head Screw_WRP</t>
         </is>
       </c>
-      <c r="I34" s="10" t="inlineStr">
+      <c r="I34" s="18" t="inlineStr">
         <is>
           <t>Tritanium Socket Head Screw (HD301004 SBS 92196A108_Tritanium Socket Head Screw_WRP.SLDPRT)</t>
         </is>
       </c>
-      <c r="J34" s="10" t="inlineStr">
+      <c r="J34" s="18" t="inlineStr">
         <is>
           <t>Tritanium Socket Head Screw</t>
         </is>
       </c>
-      <c r="K34" s="10" t="inlineStr"/>
-      <c r="L34" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="M34" s="10" t="n">
+      <c r="K34" s="18" t="inlineStr"/>
+      <c r="L34" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="M34" s="18" t="n">
         <v>6</v>
       </c>
-      <c r="N34" s="10" t="inlineStr">
+      <c r="N34" s="18" t="inlineStr">
         <is>
           <t>Tritanium 18-8</t>
         </is>
       </c>
-      <c r="O34" s="10" t="inlineStr"/>
+      <c r="O34" s="18" t="inlineStr"/>
     </row>
     <row r="35" outlineLevel="4">
-      <c r="B35" s="8" t="n"/>
-      <c r="C35" s="8" t="n"/>
-      <c r="D35" s="8" t="n"/>
-      <c r="E35" s="8" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="F35" s="8" t="n"/>
-      <c r="G35" s="10" t="n">
+      <c r="B35" s="16" t="n"/>
+      <c r="C35" s="16" t="n"/>
+      <c r="D35" s="16" t="n"/>
+      <c r="E35" s="16" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F35" s="16" t="n"/>
+      <c r="G35" s="18" t="n">
         <v>4</v>
       </c>
-      <c r="H35" s="10" t="inlineStr">
+      <c r="H35" s="18" t="inlineStr">
         <is>
           <t>HD101004 EPS Tap Adjuster Rev B_WRP</t>
         </is>
       </c>
-      <c r="I35" s="10" t="inlineStr">
+      <c r="I35" s="18" t="inlineStr">
         <is>
           <t>HD101004 EPS Tap Adjuster Rev B WRP (HD101004 EPS Tap Adjuster Rev B_WRP.SLDPRT)</t>
         </is>
       </c>
-      <c r="J35" s="10" t="inlineStr"/>
-      <c r="K35" s="10" t="inlineStr"/>
-      <c r="L35" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="M35" s="10" t="n">
+      <c r="J35" s="18" t="inlineStr"/>
+      <c r="K35" s="18" t="inlineStr"/>
+      <c r="L35" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="M35" s="18" t="n">
         <v>6</v>
       </c>
-      <c r="N35" s="10" t="inlineStr"/>
-      <c r="O35" s="10" t="inlineStr"/>
+      <c r="N35" s="18" t="inlineStr"/>
+      <c r="O35" s="18" t="inlineStr"/>
     </row>
     <row r="36" outlineLevel="2">
-      <c r="B36" s="8" t="n"/>
-      <c r="C36" s="8" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="D36" s="8" t="n"/>
-      <c r="E36" s="8" t="n"/>
-      <c r="F36" s="8" t="n"/>
-      <c r="G36" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="H36" s="10" t="inlineStr">
+      <c r="B36" s="16" t="n"/>
+      <c r="C36" s="16" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="D36" s="16" t="n"/>
+      <c r="E36" s="16" t="n"/>
+      <c r="F36" s="16" t="n"/>
+      <c r="G36" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="H36" s="18" t="inlineStr">
         <is>
           <t>FM2_WRP</t>
         </is>
       </c>
-      <c r="I36" s="10" t="inlineStr">
+      <c r="I36" s="18" t="inlineStr">
         <is>
           <t>WRP-NCC-2219 (FM2_WRP.SLDPRT)</t>
         </is>
       </c>
-      <c r="J36" s="10" t="inlineStr">
+      <c r="J36" s="18" t="inlineStr">
         <is>
           <t>FM2 FOR RCS</t>
         </is>
       </c>
-      <c r="K36" s="10" t="inlineStr"/>
-      <c r="L36" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="M36" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="N36" s="10" t="inlineStr"/>
-      <c r="O36" s="10" t="inlineStr"/>
+      <c r="K36" s="18" t="inlineStr"/>
+      <c r="L36" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="M36" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="N36" s="18" t="inlineStr"/>
+      <c r="O36" s="18" t="inlineStr"/>
     </row>
     <row r="37" outlineLevel="2">
-      <c r="B37" s="8" t="n"/>
-      <c r="C37" s="8" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="D37" s="8" t="n"/>
-      <c r="E37" s="8" t="n"/>
-      <c r="F37" s="8" t="n"/>
-      <c r="G37" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="H37" s="10" t="inlineStr">
+      <c r="B37" s="16" t="n"/>
+      <c r="C37" s="16" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="D37" s="16" t="n"/>
+      <c r="E37" s="16" t="n"/>
+      <c r="F37" s="16" t="n"/>
+      <c r="G37" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="H37" s="18" t="inlineStr">
         <is>
           <t>NCC-FP060-00</t>
         </is>
       </c>
-      <c r="I37" s="10" t="inlineStr">
+      <c r="I37" s="18" t="inlineStr">
         <is>
           <t>Emitter - Coil9A (NCC-FP060.SLDPRT)</t>
         </is>
       </c>
-      <c r="J37" s="10" t="inlineStr">
+      <c r="J37" s="18" t="inlineStr">
         <is>
           <t>1k Coil9</t>
         </is>
       </c>
-      <c r="K37" s="10" t="inlineStr"/>
-      <c r="L37" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="M37" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="N37" s="10" t="inlineStr">
+      <c r="K37" s="18" t="inlineStr"/>
+      <c r="L37" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="M37" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="N37" s="18" t="inlineStr">
         <is>
           <t>Transparent Aluminum</t>
         </is>
       </c>
-      <c r="O37" s="10" t="inlineStr">
+      <c r="O37" s="18" t="inlineStr">
         <is>
           <t>0.01</t>
         </is>
       </c>
     </row>
     <row r="38" outlineLevel="1">
-      <c r="B38" s="8" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="C38" s="8" t="n"/>
-      <c r="D38" s="8" t="n"/>
-      <c r="E38" s="8" t="n"/>
-      <c r="F38" s="8" t="n"/>
-      <c r="G38" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="H38" s="9" t="inlineStr">
+      <c r="B38" s="16" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="C38" s="16" t="n"/>
+      <c r="D38" s="16" t="n"/>
+      <c r="E38" s="16" t="n"/>
+      <c r="F38" s="16" t="n"/>
+      <c r="G38" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="H38" s="17" t="inlineStr">
         <is>
           <t>NCC-FA019-00</t>
         </is>
       </c>
-      <c r="I38" s="9" t="inlineStr">
+      <c r="I38" s="17" t="inlineStr">
         <is>
           <t>Deflector Pinhole Blocker Assembly (NCC-FA019.SLDASM)</t>
         </is>
       </c>
-      <c r="J38" s="9" t="inlineStr">
+      <c r="J38" s="17" t="inlineStr">
         <is>
           <t>Fail into beam blocker for secondary pinhole in deflector stop</t>
         </is>
       </c>
-      <c r="K38" s="9" t="inlineStr"/>
-      <c r="L38" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="M38" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="N38" s="9" t="inlineStr"/>
-      <c r="O38" s="9" t="inlineStr"/>
+      <c r="K38" s="17" t="inlineStr"/>
+      <c r="L38" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="M38" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="N38" s="17" t="inlineStr"/>
+      <c r="O38" s="17" t="inlineStr"/>
     </row>
     <row r="39" outlineLevel="2">
-      <c r="B39" s="8" t="n"/>
-      <c r="C39" s="8" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="D39" s="8" t="n"/>
-      <c r="E39" s="8" t="n"/>
-      <c r="F39" s="8" t="n"/>
-      <c r="G39" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="H39" s="10" t="inlineStr">
+      <c r="B39" s="16" t="n"/>
+      <c r="C39" s="16" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="D39" s="16" t="n"/>
+      <c r="E39" s="16" t="n"/>
+      <c r="F39" s="16" t="n"/>
+      <c r="G39" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="H39" s="18" t="inlineStr">
         <is>
           <t>deflectorActuatorFlag</t>
         </is>
       </c>
-      <c r="I39" s="10" t="inlineStr">
+      <c r="I39" s="18" t="inlineStr">
         <is>
           <t>deflectorActuatorFlag (deflectorActuatorFlag.SLDPRT)</t>
         </is>
       </c>
-      <c r="J39" s="10" t="inlineStr"/>
-      <c r="K39" s="10" t="inlineStr"/>
-      <c r="L39" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="M39" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="N39" s="10" t="inlineStr"/>
-      <c r="O39" s="10" t="inlineStr"/>
+      <c r="J39" s="18" t="inlineStr"/>
+      <c r="K39" s="18" t="inlineStr"/>
+      <c r="L39" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="M39" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="N39" s="18" t="inlineStr"/>
+      <c r="O39" s="18" t="inlineStr"/>
     </row>
     <row r="40" outlineLevel="2">
-      <c r="B40" s="8" t="n"/>
-      <c r="C40" s="8" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="D40" s="8" t="n"/>
-      <c r="E40" s="8" t="n"/>
-      <c r="F40" s="8" t="n"/>
-      <c r="G40" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="H40" s="10" t="inlineStr">
+      <c r="B40" s="16" t="n"/>
+      <c r="C40" s="16" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="D40" s="16" t="n"/>
+      <c r="E40" s="16" t="n"/>
+      <c r="F40" s="16" t="n"/>
+      <c r="G40" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="H40" s="18" t="inlineStr">
         <is>
           <t>92423A412_High-Strength Duranium Socket Head Screw_ENT</t>
         </is>
       </c>
-      <c r="I40" s="10" t="inlineStr">
+      <c r="I40" s="18" t="inlineStr">
         <is>
           <t>92423A412 High-Strength Duranium Socket Head Screw ENT (92423A412_High-Strength Duranium Socket Head Screw_ENT.SLDPRT)</t>
         </is>
       </c>
-      <c r="J40" s="10" t="inlineStr"/>
-      <c r="K40" s="10" t="inlineStr"/>
-      <c r="L40" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="M40" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="N40" s="10" t="inlineStr">
+      <c r="J40" s="18" t="inlineStr"/>
+      <c r="K40" s="18" t="inlineStr"/>
+      <c r="L40" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="M40" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="N40" s="18" t="inlineStr">
         <is>
           <t>Duranium A286 Alloy</t>
         </is>
       </c>
-      <c r="O40" s="10" t="inlineStr">
+      <c r="O40" s="18" t="inlineStr">
         <is>
           <t>SW-Mass@.SLDPRT</t>
         </is>
       </c>
     </row>
     <row r="41" outlineLevel="2">
-      <c r="B41" s="8" t="n"/>
-      <c r="C41" s="8" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="D41" s="8" t="n"/>
-      <c r="E41" s="8" t="n"/>
-      <c r="F41" s="8" t="n"/>
-      <c r="G41" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="H41" s="10" t="inlineStr">
+      <c r="B41" s="16" t="n"/>
+      <c r="C41" s="16" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="D41" s="16" t="n"/>
+      <c r="E41" s="16" t="n"/>
+      <c r="F41" s="16" t="n"/>
+      <c r="G41" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="H41" s="18" t="inlineStr">
         <is>
           <t>96246A074_Duranium Helical Insert_ENT</t>
         </is>
       </c>
-      <c r="I41" s="10" t="inlineStr">
+      <c r="I41" s="18" t="inlineStr">
         <is>
           <t>96246A074 Duranium Helical Insert ENT (96246A074_Duranium Helical Insert_ENT.SLDPRT)</t>
         </is>
       </c>
-      <c r="J41" s="10" t="inlineStr"/>
-      <c r="K41" s="10" t="inlineStr"/>
-      <c r="L41" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="M41" s="10" t="n">
+      <c r="J41" s="18" t="inlineStr"/>
+      <c r="K41" s="18" t="inlineStr"/>
+      <c r="L41" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="M41" s="18" t="n">
         <v>4</v>
       </c>
-      <c r="N41" s="10" t="inlineStr">
+      <c r="N41" s="18" t="inlineStr">
         <is>
           <t>Nitronium 60 Duranium Alloy</t>
         </is>
       </c>
-      <c r="O41" s="10" t="inlineStr">
+      <c r="O41" s="18" t="inlineStr">
         <is>
           <t>SW-Mass@.SLDPRT</t>
         </is>
       </c>
     </row>
     <row r="42" outlineLevel="2">
-      <c r="B42" s="8" t="n"/>
-      <c r="C42" s="8" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="D42" s="8" t="n"/>
-      <c r="E42" s="8" t="n"/>
-      <c r="F42" s="8" t="n"/>
-      <c r="G42" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="H42" s="10" t="inlineStr">
+      <c r="B42" s="16" t="n"/>
+      <c r="C42" s="16" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="D42" s="16" t="n"/>
+      <c r="E42" s="16" t="n"/>
+      <c r="F42" s="16" t="n"/>
+      <c r="G42" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="H42" s="18" t="inlineStr">
         <is>
           <t>a1439solenoid</t>
         </is>
       </c>
-      <c r="I42" s="10" t="inlineStr">
+      <c r="I42" s="18" t="inlineStr">
         <is>
           <t>Deflector Shutter (a1439solenoid.SLDPRT)</t>
         </is>
       </c>
-      <c r="J42" s="10" t="inlineStr">
+      <c r="J42" s="18" t="inlineStr">
         <is>
           <t>Modified COTS part a1320-1 shutter</t>
         </is>
       </c>
-      <c r="K42" s="10" t="inlineStr"/>
-      <c r="L42" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="M42" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="N42" s="10" t="inlineStr"/>
-      <c r="O42" s="10" t="inlineStr">
+      <c r="K42" s="18" t="inlineStr"/>
+      <c r="L42" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="M42" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="N42" s="18" t="inlineStr"/>
+      <c r="O42" s="18" t="inlineStr">
         <is>
           <t>0.004179</t>
         </is>
       </c>
     </row>
     <row r="43" outlineLevel="2">
-      <c r="B43" s="8" t="n"/>
-      <c r="C43" s="8" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="D43" s="8" t="n"/>
-      <c r="E43" s="8" t="n"/>
-      <c r="F43" s="8" t="n"/>
-      <c r="G43" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="H43" s="10" t="inlineStr">
+      <c r="B43" s="16" t="n"/>
+      <c r="C43" s="16" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="D43" s="16" t="n"/>
+      <c r="E43" s="16" t="n"/>
+      <c r="F43" s="16" t="n"/>
+      <c r="G43" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="H43" s="18" t="inlineStr">
         <is>
           <t>92423A461_High-Strength Duranium Socket Head Screw</t>
         </is>
       </c>
-      <c r="I43" s="10" t="inlineStr">
+      <c r="I43" s="18" t="inlineStr">
         <is>
           <t>92423A461 High-Strength Duranium Socket Head Screw (92423A461_High-Strength Duranium Socket Head Screw.SLDPRT)</t>
         </is>
       </c>
-      <c r="J43" s="10" t="inlineStr"/>
-      <c r="K43" s="10" t="inlineStr"/>
-      <c r="L43" s="10" t="n">
-        <v>3</v>
-      </c>
-      <c r="M43" s="10" t="n">
+      <c r="J43" s="18" t="inlineStr"/>
+      <c r="K43" s="18" t="inlineStr"/>
+      <c r="L43" s="18" t="n">
+        <v>3</v>
+      </c>
+      <c r="M43" s="18" t="n">
         <v>6</v>
       </c>
-      <c r="N43" s="10" t="inlineStr">
+      <c r="N43" s="18" t="inlineStr">
         <is>
           <t>Duranium A286 Alloy</t>
         </is>
       </c>
-      <c r="O43" s="10" t="inlineStr"/>
+      <c r="O43" s="18" t="inlineStr"/>
     </row>
     <row r="44" outlineLevel="2">
-      <c r="B44" s="8" t="n"/>
-      <c r="C44" s="8" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="D44" s="8" t="n"/>
-      <c r="E44" s="8" t="n"/>
-      <c r="F44" s="8" t="n"/>
-      <c r="G44" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="H44" s="10" t="inlineStr">
+      <c r="B44" s="16" t="n"/>
+      <c r="C44" s="16" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="D44" s="16" t="n"/>
+      <c r="E44" s="16" t="n"/>
+      <c r="F44" s="16" t="n"/>
+      <c r="G44" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="H44" s="18" t="inlineStr">
         <is>
           <t>NCC-FP040-00</t>
         </is>
       </c>
-      <c r="I44" s="10" t="inlineStr">
+      <c r="I44" s="18" t="inlineStr">
         <is>
           <t>EPS Bracket (NCC-FP040.SLDPRT)</t>
         </is>
       </c>
-      <c r="J44" s="10" t="inlineStr">
+      <c r="J44" s="18" t="inlineStr">
         <is>
           <t>Bracket for a1439 solenoid</t>
         </is>
       </c>
-      <c r="K44" s="10" t="inlineStr"/>
-      <c r="L44" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="M44" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="N44" s="10" t="inlineStr">
+      <c r="K44" s="18" t="inlineStr"/>
+      <c r="L44" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="M44" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="N44" s="18" t="inlineStr">
         <is>
           <t>Tritanium-36 Plate</t>
         </is>
       </c>
-      <c r="O44" s="10" t="inlineStr"/>
+      <c r="O44" s="18" t="inlineStr"/>
     </row>
     <row r="45" outlineLevel="2">
-      <c r="B45" s="8" t="n"/>
-      <c r="C45" s="8" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="D45" s="8" t="n"/>
-      <c r="E45" s="8" t="n"/>
-      <c r="F45" s="8" t="n"/>
-      <c r="G45" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="H45" s="10" t="inlineStr">
+      <c r="B45" s="16" t="n"/>
+      <c r="C45" s="16" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="D45" s="16" t="n"/>
+      <c r="E45" s="16" t="n"/>
+      <c r="F45" s="16" t="n"/>
+      <c r="G45" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="H45" s="18" t="inlineStr">
         <is>
           <t>92423A451_High-Strength Duranium Socket Head Screw_ENT</t>
         </is>
       </c>
-      <c r="I45" s="10" t="inlineStr">
+      <c r="I45" s="18" t="inlineStr">
         <is>
           <t>92423A451 High-Strength Duranium Socket Head Screw ENT (92423A451_High-Strength Duranium Socket Head Screw_ENT.SLDPRT)</t>
         </is>
       </c>
-      <c r="J45" s="10" t="inlineStr"/>
-      <c r="K45" s="10" t="inlineStr"/>
-      <c r="L45" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="M45" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="N45" s="10" t="inlineStr">
+      <c r="J45" s="18" t="inlineStr"/>
+      <c r="K45" s="18" t="inlineStr"/>
+      <c r="L45" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="M45" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="N45" s="18" t="inlineStr">
         <is>
           <t>Duranium A286 Alloy</t>
         </is>
       </c>
-      <c r="O45" s="10" t="inlineStr">
+      <c r="O45" s="18" t="inlineStr">
         <is>
           <t>SW-Mass@.SLDPRT</t>
         </is>
       </c>
     </row>
     <row r="46" outlineLevel="2">
-      <c r="B46" s="8" t="n"/>
-      <c r="C46" s="8" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="D46" s="8" t="n"/>
-      <c r="E46" s="8" t="n"/>
-      <c r="F46" s="8" t="n"/>
-      <c r="G46" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="H46" s="10" t="inlineStr">
+      <c r="B46" s="16" t="n"/>
+      <c r="C46" s="16" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="D46" s="16" t="n"/>
+      <c r="E46" s="16" t="n"/>
+      <c r="F46" s="16" t="n"/>
+      <c r="G46" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="H46" s="18" t="inlineStr">
         <is>
           <t>epsIsolator</t>
         </is>
       </c>
-      <c r="I46" s="10" t="inlineStr">
+      <c r="I46" s="18" t="inlineStr">
         <is>
           <t>epsIsolator (epsIsolator.SLDPRT)</t>
         </is>
       </c>
-      <c r="J46" s="10" t="inlineStr"/>
-      <c r="K46" s="10" t="inlineStr"/>
-      <c r="L46" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="M46" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="N46" s="10" t="inlineStr">
+      <c r="J46" s="18" t="inlineStr"/>
+      <c r="K46" s="18" t="inlineStr"/>
+      <c r="L46" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="M46" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="N46" s="18" t="inlineStr">
         <is>
           <t>Castrodinium Epoxy Composite</t>
         </is>
       </c>
-      <c r="O46" s="10" t="inlineStr">
+      <c r="O46" s="18" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
     </row>
     <row r="47" outlineLevel="2">
-      <c r="B47" s="8" t="n"/>
-      <c r="C47" s="8" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="D47" s="8" t="n"/>
-      <c r="E47" s="8" t="n"/>
-      <c r="F47" s="8" t="n"/>
-      <c r="G47" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="H47" s="10" t="inlineStr">
+      <c r="B47" s="16" t="n"/>
+      <c r="C47" s="16" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="D47" s="16" t="n"/>
+      <c r="E47" s="16" t="n"/>
+      <c r="F47" s="16" t="n"/>
+      <c r="G47" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="H47" s="18" t="inlineStr">
         <is>
           <t>NCC-FP033-00</t>
         </is>
       </c>
-      <c r="I47" s="10" t="inlineStr">
+      <c r="I47" s="18" t="inlineStr">
         <is>
           <t>EPS Deflector Shutter (NCC-FP033.SLDPRT)</t>
         </is>
       </c>
-      <c r="J47" s="10" t="inlineStr">
+      <c r="J47" s="18" t="inlineStr">
         <is>
           <t>Modified COTS part a1320-1_shutter</t>
         </is>
       </c>
-      <c r="K47" s="10" t="inlineStr"/>
-      <c r="L47" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="M47" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="N47" s="10" t="inlineStr"/>
-      <c r="O47" s="10" t="inlineStr"/>
+      <c r="K47" s="18" t="inlineStr"/>
+      <c r="L47" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="M47" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="N47" s="18" t="inlineStr"/>
+      <c r="O47" s="18" t="inlineStr"/>
     </row>
     <row r="48" outlineLevel="2">
-      <c r="B48" s="8" t="n"/>
-      <c r="C48" s="8" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="D48" s="8" t="n"/>
-      <c r="E48" s="8" t="n"/>
-      <c r="F48" s="8" t="n"/>
-      <c r="G48" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="H48" s="10" t="inlineStr">
+      <c r="B48" s="16" t="n"/>
+      <c r="C48" s="16" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="D48" s="16" t="n"/>
+      <c r="E48" s="16" t="n"/>
+      <c r="F48" s="16" t="n"/>
+      <c r="G48" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="H48" s="18" t="inlineStr">
         <is>
           <t>92423A462_High-Strength Duranium Socket Head Screw_ENT</t>
         </is>
       </c>
-      <c r="I48" s="10" t="inlineStr">
+      <c r="I48" s="18" t="inlineStr">
         <is>
           <t>92423A462 High-Strength Duranium Socket Head Screw ENT (92423A462_High-Strength Duranium Socket Head Screw_ENT.SLDPRT)</t>
         </is>
       </c>
-      <c r="J48" s="10" t="inlineStr"/>
-      <c r="K48" s="10" t="inlineStr"/>
-      <c r="L48" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="M48" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="N48" s="10" t="inlineStr">
+      <c r="J48" s="18" t="inlineStr"/>
+      <c r="K48" s="18" t="inlineStr"/>
+      <c r="L48" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="M48" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="N48" s="18" t="inlineStr">
         <is>
           <t>Duranium A286 Alloy</t>
         </is>
       </c>
-      <c r="O48" s="10" t="inlineStr">
+      <c r="O48" s="18" t="inlineStr">
         <is>
           <t>SW-Mass@.SLDPRT</t>
         </is>
       </c>
     </row>
     <row r="49" outlineLevel="1">
-      <c r="B49" s="8" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="C49" s="8" t="n"/>
-      <c r="D49" s="8" t="n"/>
-      <c r="E49" s="8" t="n"/>
-      <c r="F49" s="8" t="n"/>
-      <c r="G49" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="H49" s="9" t="inlineStr">
+      <c r="B49" s="16" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="C49" s="16" t="n"/>
+      <c r="D49" s="16" t="n"/>
+      <c r="E49" s="16" t="n"/>
+      <c r="F49" s="16" t="n"/>
+      <c r="G49" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="H49" s="17" t="inlineStr">
         <is>
           <t>NCC-FA014-00</t>
         </is>
       </c>
-      <c r="I49" s="9" t="inlineStr">
+      <c r="I49" s="17" t="inlineStr">
         <is>
           <t>1in Cell Mounted Plasma Injector 5-DOF Mount Port With Coil (NCC-FA014.SLDASM)</t>
         </is>
       </c>
-      <c r="J49" s="9" t="inlineStr">
+      <c r="J49" s="17" t="inlineStr">
         <is>
           <t>1in Cell Mounted Plasma Injector 5-DOF Mount Port With Coil</t>
         </is>
       </c>
-      <c r="K49" s="9" t="inlineStr"/>
-      <c r="L49" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="M49" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="N49" s="9" t="inlineStr"/>
-      <c r="O49" s="9" t="inlineStr"/>
+      <c r="K49" s="17" t="inlineStr"/>
+      <c r="L49" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="M49" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="N49" s="17" t="inlineStr"/>
+      <c r="O49" s="17" t="inlineStr"/>
     </row>
     <row r="50" outlineLevel="2">
-      <c r="B50" s="8" t="n"/>
-      <c r="C50" s="8" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="D50" s="8" t="n"/>
-      <c r="E50" s="8" t="n"/>
-      <c r="F50" s="8" t="n"/>
-      <c r="G50" s="9" t="n">
-        <v>2</v>
-      </c>
-      <c r="H50" s="9" t="inlineStr">
+      <c r="B50" s="16" t="n"/>
+      <c r="C50" s="16" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="D50" s="16" t="n"/>
+      <c r="E50" s="16" t="n"/>
+      <c r="F50" s="16" t="n"/>
+      <c r="G50" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="H50" s="17" t="inlineStr">
         <is>
           <t>NCC-FA004-00</t>
         </is>
       </c>
-      <c r="I50" s="9" t="inlineStr">
+      <c r="I50" s="17" t="inlineStr">
         <is>
           <t>Injector Mount Assembly Port No Coil (NCC-FA004.SLDASM)</t>
         </is>
       </c>
-      <c r="J50" s="9" t="inlineStr">
+      <c r="J50" s="17" t="inlineStr">
         <is>
           <t>1in Cell Mounted Plasma Injector 5-DOF Mount Port No Coil</t>
         </is>
       </c>
-      <c r="K50" s="9" t="inlineStr"/>
-      <c r="L50" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="M50" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="N50" s="9" t="inlineStr"/>
-      <c r="O50" s="9" t="inlineStr"/>
+      <c r="K50" s="17" t="inlineStr"/>
+      <c r="L50" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="M50" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="N50" s="17" t="inlineStr"/>
+      <c r="O50" s="17" t="inlineStr"/>
     </row>
     <row r="51" outlineLevel="3">
-      <c r="B51" s="8" t="n"/>
-      <c r="C51" s="8" t="n"/>
-      <c r="D51" s="8" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="E51" s="8" t="n"/>
-      <c r="F51" s="8" t="n"/>
-      <c r="G51" s="10" t="n">
-        <v>3</v>
-      </c>
-      <c r="H51" s="10" t="inlineStr">
+      <c r="B51" s="16" t="n"/>
+      <c r="C51" s="16" t="n"/>
+      <c r="D51" s="16" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E51" s="16" t="n"/>
+      <c r="F51" s="16" t="n"/>
+      <c r="G51" s="18" t="n">
+        <v>3</v>
+      </c>
+      <c r="H51" s="18" t="inlineStr">
         <is>
           <t>NCC-FP005-02</t>
         </is>
       </c>
-      <c r="I51" s="10" t="inlineStr">
+      <c r="I51" s="18" t="inlineStr">
         <is>
           <t>Injector Base Port (NCC-FP005.SLDPRT)</t>
         </is>
       </c>
-      <c r="J51" s="10" t="inlineStr">
+      <c r="J51" s="18" t="inlineStr">
         <is>
           <t>INJECTOR BASE, 1" COIL</t>
         </is>
       </c>
-      <c r="K51" s="10" t="inlineStr"/>
-      <c r="L51" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="M51" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="N51" s="10" t="inlineStr"/>
-      <c r="O51" s="10" t="inlineStr"/>
+      <c r="K51" s="18" t="inlineStr"/>
+      <c r="L51" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="M51" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="N51" s="18" t="inlineStr"/>
+      <c r="O51" s="18" t="inlineStr"/>
     </row>
     <row r="52" outlineLevel="3">
-      <c r="B52" s="8" t="n"/>
-      <c r="C52" s="8" t="n"/>
-      <c r="D52" s="8" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="E52" s="8" t="n"/>
-      <c r="F52" s="8" t="n"/>
-      <c r="G52" s="10" t="n">
-        <v>3</v>
-      </c>
-      <c r="H52" s="10" t="inlineStr">
+      <c r="B52" s="16" t="n"/>
+      <c r="C52" s="16" t="n"/>
+      <c r="D52" s="16" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E52" s="16" t="n"/>
+      <c r="F52" s="16" t="n"/>
+      <c r="G52" s="18" t="n">
+        <v>3</v>
+      </c>
+      <c r="H52" s="18" t="inlineStr">
         <is>
           <t>96246A088_Duranium Helical Insert_WRP</t>
         </is>
       </c>
-      <c r="I52" s="10" t="inlineStr">
+      <c r="I52" s="18" t="inlineStr">
         <is>
           <t>Duranium Helical Insert (96246A088_Duranium Helical Insert_WRP.SLDPRT)</t>
         </is>
       </c>
-      <c r="J52" s="10" t="inlineStr">
+      <c r="J52" s="18" t="inlineStr">
         <is>
           <t>Duranium Helical Insert</t>
         </is>
       </c>
-      <c r="K52" s="10" t="inlineStr"/>
-      <c r="L52" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="M52" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="N52" s="10" t="inlineStr">
+      <c r="K52" s="18" t="inlineStr"/>
+      <c r="L52" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="M52" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="N52" s="18" t="inlineStr">
         <is>
           <t>Nitronium 60 Duranium Alloy</t>
         </is>
       </c>
-      <c r="O52" s="10" t="inlineStr"/>
+      <c r="O52" s="18" t="inlineStr"/>
     </row>
     <row r="53" outlineLevel="3">
-      <c r="B53" s="8" t="n"/>
-      <c r="C53" s="8" t="n"/>
-      <c r="D53" s="8" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="E53" s="8" t="n"/>
-      <c r="F53" s="8" t="n"/>
-      <c r="G53" s="10" t="n">
-        <v>3</v>
-      </c>
-      <c r="H53" s="10" t="inlineStr">
+      <c r="B53" s="16" t="n"/>
+      <c r="C53" s="16" t="n"/>
+      <c r="D53" s="16" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E53" s="16" t="n"/>
+      <c r="F53" s="16" t="n"/>
+      <c r="G53" s="18" t="n">
+        <v>3</v>
+      </c>
+      <c r="H53" s="18" t="inlineStr">
         <is>
           <t>90945A715_Tritanium Fleet Spec. Washer_WRP</t>
         </is>
       </c>
-      <c r="I53" s="10" t="inlineStr">
+      <c r="I53" s="18" t="inlineStr">
         <is>
           <t>Tritanium Fleet Spec. Washer (90945A715_Tritanium Fleet Spec. Washer_WRP.SLDPRT)</t>
         </is>
       </c>
-      <c r="J53" s="10" t="inlineStr">
+      <c r="J53" s="18" t="inlineStr">
         <is>
           <t>Tritanium Fleet Spec. Washer</t>
         </is>
       </c>
-      <c r="K53" s="10" t="inlineStr"/>
-      <c r="L53" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="M53" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="N53" s="10" t="inlineStr">
+      <c r="K53" s="18" t="inlineStr"/>
+      <c r="L53" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="M53" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="N53" s="18" t="inlineStr">
         <is>
           <t>Tritanium 18-8</t>
         </is>
       </c>
-      <c r="O53" s="10" t="inlineStr"/>
+      <c r="O53" s="18" t="inlineStr"/>
     </row>
     <row r="54" outlineLevel="3">
-      <c r="B54" s="8" t="n"/>
-      <c r="C54" s="8" t="n"/>
-      <c r="D54" s="8" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="E54" s="8" t="n"/>
-      <c r="F54" s="8" t="n"/>
-      <c r="G54" s="10" t="n">
-        <v>3</v>
-      </c>
-      <c r="H54" s="10" t="inlineStr">
+      <c r="B54" s="16" t="n"/>
+      <c r="C54" s="16" t="n"/>
+      <c r="D54" s="16" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E54" s="16" t="n"/>
+      <c r="F54" s="16" t="n"/>
+      <c r="G54" s="18" t="n">
+        <v>3</v>
+      </c>
+      <c r="H54" s="18" t="inlineStr">
         <is>
           <t>92423A458_High-Strength Duranium Socket Head Screw_WRP</t>
         </is>
       </c>
-      <c r="I54" s="10" t="inlineStr">
+      <c r="I54" s="18" t="inlineStr">
         <is>
           <t>High-Strength Duranium Socket Head Screw (92423A458_High-Strength Duranium Socket Head Screw_WRP.SLDPRT)</t>
         </is>
       </c>
-      <c r="J54" s="10" t="inlineStr">
+      <c r="J54" s="18" t="inlineStr">
         <is>
           <t>High-Strength Duranium Socket Head Screw</t>
         </is>
       </c>
-      <c r="K54" s="10" t="inlineStr"/>
-      <c r="L54" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="M54" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="N54" s="10" t="inlineStr">
+      <c r="K54" s="18" t="inlineStr"/>
+      <c r="L54" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="M54" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="N54" s="18" t="inlineStr">
         <is>
           <t>Duranium A286 Alloy</t>
         </is>
       </c>
-      <c r="O54" s="10" t="inlineStr"/>
+      <c r="O54" s="18" t="inlineStr"/>
     </row>
     <row r="55" outlineLevel="3">
-      <c r="B55" s="8" t="n"/>
-      <c r="C55" s="8" t="n"/>
-      <c r="D55" s="8" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="E55" s="8" t="n"/>
-      <c r="F55" s="8" t="n"/>
-      <c r="G55" s="10" t="n">
-        <v>3</v>
-      </c>
-      <c r="H55" s="10" t="inlineStr">
+      <c r="B55" s="16" t="n"/>
+      <c r="C55" s="16" t="n"/>
+      <c r="D55" s="16" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E55" s="16" t="n"/>
+      <c r="F55" s="16" t="n"/>
+      <c r="G55" s="18" t="n">
+        <v>3</v>
+      </c>
+      <c r="H55" s="18" t="inlineStr">
         <is>
           <t>Custom Injector Shim_WRP</t>
         </is>
       </c>
-      <c r="I55" s="10" t="inlineStr">
+      <c r="I55" s="18" t="inlineStr">
         <is>
           <t>Custom Injector Shim WRP (Custom Injector Shim_WRP.SLDPRT)</t>
         </is>
       </c>
-      <c r="J55" s="10" t="inlineStr"/>
-      <c r="K55" s="10" t="inlineStr"/>
-      <c r="L55" s="10" t="n">
-        <v>3</v>
-      </c>
-      <c r="M55" s="10" t="n">
-        <v>3</v>
-      </c>
-      <c r="N55" s="10" t="inlineStr"/>
-      <c r="O55" s="10" t="inlineStr"/>
+      <c r="J55" s="18" t="inlineStr"/>
+      <c r="K55" s="18" t="inlineStr"/>
+      <c r="L55" s="18" t="n">
+        <v>3</v>
+      </c>
+      <c r="M55" s="18" t="n">
+        <v>3</v>
+      </c>
+      <c r="N55" s="18" t="inlineStr"/>
+      <c r="O55" s="18" t="inlineStr"/>
     </row>
     <row r="56" outlineLevel="3">
-      <c r="B56" s="8" t="n"/>
-      <c r="C56" s="8" t="n"/>
-      <c r="D56" s="8" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="E56" s="8" t="n"/>
-      <c r="F56" s="8" t="n"/>
-      <c r="G56" s="10" t="n">
-        <v>3</v>
-      </c>
-      <c r="H56" s="10" t="inlineStr">
+      <c r="B56" s="16" t="n"/>
+      <c r="C56" s="16" t="n"/>
+      <c r="D56" s="16" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E56" s="16" t="n"/>
+      <c r="F56" s="16" t="n"/>
+      <c r="G56" s="18" t="n">
+        <v>3</v>
+      </c>
+      <c r="H56" s="18" t="inlineStr">
         <is>
           <t>NCC-FP006-02</t>
         </is>
       </c>
-      <c r="I56" s="10" t="inlineStr">
+      <c r="I56" s="18" t="inlineStr">
         <is>
           <t>1in Injector Stage Port (NCC-FP006.SLDPRT)</t>
         </is>
       </c>
-      <c r="J56" s="10" t="inlineStr">
+      <c r="J56" s="18" t="inlineStr">
         <is>
           <t>INJECTOR STAGE, 1" COIL</t>
         </is>
       </c>
-      <c r="K56" s="10" t="inlineStr"/>
-      <c r="L56" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="M56" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="N56" s="10" t="inlineStr"/>
-      <c r="O56" s="10" t="inlineStr"/>
+      <c r="K56" s="18" t="inlineStr"/>
+      <c r="L56" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="M56" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="N56" s="18" t="inlineStr"/>
+      <c r="O56" s="18" t="inlineStr"/>
     </row>
     <row r="57" outlineLevel="3">
-      <c r="B57" s="8" t="n"/>
-      <c r="C57" s="8" t="n"/>
-      <c r="D57" s="8" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="E57" s="8" t="n"/>
-      <c r="F57" s="8" t="n"/>
-      <c r="G57" s="10" t="n">
-        <v>3</v>
-      </c>
-      <c r="H57" s="10" t="inlineStr">
+      <c r="B57" s="16" t="n"/>
+      <c r="C57" s="16" t="n"/>
+      <c r="D57" s="16" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E57" s="16" t="n"/>
+      <c r="F57" s="16" t="n"/>
+      <c r="G57" s="18" t="n">
+        <v>3</v>
+      </c>
+      <c r="H57" s="18" t="inlineStr">
         <is>
           <t>90945A725_Tritanium Fleet Spec. Washer_WRP</t>
         </is>
       </c>
-      <c r="I57" s="10" t="inlineStr">
+      <c r="I57" s="18" t="inlineStr">
         <is>
           <t>Tritanium Fleet Spec. Washer (90945A725_Tritanium Fleet Spec. Washer_WRP.SLDPRT)</t>
         </is>
       </c>
-      <c r="J57" s="10" t="inlineStr">
+      <c r="J57" s="18" t="inlineStr">
         <is>
           <t>Tritanium Fleet Spec. Washer</t>
         </is>
       </c>
-      <c r="K57" s="10" t="inlineStr"/>
-      <c r="L57" s="10" t="n">
-        <v>3</v>
-      </c>
-      <c r="M57" s="10" t="n">
-        <v>3</v>
-      </c>
-      <c r="N57" s="10" t="inlineStr">
+      <c r="K57" s="18" t="inlineStr"/>
+      <c r="L57" s="18" t="n">
+        <v>3</v>
+      </c>
+      <c r="M57" s="18" t="n">
+        <v>3</v>
+      </c>
+      <c r="N57" s="18" t="inlineStr">
         <is>
           <t>Tritanium 18-8</t>
         </is>
       </c>
-      <c r="O57" s="10" t="inlineStr"/>
+      <c r="O57" s="18" t="inlineStr"/>
     </row>
     <row r="58" outlineLevel="3">
-      <c r="B58" s="8" t="n"/>
-      <c r="C58" s="8" t="n"/>
-      <c r="D58" s="8" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="E58" s="8" t="n"/>
-      <c r="F58" s="8" t="n"/>
-      <c r="G58" s="10" t="n">
-        <v>3</v>
-      </c>
-      <c r="H58" s="10" t="inlineStr">
+      <c r="B58" s="16" t="n"/>
+      <c r="C58" s="16" t="n"/>
+      <c r="D58" s="16" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E58" s="16" t="n"/>
+      <c r="F58" s="16" t="n"/>
+      <c r="G58" s="18" t="n">
+        <v>3</v>
+      </c>
+      <c r="H58" s="18" t="inlineStr">
         <is>
           <t>96246A046_Duranium Helical Insert_WRP</t>
         </is>
       </c>
-      <c r="I58" s="10" t="inlineStr">
+      <c r="I58" s="18" t="inlineStr">
         <is>
           <t>Duranium Helical Insert (96246A046_Duranium Helical Insert_WRP.SLDPRT)</t>
         </is>
       </c>
-      <c r="J58" s="10" t="inlineStr">
+      <c r="J58" s="18" t="inlineStr">
         <is>
           <t>Duranium Helical Insert</t>
         </is>
       </c>
-      <c r="K58" s="10" t="inlineStr"/>
-      <c r="L58" s="10" t="n">
+      <c r="K58" s="18" t="inlineStr"/>
+      <c r="L58" s="18" t="n">
         <v>7</v>
       </c>
-      <c r="M58" s="10" t="n">
+      <c r="M58" s="18" t="n">
         <v>7</v>
       </c>
-      <c r="N58" s="10" t="inlineStr">
+      <c r="N58" s="18" t="inlineStr">
         <is>
           <t>Nitronium 60 Duranium Alloy</t>
         </is>
       </c>
-      <c r="O58" s="10" t="inlineStr"/>
+      <c r="O58" s="18" t="inlineStr"/>
     </row>
     <row r="59" outlineLevel="3">
-      <c r="B59" s="8" t="n"/>
-      <c r="C59" s="8" t="n"/>
-      <c r="D59" s="8" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="E59" s="8" t="n"/>
-      <c r="F59" s="8" t="n"/>
-      <c r="G59" s="10" t="n">
-        <v>3</v>
-      </c>
-      <c r="H59" s="10" t="inlineStr">
+      <c r="B59" s="16" t="n"/>
+      <c r="C59" s="16" t="n"/>
+      <c r="D59" s="16" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E59" s="16" t="n"/>
+      <c r="F59" s="16" t="n"/>
+      <c r="G59" s="18" t="n">
+        <v>3</v>
+      </c>
+      <c r="H59" s="18" t="inlineStr">
         <is>
           <t>NCC-FP007-00</t>
         </is>
       </c>
-      <c r="I59" s="10" t="inlineStr">
+      <c r="I59" s="18" t="inlineStr">
         <is>
           <t>Coil Glue Bond (NCC-FP007.SLDPRT)</t>
         </is>
       </c>
-      <c r="J59" s="10" t="inlineStr">
+      <c r="J59" s="18" t="inlineStr">
         <is>
           <t>Sinlge 2216 bond for 1in coil.</t>
         </is>
       </c>
-      <c r="K59" s="10" t="inlineStr"/>
-      <c r="L59" s="10" t="n">
-        <v>3</v>
-      </c>
-      <c r="M59" s="10" t="n">
-        <v>3</v>
-      </c>
-      <c r="N59" s="10" t="inlineStr"/>
-      <c r="O59" s="10" t="inlineStr"/>
+      <c r="K59" s="18" t="inlineStr"/>
+      <c r="L59" s="18" t="n">
+        <v>3</v>
+      </c>
+      <c r="M59" s="18" t="n">
+        <v>3</v>
+      </c>
+      <c r="N59" s="18" t="inlineStr"/>
+      <c r="O59" s="18" t="inlineStr"/>
     </row>
     <row r="60" outlineLevel="3">
-      <c r="B60" s="8" t="n"/>
-      <c r="C60" s="8" t="n"/>
-      <c r="D60" s="8" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="E60" s="8" t="n"/>
-      <c r="F60" s="8" t="n"/>
-      <c r="G60" s="10" t="n">
-        <v>3</v>
-      </c>
-      <c r="H60" s="10" t="inlineStr">
+      <c r="B60" s="16" t="n"/>
+      <c r="C60" s="16" t="n"/>
+      <c r="D60" s="16" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E60" s="16" t="n"/>
+      <c r="F60" s="16" t="n"/>
+      <c r="G60" s="18" t="n">
+        <v>3</v>
+      </c>
+      <c r="H60" s="18" t="inlineStr">
         <is>
           <t>NCC-FP004-B</t>
         </is>
       </c>
-      <c r="I60" s="10" t="inlineStr">
+      <c r="I60" s="18" t="inlineStr">
         <is>
           <t>1in Injector Radial Cell (NCC-FP004.SLDPRT)</t>
         </is>
       </c>
-      <c r="J60" s="10" t="inlineStr">
+      <c r="J60" s="18" t="inlineStr">
         <is>
           <t>Radial Cell of Injector 3DOF or 5DOF Coil Mount</t>
         </is>
       </c>
-      <c r="K60" s="10" t="inlineStr"/>
-      <c r="L60" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="M60" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="N60" s="10" t="inlineStr">
+      <c r="K60" s="18" t="inlineStr"/>
+      <c r="L60" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="M60" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="N60" s="18" t="inlineStr">
         <is>
           <t>Tritanium-36 Plate</t>
         </is>
       </c>
-      <c r="O60" s="10" t="inlineStr">
+      <c r="O60" s="18" t="inlineStr">
         <is>
           <t>0.064</t>
         </is>
       </c>
     </row>
     <row r="61" outlineLevel="3">
-      <c r="B61" s="8" t="n"/>
-      <c r="C61" s="8" t="n"/>
-      <c r="D61" s="8" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="E61" s="8" t="n"/>
-      <c r="F61" s="8" t="n"/>
-      <c r="G61" s="10" t="n">
-        <v>3</v>
-      </c>
-      <c r="H61" s="10" t="inlineStr">
+      <c r="B61" s="16" t="n"/>
+      <c r="C61" s="16" t="n"/>
+      <c r="D61" s="16" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E61" s="16" t="n"/>
+      <c r="F61" s="16" t="n"/>
+      <c r="G61" s="18" t="n">
+        <v>3</v>
+      </c>
+      <c r="H61" s="18" t="inlineStr">
         <is>
           <t>92423A491_High-Strength Duranium Socket Head Screw_WRP</t>
         </is>
       </c>
-      <c r="I61" s="10" t="inlineStr">
+      <c r="I61" s="18" t="inlineStr">
         <is>
           <t>High-Strength Duranium Socket Head Screw (92423A491_High-Strength Duranium Socket Head Screw_WRP.SLDPRT)</t>
         </is>
       </c>
-      <c r="J61" s="10" t="inlineStr">
+      <c r="J61" s="18" t="inlineStr">
         <is>
           <t>High-Strength Duranium Socket Head Screw</t>
         </is>
       </c>
-      <c r="K61" s="10" t="inlineStr"/>
-      <c r="L61" s="10" t="n">
-        <v>3</v>
-      </c>
-      <c r="M61" s="10" t="n">
-        <v>3</v>
-      </c>
-      <c r="N61" s="10" t="inlineStr">
+      <c r="K61" s="18" t="inlineStr"/>
+      <c r="L61" s="18" t="n">
+        <v>3</v>
+      </c>
+      <c r="M61" s="18" t="n">
+        <v>3</v>
+      </c>
+      <c r="N61" s="18" t="inlineStr">
         <is>
           <t>Duranium A286 Alloy</t>
         </is>
       </c>
-      <c r="O61" s="10" t="inlineStr"/>
+      <c r="O61" s="18" t="inlineStr"/>
     </row>
     <row r="62" outlineLevel="3">
-      <c r="B62" s="8" t="n"/>
-      <c r="C62" s="8" t="n"/>
-      <c r="D62" s="8" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="E62" s="8" t="n"/>
-      <c r="F62" s="8" t="n"/>
-      <c r="G62" s="9" t="n">
-        <v>3</v>
-      </c>
-      <c r="H62" s="9" t="inlineStr">
+      <c r="B62" s="16" t="n"/>
+      <c r="C62" s="16" t="n"/>
+      <c r="D62" s="16" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E62" s="16" t="n"/>
+      <c r="F62" s="16" t="n"/>
+      <c r="G62" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="H62" s="17" t="inlineStr">
         <is>
           <t>AK000007S_WRP</t>
         </is>
       </c>
-      <c r="I62" s="9" t="inlineStr">
+      <c r="I62" s="17" t="inlineStr">
         <is>
           <t>AK000007S WRP (AK000007S_WRP.SLDASM)</t>
         </is>
       </c>
-      <c r="J62" s="9" t="inlineStr"/>
-      <c r="K62" s="9" t="inlineStr"/>
-      <c r="L62" s="9" t="n">
+      <c r="J62" s="17" t="inlineStr"/>
+      <c r="K62" s="17" t="inlineStr"/>
+      <c r="L62" s="17" t="n">
         <v>6</v>
       </c>
-      <c r="M62" s="9" t="n">
+      <c r="M62" s="17" t="n">
         <v>6</v>
       </c>
-      <c r="N62" s="9" t="inlineStr"/>
-      <c r="O62" s="9" t="inlineStr"/>
+      <c r="N62" s="17" t="inlineStr"/>
+      <c r="O62" s="17" t="inlineStr"/>
     </row>
     <row r="63" outlineLevel="4">
-      <c r="B63" s="8" t="n"/>
-      <c r="C63" s="8" t="n"/>
-      <c r="D63" s="8" t="n"/>
-      <c r="E63" s="8" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="F63" s="8" t="n"/>
-      <c r="G63" s="10" t="n">
+      <c r="B63" s="16" t="n"/>
+      <c r="C63" s="16" t="n"/>
+      <c r="D63" s="16" t="n"/>
+      <c r="E63" s="16" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F63" s="16" t="n"/>
+      <c r="G63" s="18" t="n">
         <v>4</v>
       </c>
-      <c r="H63" s="10" t="inlineStr">
+      <c r="H63" s="18" t="inlineStr">
         <is>
           <t>AK020004 EPS Tap Rev A_WRP</t>
         </is>
       </c>
-      <c r="I63" s="10" t="inlineStr">
+      <c r="I63" s="18" t="inlineStr">
         <is>
           <t>AK020004 EPS Tap Rev A WRP (AK020004 EPS Tap Rev A_WRP.SLDPRT)</t>
         </is>
       </c>
-      <c r="J63" s="10" t="inlineStr"/>
-      <c r="K63" s="10" t="inlineStr"/>
-      <c r="L63" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="M63" s="10" t="n">
+      <c r="J63" s="18" t="inlineStr"/>
+      <c r="K63" s="18" t="inlineStr"/>
+      <c r="L63" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="M63" s="18" t="n">
         <v>6</v>
       </c>
-      <c r="N63" s="10" t="inlineStr"/>
-      <c r="O63" s="10" t="inlineStr"/>
+      <c r="N63" s="18" t="inlineStr"/>
+      <c r="O63" s="18" t="inlineStr"/>
     </row>
     <row r="64" outlineLevel="4">
-      <c r="B64" s="8" t="n"/>
-      <c r="C64" s="8" t="n"/>
-      <c r="D64" s="8" t="n"/>
-      <c r="E64" s="8" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="F64" s="8" t="n"/>
-      <c r="G64" s="10" t="n">
+      <c r="B64" s="16" t="n"/>
+      <c r="C64" s="16" t="n"/>
+      <c r="D64" s="16" t="n"/>
+      <c r="E64" s="16" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F64" s="16" t="n"/>
+      <c r="G64" s="18" t="n">
         <v>4</v>
       </c>
-      <c r="H64" s="10" t="inlineStr">
+      <c r="H64" s="18" t="inlineStr">
         <is>
           <t>HD301004 SBS 92196A108_Tritanium Socket Head Screw_WRP</t>
         </is>
       </c>
-      <c r="I64" s="10" t="inlineStr">
+      <c r="I64" s="18" t="inlineStr">
         <is>
           <t>Tritanium Socket Head Screw (HD301004 SBS 92196A108_Tritanium Socket Head Screw_WRP.SLDPRT)</t>
         </is>
       </c>
-      <c r="J64" s="10" t="inlineStr">
+      <c r="J64" s="18" t="inlineStr">
         <is>
           <t>Tritanium Socket Head Screw</t>
         </is>
       </c>
-      <c r="K64" s="10" t="inlineStr"/>
-      <c r="L64" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="M64" s="10" t="n">
+      <c r="K64" s="18" t="inlineStr"/>
+      <c r="L64" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="M64" s="18" t="n">
         <v>6</v>
       </c>
-      <c r="N64" s="10" t="inlineStr">
+      <c r="N64" s="18" t="inlineStr">
         <is>
           <t>Tritanium 18-8</t>
         </is>
       </c>
-      <c r="O64" s="10" t="inlineStr"/>
+      <c r="O64" s="18" t="inlineStr"/>
     </row>
     <row r="65" outlineLevel="4">
-      <c r="B65" s="8" t="n"/>
-      <c r="C65" s="8" t="n"/>
-      <c r="D65" s="8" t="n"/>
-      <c r="E65" s="8" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="F65" s="8" t="n"/>
-      <c r="G65" s="10" t="n">
+      <c r="B65" s="16" t="n"/>
+      <c r="C65" s="16" t="n"/>
+      <c r="D65" s="16" t="n"/>
+      <c r="E65" s="16" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F65" s="16" t="n"/>
+      <c r="G65" s="18" t="n">
         <v>4</v>
       </c>
-      <c r="H65" s="10" t="inlineStr">
+      <c r="H65" s="18" t="inlineStr">
         <is>
           <t>HD101004 EPS Tap Adjuster Rev B_WRP</t>
         </is>
       </c>
-      <c r="I65" s="10" t="inlineStr">
+      <c r="I65" s="18" t="inlineStr">
         <is>
           <t>HD101004 EPS Tap Adjuster Rev B WRP (HD101004 EPS Tap Adjuster Rev B_WRP.SLDPRT)</t>
         </is>
       </c>
-      <c r="J65" s="10" t="inlineStr"/>
-      <c r="K65" s="10" t="inlineStr"/>
-      <c r="L65" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="M65" s="10" t="n">
+      <c r="J65" s="18" t="inlineStr"/>
+      <c r="K65" s="18" t="inlineStr"/>
+      <c r="L65" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="M65" s="18" t="n">
         <v>6</v>
       </c>
-      <c r="N65" s="10" t="inlineStr"/>
-      <c r="O65" s="10" t="inlineStr"/>
+      <c r="N65" s="18" t="inlineStr"/>
+      <c r="O65" s="18" t="inlineStr"/>
     </row>
     <row r="66" outlineLevel="2">
-      <c r="B66" s="8" t="n"/>
-      <c r="C66" s="8" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="D66" s="8" t="n"/>
-      <c r="E66" s="8" t="n"/>
-      <c r="F66" s="8" t="n"/>
-      <c r="G66" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="H66" s="10" t="inlineStr">
+      <c r="B66" s="16" t="n"/>
+      <c r="C66" s="16" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="D66" s="16" t="n"/>
+      <c r="E66" s="16" t="n"/>
+      <c r="F66" s="16" t="n"/>
+      <c r="G66" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="H66" s="18" t="inlineStr">
         <is>
           <t>NCC-FP053-00</t>
         </is>
       </c>
-      <c r="I66" s="10" t="inlineStr">
+      <c r="I66" s="18" t="inlineStr">
         <is>
           <t>Emitter - Coil2 (NCC-FP053.SLDPRT)</t>
         </is>
       </c>
-      <c r="J66" s="10" t="inlineStr">
+      <c r="J66" s="18" t="inlineStr">
         <is>
           <t>Fore Coil2</t>
         </is>
       </c>
-      <c r="K66" s="10" t="inlineStr"/>
-      <c r="L66" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="M66" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="N66" s="10" t="inlineStr">
+      <c r="K66" s="18" t="inlineStr"/>
+      <c r="L66" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="M66" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="N66" s="18" t="inlineStr">
         <is>
           <t>Transparent Aluminum</t>
         </is>
       </c>
-      <c r="O66" s="10" t="inlineStr">
+      <c r="O66" s="18" t="inlineStr">
         <is>
           <t>0.01</t>
         </is>
@@ -2584,11 +2734,12 @@
     </row>
   </sheetData>
   <autoFilter ref="G17:O66"/>
-  <mergeCells count="9">
+  <mergeCells count="10">
     <mergeCell ref="B10:G10"/>
     <mergeCell ref="B16:F16"/>
     <mergeCell ref="L16:M16"/>
     <mergeCell ref="B9:G9"/>
+    <mergeCell ref="B2:O5"/>
     <mergeCell ref="B12:G12"/>
     <mergeCell ref="B13:G13"/>
     <mergeCell ref="B7:G7"/>

--- a/examples/NCC-1701_pdmout_BOM.xlsx
+++ b/examples/NCC-1701_pdmout_BOM.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="BOM" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BOM" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'BOM'!$G$17:$O$66</definedName>

--- a/examples/NCC-1701_pdmout_BOM.xlsx
+++ b/examples/NCC-1701_pdmout_BOM.xlsx
@@ -19,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -41,6 +41,10 @@
       <name val="Aptos Narrow"/>
       <b val="1"/>
       <sz val="14"/>
+    </font>
+    <font>
+      <name val="Aptos Narrow"/>
+      <sz val="8"/>
     </font>
     <font>
       <name val="Aptos Narrow"/>
@@ -170,7 +174,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -184,6 +188,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -193,11 +198,11 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -678,124 +683,131 @@
         </is>
       </c>
     </row>
+    <row r="14">
+      <c r="B14" s="11" t="inlineStr">
+        <is>
+          <t>Source BOM: examples/NCC-1701_pdmout.csv · Config: bomgen.toml · bomgen: 0.1.0 · Python: 3.11.15 · openpyxl: 3.1.5 · Generated: 2026-07-20 05:46</t>
+        </is>
+      </c>
+    </row>
     <row r="16">
-      <c r="B16" s="11" t="inlineStr">
+      <c r="B16" s="12" t="inlineStr">
         <is>
           <t>Assembly Level</t>
         </is>
       </c>
-      <c r="C16" s="12" t="n"/>
-      <c r="D16" s="12" t="n"/>
-      <c r="E16" s="12" t="n"/>
-      <c r="F16" s="12" t="n"/>
-      <c r="G16" s="12" t="n"/>
-      <c r="H16" s="12" t="n"/>
-      <c r="I16" s="12" t="n"/>
-      <c r="J16" s="12" t="n"/>
-      <c r="K16" s="12" t="n"/>
-      <c r="L16" s="13" t="inlineStr">
+      <c r="C16" s="13" t="n"/>
+      <c r="D16" s="13" t="n"/>
+      <c r="E16" s="13" t="n"/>
+      <c r="F16" s="13" t="n"/>
+      <c r="G16" s="13" t="n"/>
+      <c r="H16" s="13" t="n"/>
+      <c r="I16" s="13" t="n"/>
+      <c r="J16" s="13" t="n"/>
+      <c r="K16" s="13" t="n"/>
+      <c r="L16" s="14" t="inlineStr">
         <is>
           <t>Quantity Required</t>
         </is>
       </c>
-      <c r="M16" s="12" t="n"/>
-      <c r="N16" s="12" t="n"/>
-      <c r="O16" s="12" t="n"/>
+      <c r="M16" s="13" t="n"/>
+      <c r="N16" s="13" t="n"/>
+      <c r="O16" s="13" t="n"/>
     </row>
     <row r="17">
-      <c r="B17" s="14" t="inlineStr">
+      <c r="B17" s="15" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="C17" s="14" t="inlineStr">
+      <c r="C17" s="15" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D17" s="14" t="inlineStr">
+      <c r="D17" s="15" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E17" s="14" t="inlineStr">
+      <c r="E17" s="15" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="F17" s="14" t="inlineStr">
+      <c r="F17" s="15" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="G17" s="13" t="inlineStr">
+      <c r="G17" s="14" t="inlineStr">
         <is>
           <t>Level</t>
         </is>
       </c>
-      <c r="H17" s="13" t="inlineStr">
+      <c r="H17" s="14" t="inlineStr">
         <is>
           <t>Abbreviated Part Number</t>
         </is>
       </c>
-      <c r="I17" s="13" t="inlineStr">
+      <c r="I17" s="14" t="inlineStr">
         <is>
           <t>Part Name</t>
         </is>
       </c>
-      <c r="J17" s="13" t="inlineStr">
+      <c r="J17" s="14" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
-      <c r="K17" s="13" t="inlineStr">
+      <c r="K17" s="14" t="inlineStr">
         <is>
           <t>COTS</t>
         </is>
       </c>
-      <c r="L17" s="13" t="inlineStr">
+      <c r="L17" s="14" t="inlineStr">
         <is>
           <t>Qty (Assembly)</t>
         </is>
       </c>
-      <c r="M17" s="13" t="inlineStr">
+      <c r="M17" s="14" t="inlineStr">
         <is>
           <t>Qty (Total)</t>
         </is>
       </c>
-      <c r="N17" s="13" t="inlineStr">
+      <c r="N17" s="14" t="inlineStr">
         <is>
           <t>Material</t>
         </is>
       </c>
-      <c r="O17" s="13" t="inlineStr">
+      <c r="O17" s="14" t="inlineStr">
         <is>
           <t>Mass</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="B18" s="15" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="C18" s="15" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="D18" s="15" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="E18" s="15" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="F18" s="15" t="inlineStr">
+      <c r="B18" s="16" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="C18" s="16" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="D18" s="16" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E18" s="16" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F18" s="16" t="inlineStr">
         <is>
           <t>X</t>
         </is>
@@ -829,1904 +841,1904 @@
       <c r="O18" s="10" t="inlineStr"/>
     </row>
     <row r="19" outlineLevel="1">
-      <c r="B19" s="16" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="C19" s="16" t="n"/>
-      <c r="D19" s="16" t="n"/>
-      <c r="E19" s="16" t="n"/>
-      <c r="F19" s="16" t="n"/>
-      <c r="G19" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="H19" s="17" t="inlineStr">
+      <c r="B19" s="17" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="C19" s="17" t="n"/>
+      <c r="D19" s="17" t="n"/>
+      <c r="E19" s="17" t="n"/>
+      <c r="F19" s="17" t="n"/>
+      <c r="G19" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="H19" s="18" t="inlineStr">
         <is>
           <t>NCC-FA014-00</t>
         </is>
       </c>
-      <c r="I19" s="17" t="inlineStr">
+      <c r="I19" s="18" t="inlineStr">
         <is>
           <t>1in Cell Mounted Plasma Injector 5-DOF Mount Port With Coil (NCC-FA014.SLDASM)</t>
         </is>
       </c>
-      <c r="J19" s="17" t="inlineStr">
+      <c r="J19" s="18" t="inlineStr">
         <is>
           <t>1in Cell Mounted Plasma Injector 5-DOF Mount Port With Coil</t>
         </is>
       </c>
-      <c r="K19" s="17" t="inlineStr"/>
-      <c r="L19" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="M19" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="N19" s="17" t="inlineStr"/>
-      <c r="O19" s="17" t="inlineStr"/>
+      <c r="K19" s="18" t="inlineStr"/>
+      <c r="L19" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="M19" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="N19" s="18" t="inlineStr"/>
+      <c r="O19" s="18" t="inlineStr"/>
     </row>
     <row r="20" outlineLevel="2">
-      <c r="B20" s="16" t="n"/>
-      <c r="C20" s="16" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="D20" s="16" t="n"/>
-      <c r="E20" s="16" t="n"/>
-      <c r="F20" s="16" t="n"/>
-      <c r="G20" s="17" t="n">
-        <v>2</v>
-      </c>
-      <c r="H20" s="17" t="inlineStr">
+      <c r="B20" s="17" t="n"/>
+      <c r="C20" s="17" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="D20" s="17" t="n"/>
+      <c r="E20" s="17" t="n"/>
+      <c r="F20" s="17" t="n"/>
+      <c r="G20" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="H20" s="18" t="inlineStr">
         <is>
           <t>NCC-FA004-00</t>
         </is>
       </c>
-      <c r="I20" s="17" t="inlineStr">
+      <c r="I20" s="18" t="inlineStr">
         <is>
           <t>Injector Mount Assembly Port No Coil (NCC-FA004.SLDASM)</t>
         </is>
       </c>
-      <c r="J20" s="17" t="inlineStr">
+      <c r="J20" s="18" t="inlineStr">
         <is>
           <t>1in Cell Mounted Plasma Injector 5-DOF Mount Port No Coil</t>
         </is>
       </c>
-      <c r="K20" s="17" t="inlineStr"/>
-      <c r="L20" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="M20" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="N20" s="17" t="inlineStr"/>
-      <c r="O20" s="17" t="inlineStr"/>
+      <c r="K20" s="18" t="inlineStr"/>
+      <c r="L20" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="M20" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="N20" s="18" t="inlineStr"/>
+      <c r="O20" s="18" t="inlineStr"/>
     </row>
     <row r="21" outlineLevel="3">
-      <c r="B21" s="16" t="n"/>
-      <c r="C21" s="16" t="n"/>
-      <c r="D21" s="16" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="E21" s="16" t="n"/>
-      <c r="F21" s="16" t="n"/>
-      <c r="G21" s="18" t="n">
-        <v>3</v>
-      </c>
-      <c r="H21" s="18" t="inlineStr">
+      <c r="B21" s="17" t="n"/>
+      <c r="C21" s="17" t="n"/>
+      <c r="D21" s="17" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E21" s="17" t="n"/>
+      <c r="F21" s="17" t="n"/>
+      <c r="G21" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="H21" s="19" t="inlineStr">
         <is>
           <t>NCC-FP005-02</t>
         </is>
       </c>
-      <c r="I21" s="18" t="inlineStr">
+      <c r="I21" s="19" t="inlineStr">
         <is>
           <t>Injector Base Port (NCC-FP005.SLDPRT)</t>
         </is>
       </c>
-      <c r="J21" s="18" t="inlineStr">
+      <c r="J21" s="19" t="inlineStr">
         <is>
           <t>INJECTOR BASE, 1" COIL</t>
         </is>
       </c>
-      <c r="K21" s="18" t="inlineStr"/>
-      <c r="L21" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="M21" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="N21" s="18" t="inlineStr"/>
-      <c r="O21" s="18" t="inlineStr"/>
+      <c r="K21" s="19" t="inlineStr"/>
+      <c r="L21" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="M21" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="N21" s="19" t="inlineStr"/>
+      <c r="O21" s="19" t="inlineStr"/>
     </row>
     <row r="22" outlineLevel="3">
-      <c r="B22" s="16" t="n"/>
-      <c r="C22" s="16" t="n"/>
-      <c r="D22" s="16" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="E22" s="16" t="n"/>
-      <c r="F22" s="16" t="n"/>
-      <c r="G22" s="18" t="n">
-        <v>3</v>
-      </c>
-      <c r="H22" s="18" t="inlineStr">
+      <c r="B22" s="17" t="n"/>
+      <c r="C22" s="17" t="n"/>
+      <c r="D22" s="17" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E22" s="17" t="n"/>
+      <c r="F22" s="17" t="n"/>
+      <c r="G22" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="H22" s="19" t="inlineStr">
         <is>
           <t>96246A088_Duranium Helical Insert_WRP</t>
         </is>
       </c>
-      <c r="I22" s="18" t="inlineStr">
+      <c r="I22" s="19" t="inlineStr">
         <is>
           <t>Duranium Helical Insert (96246A088_Duranium Helical Insert_WRP.SLDPRT)</t>
         </is>
       </c>
-      <c r="J22" s="18" t="inlineStr">
+      <c r="J22" s="19" t="inlineStr">
         <is>
           <t>Duranium Helical Insert</t>
         </is>
       </c>
-      <c r="K22" s="18" t="inlineStr"/>
-      <c r="L22" s="18" t="n">
-        <v>2</v>
-      </c>
-      <c r="M22" s="18" t="n">
-        <v>2</v>
-      </c>
-      <c r="N22" s="18" t="inlineStr">
+      <c r="K22" s="19" t="inlineStr"/>
+      <c r="L22" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="M22" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="N22" s="19" t="inlineStr">
         <is>
           <t>Nitronium 60 Duranium Alloy</t>
         </is>
       </c>
-      <c r="O22" s="18" t="inlineStr"/>
+      <c r="O22" s="19" t="inlineStr"/>
     </row>
     <row r="23" outlineLevel="3">
-      <c r="B23" s="16" t="n"/>
-      <c r="C23" s="16" t="n"/>
-      <c r="D23" s="16" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="E23" s="16" t="n"/>
-      <c r="F23" s="16" t="n"/>
-      <c r="G23" s="18" t="n">
-        <v>3</v>
-      </c>
-      <c r="H23" s="18" t="inlineStr">
+      <c r="B23" s="17" t="n"/>
+      <c r="C23" s="17" t="n"/>
+      <c r="D23" s="17" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E23" s="17" t="n"/>
+      <c r="F23" s="17" t="n"/>
+      <c r="G23" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="H23" s="19" t="inlineStr">
         <is>
           <t>90945A715_Tritanium Fleet Spec. Washer_WRP</t>
         </is>
       </c>
-      <c r="I23" s="18" t="inlineStr">
+      <c r="I23" s="19" t="inlineStr">
         <is>
           <t>Tritanium Fleet Spec. Washer (90945A715_Tritanium Fleet Spec. Washer_WRP.SLDPRT)</t>
         </is>
       </c>
-      <c r="J23" s="18" t="inlineStr">
+      <c r="J23" s="19" t="inlineStr">
         <is>
           <t>Tritanium Fleet Spec. Washer</t>
         </is>
       </c>
-      <c r="K23" s="18" t="inlineStr"/>
-      <c r="L23" s="18" t="n">
-        <v>2</v>
-      </c>
-      <c r="M23" s="18" t="n">
-        <v>2</v>
-      </c>
-      <c r="N23" s="18" t="inlineStr">
+      <c r="K23" s="19" t="inlineStr"/>
+      <c r="L23" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="M23" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="N23" s="19" t="inlineStr">
         <is>
           <t>Tritanium 18-8</t>
         </is>
       </c>
-      <c r="O23" s="18" t="inlineStr"/>
+      <c r="O23" s="19" t="inlineStr"/>
     </row>
     <row r="24" outlineLevel="3">
-      <c r="B24" s="16" t="n"/>
-      <c r="C24" s="16" t="n"/>
-      <c r="D24" s="16" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="E24" s="16" t="n"/>
-      <c r="F24" s="16" t="n"/>
-      <c r="G24" s="18" t="n">
-        <v>3</v>
-      </c>
-      <c r="H24" s="18" t="inlineStr">
+      <c r="B24" s="17" t="n"/>
+      <c r="C24" s="17" t="n"/>
+      <c r="D24" s="17" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E24" s="17" t="n"/>
+      <c r="F24" s="17" t="n"/>
+      <c r="G24" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="H24" s="19" t="inlineStr">
         <is>
           <t>92423A458_High-Strength Duranium Socket Head Screw_WRP</t>
         </is>
       </c>
-      <c r="I24" s="18" t="inlineStr">
+      <c r="I24" s="19" t="inlineStr">
         <is>
           <t>High-Strength Duranium Socket Head Screw (92423A458_High-Strength Duranium Socket Head Screw_WRP.SLDPRT)</t>
         </is>
       </c>
-      <c r="J24" s="18" t="inlineStr">
+      <c r="J24" s="19" t="inlineStr">
         <is>
           <t>High-Strength Duranium Socket Head Screw</t>
         </is>
       </c>
-      <c r="K24" s="18" t="inlineStr"/>
-      <c r="L24" s="18" t="n">
-        <v>2</v>
-      </c>
-      <c r="M24" s="18" t="n">
-        <v>2</v>
-      </c>
-      <c r="N24" s="18" t="inlineStr">
+      <c r="K24" s="19" t="inlineStr"/>
+      <c r="L24" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="M24" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="N24" s="19" t="inlineStr">
         <is>
           <t>Duranium A286 Alloy</t>
         </is>
       </c>
-      <c r="O24" s="18" t="inlineStr"/>
+      <c r="O24" s="19" t="inlineStr"/>
     </row>
     <row r="25" outlineLevel="3">
-      <c r="B25" s="16" t="n"/>
-      <c r="C25" s="16" t="n"/>
-      <c r="D25" s="16" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="E25" s="16" t="n"/>
-      <c r="F25" s="16" t="n"/>
-      <c r="G25" s="18" t="n">
-        <v>3</v>
-      </c>
-      <c r="H25" s="18" t="inlineStr">
+      <c r="B25" s="17" t="n"/>
+      <c r="C25" s="17" t="n"/>
+      <c r="D25" s="17" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E25" s="17" t="n"/>
+      <c r="F25" s="17" t="n"/>
+      <c r="G25" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="H25" s="19" t="inlineStr">
         <is>
           <t>Custom Injector Shim_WRP</t>
         </is>
       </c>
-      <c r="I25" s="18" t="inlineStr">
+      <c r="I25" s="19" t="inlineStr">
         <is>
           <t>Custom Injector Shim WRP (Custom Injector Shim_WRP.SLDPRT)</t>
         </is>
       </c>
-      <c r="J25" s="18" t="inlineStr"/>
-      <c r="K25" s="18" t="inlineStr"/>
-      <c r="L25" s="18" t="n">
-        <v>3</v>
-      </c>
-      <c r="M25" s="18" t="n">
-        <v>3</v>
-      </c>
-      <c r="N25" s="18" t="inlineStr"/>
-      <c r="O25" s="18" t="inlineStr"/>
+      <c r="J25" s="19" t="inlineStr"/>
+      <c r="K25" s="19" t="inlineStr"/>
+      <c r="L25" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="M25" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="N25" s="19" t="inlineStr"/>
+      <c r="O25" s="19" t="inlineStr"/>
     </row>
     <row r="26" outlineLevel="3">
-      <c r="B26" s="16" t="n"/>
-      <c r="C26" s="16" t="n"/>
-      <c r="D26" s="16" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="E26" s="16" t="n"/>
-      <c r="F26" s="16" t="n"/>
-      <c r="G26" s="18" t="n">
-        <v>3</v>
-      </c>
-      <c r="H26" s="18" t="inlineStr">
+      <c r="B26" s="17" t="n"/>
+      <c r="C26" s="17" t="n"/>
+      <c r="D26" s="17" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E26" s="17" t="n"/>
+      <c r="F26" s="17" t="n"/>
+      <c r="G26" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="H26" s="19" t="inlineStr">
         <is>
           <t>NCC-FP006-02</t>
         </is>
       </c>
-      <c r="I26" s="18" t="inlineStr">
+      <c r="I26" s="19" t="inlineStr">
         <is>
           <t>1in Injector Stage Port (NCC-FP006.SLDPRT)</t>
         </is>
       </c>
-      <c r="J26" s="18" t="inlineStr">
+      <c r="J26" s="19" t="inlineStr">
         <is>
           <t>INJECTOR STAGE, 1" COIL</t>
         </is>
       </c>
-      <c r="K26" s="18" t="inlineStr"/>
-      <c r="L26" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="M26" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="N26" s="18" t="inlineStr"/>
-      <c r="O26" s="18" t="inlineStr"/>
+      <c r="K26" s="19" t="inlineStr"/>
+      <c r="L26" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="M26" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="N26" s="19" t="inlineStr"/>
+      <c r="O26" s="19" t="inlineStr"/>
     </row>
     <row r="27" outlineLevel="3">
-      <c r="B27" s="16" t="n"/>
-      <c r="C27" s="16" t="n"/>
-      <c r="D27" s="16" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="E27" s="16" t="n"/>
-      <c r="F27" s="16" t="n"/>
-      <c r="G27" s="18" t="n">
-        <v>3</v>
-      </c>
-      <c r="H27" s="18" t="inlineStr">
+      <c r="B27" s="17" t="n"/>
+      <c r="C27" s="17" t="n"/>
+      <c r="D27" s="17" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E27" s="17" t="n"/>
+      <c r="F27" s="17" t="n"/>
+      <c r="G27" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="H27" s="19" t="inlineStr">
         <is>
           <t>90945A725_Tritanium Fleet Spec. Washer_WRP</t>
         </is>
       </c>
-      <c r="I27" s="18" t="inlineStr">
+      <c r="I27" s="19" t="inlineStr">
         <is>
           <t>Tritanium Fleet Spec. Washer (90945A725_Tritanium Fleet Spec. Washer_WRP.SLDPRT)</t>
         </is>
       </c>
-      <c r="J27" s="18" t="inlineStr">
+      <c r="J27" s="19" t="inlineStr">
         <is>
           <t>Tritanium Fleet Spec. Washer</t>
         </is>
       </c>
-      <c r="K27" s="18" t="inlineStr"/>
-      <c r="L27" s="18" t="n">
-        <v>3</v>
-      </c>
-      <c r="M27" s="18" t="n">
-        <v>3</v>
-      </c>
-      <c r="N27" s="18" t="inlineStr">
+      <c r="K27" s="19" t="inlineStr"/>
+      <c r="L27" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="M27" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="N27" s="19" t="inlineStr">
         <is>
           <t>Tritanium 18-8</t>
         </is>
       </c>
-      <c r="O27" s="18" t="inlineStr"/>
+      <c r="O27" s="19" t="inlineStr"/>
     </row>
     <row r="28" outlineLevel="3">
-      <c r="B28" s="16" t="n"/>
-      <c r="C28" s="16" t="n"/>
-      <c r="D28" s="16" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="E28" s="16" t="n"/>
-      <c r="F28" s="16" t="n"/>
-      <c r="G28" s="18" t="n">
-        <v>3</v>
-      </c>
-      <c r="H28" s="18" t="inlineStr">
+      <c r="B28" s="17" t="n"/>
+      <c r="C28" s="17" t="n"/>
+      <c r="D28" s="17" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E28" s="17" t="n"/>
+      <c r="F28" s="17" t="n"/>
+      <c r="G28" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="H28" s="19" t="inlineStr">
         <is>
           <t>96246A046_Duranium Helical Insert_WRP</t>
         </is>
       </c>
-      <c r="I28" s="18" t="inlineStr">
+      <c r="I28" s="19" t="inlineStr">
         <is>
           <t>Duranium Helical Insert (96246A046_Duranium Helical Insert_WRP.SLDPRT)</t>
         </is>
       </c>
-      <c r="J28" s="18" t="inlineStr">
+      <c r="J28" s="19" t="inlineStr">
         <is>
           <t>Duranium Helical Insert</t>
         </is>
       </c>
-      <c r="K28" s="18" t="inlineStr"/>
-      <c r="L28" s="18" t="n">
+      <c r="K28" s="19" t="inlineStr"/>
+      <c r="L28" s="19" t="n">
         <v>7</v>
       </c>
-      <c r="M28" s="18" t="n">
+      <c r="M28" s="19" t="n">
         <v>7</v>
       </c>
-      <c r="N28" s="18" t="inlineStr">
+      <c r="N28" s="19" t="inlineStr">
         <is>
           <t>Nitronium 60 Duranium Alloy</t>
         </is>
       </c>
-      <c r="O28" s="18" t="inlineStr"/>
+      <c r="O28" s="19" t="inlineStr"/>
     </row>
     <row r="29" outlineLevel="3">
-      <c r="B29" s="16" t="n"/>
-      <c r="C29" s="16" t="n"/>
-      <c r="D29" s="16" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="E29" s="16" t="n"/>
-      <c r="F29" s="16" t="n"/>
-      <c r="G29" s="18" t="n">
-        <v>3</v>
-      </c>
-      <c r="H29" s="18" t="inlineStr">
+      <c r="B29" s="17" t="n"/>
+      <c r="C29" s="17" t="n"/>
+      <c r="D29" s="17" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E29" s="17" t="n"/>
+      <c r="F29" s="17" t="n"/>
+      <c r="G29" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="H29" s="19" t="inlineStr">
         <is>
           <t>NCC-FP007-00</t>
         </is>
       </c>
-      <c r="I29" s="18" t="inlineStr">
+      <c r="I29" s="19" t="inlineStr">
         <is>
           <t>Coil Glue Bond (NCC-FP007.SLDPRT)</t>
         </is>
       </c>
-      <c r="J29" s="18" t="inlineStr">
+      <c r="J29" s="19" t="inlineStr">
         <is>
           <t>Sinlge 2216 bond for 1in coil.</t>
         </is>
       </c>
-      <c r="K29" s="18" t="inlineStr"/>
-      <c r="L29" s="18" t="n">
-        <v>3</v>
-      </c>
-      <c r="M29" s="18" t="n">
-        <v>3</v>
-      </c>
-      <c r="N29" s="18" t="inlineStr"/>
-      <c r="O29" s="18" t="inlineStr"/>
+      <c r="K29" s="19" t="inlineStr"/>
+      <c r="L29" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="M29" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="N29" s="19" t="inlineStr"/>
+      <c r="O29" s="19" t="inlineStr"/>
     </row>
     <row r="30" outlineLevel="3">
-      <c r="B30" s="16" t="n"/>
-      <c r="C30" s="16" t="n"/>
-      <c r="D30" s="16" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="E30" s="16" t="n"/>
-      <c r="F30" s="16" t="n"/>
-      <c r="G30" s="18" t="n">
-        <v>3</v>
-      </c>
-      <c r="H30" s="18" t="inlineStr">
+      <c r="B30" s="17" t="n"/>
+      <c r="C30" s="17" t="n"/>
+      <c r="D30" s="17" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E30" s="17" t="n"/>
+      <c r="F30" s="17" t="n"/>
+      <c r="G30" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="H30" s="19" t="inlineStr">
         <is>
           <t>NCC-FP004-B</t>
         </is>
       </c>
-      <c r="I30" s="18" t="inlineStr">
+      <c r="I30" s="19" t="inlineStr">
         <is>
           <t>1in Injector Radial Cell (NCC-FP004.SLDPRT)</t>
         </is>
       </c>
-      <c r="J30" s="18" t="inlineStr">
+      <c r="J30" s="19" t="inlineStr">
         <is>
           <t>Radial Cell of Injector 3DOF or 5DOF Coil Mount</t>
         </is>
       </c>
-      <c r="K30" s="18" t="inlineStr"/>
-      <c r="L30" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="M30" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="N30" s="18" t="inlineStr">
+      <c r="K30" s="19" t="inlineStr"/>
+      <c r="L30" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="M30" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="N30" s="19" t="inlineStr">
         <is>
           <t>Tritanium-36 Plate</t>
         </is>
       </c>
-      <c r="O30" s="18" t="inlineStr">
+      <c r="O30" s="19" t="inlineStr">
         <is>
           <t>0.064</t>
         </is>
       </c>
     </row>
     <row r="31" outlineLevel="3">
-      <c r="B31" s="16" t="n"/>
-      <c r="C31" s="16" t="n"/>
-      <c r="D31" s="16" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="E31" s="16" t="n"/>
-      <c r="F31" s="16" t="n"/>
-      <c r="G31" s="18" t="n">
-        <v>3</v>
-      </c>
-      <c r="H31" s="18" t="inlineStr">
+      <c r="B31" s="17" t="n"/>
+      <c r="C31" s="17" t="n"/>
+      <c r="D31" s="17" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E31" s="17" t="n"/>
+      <c r="F31" s="17" t="n"/>
+      <c r="G31" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="H31" s="19" t="inlineStr">
         <is>
           <t>92423A491_High-Strength Duranium Socket Head Screw_WRP</t>
         </is>
       </c>
-      <c r="I31" s="18" t="inlineStr">
+      <c r="I31" s="19" t="inlineStr">
         <is>
           <t>High-Strength Duranium Socket Head Screw (92423A491_High-Strength Duranium Socket Head Screw_WRP.SLDPRT)</t>
         </is>
       </c>
-      <c r="J31" s="18" t="inlineStr">
+      <c r="J31" s="19" t="inlineStr">
         <is>
           <t>High-Strength Duranium Socket Head Screw</t>
         </is>
       </c>
-      <c r="K31" s="18" t="inlineStr"/>
-      <c r="L31" s="18" t="n">
-        <v>3</v>
-      </c>
-      <c r="M31" s="18" t="n">
-        <v>3</v>
-      </c>
-      <c r="N31" s="18" t="inlineStr">
+      <c r="K31" s="19" t="inlineStr"/>
+      <c r="L31" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="M31" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="N31" s="19" t="inlineStr">
         <is>
           <t>Duranium A286 Alloy</t>
         </is>
       </c>
-      <c r="O31" s="18" t="inlineStr"/>
+      <c r="O31" s="19" t="inlineStr"/>
     </row>
     <row r="32" outlineLevel="3">
-      <c r="B32" s="16" t="n"/>
-      <c r="C32" s="16" t="n"/>
-      <c r="D32" s="16" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="E32" s="16" t="n"/>
-      <c r="F32" s="16" t="n"/>
-      <c r="G32" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="H32" s="17" t="inlineStr">
+      <c r="B32" s="17" t="n"/>
+      <c r="C32" s="17" t="n"/>
+      <c r="D32" s="17" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E32" s="17" t="n"/>
+      <c r="F32" s="17" t="n"/>
+      <c r="G32" s="18" t="n">
+        <v>3</v>
+      </c>
+      <c r="H32" s="18" t="inlineStr">
         <is>
           <t>AK000007S_WRP</t>
         </is>
       </c>
-      <c r="I32" s="17" t="inlineStr">
+      <c r="I32" s="18" t="inlineStr">
         <is>
           <t>AK000007S WRP (AK000007S_WRP.SLDASM)</t>
         </is>
       </c>
-      <c r="J32" s="17" t="inlineStr"/>
-      <c r="K32" s="17" t="inlineStr"/>
-      <c r="L32" s="17" t="n">
+      <c r="J32" s="18" t="inlineStr"/>
+      <c r="K32" s="18" t="inlineStr"/>
+      <c r="L32" s="18" t="n">
         <v>6</v>
       </c>
-      <c r="M32" s="17" t="n">
+      <c r="M32" s="18" t="n">
         <v>6</v>
       </c>
-      <c r="N32" s="17" t="inlineStr"/>
-      <c r="O32" s="17" t="inlineStr"/>
+      <c r="N32" s="18" t="inlineStr"/>
+      <c r="O32" s="18" t="inlineStr"/>
     </row>
     <row r="33" outlineLevel="4">
-      <c r="B33" s="16" t="n"/>
-      <c r="C33" s="16" t="n"/>
-      <c r="D33" s="16" t="n"/>
-      <c r="E33" s="16" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="F33" s="16" t="n"/>
-      <c r="G33" s="18" t="n">
+      <c r="B33" s="17" t="n"/>
+      <c r="C33" s="17" t="n"/>
+      <c r="D33" s="17" t="n"/>
+      <c r="E33" s="17" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F33" s="17" t="n"/>
+      <c r="G33" s="19" t="n">
         <v>4</v>
       </c>
-      <c r="H33" s="18" t="inlineStr">
+      <c r="H33" s="19" t="inlineStr">
         <is>
           <t>AK020004 EPS Tap Rev A_WRP</t>
         </is>
       </c>
-      <c r="I33" s="18" t="inlineStr">
+      <c r="I33" s="19" t="inlineStr">
         <is>
           <t>AK020004 EPS Tap Rev A WRP (AK020004 EPS Tap Rev A_WRP.SLDPRT)</t>
         </is>
       </c>
-      <c r="J33" s="18" t="inlineStr"/>
-      <c r="K33" s="18" t="inlineStr"/>
-      <c r="L33" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="M33" s="18" t="n">
+      <c r="J33" s="19" t="inlineStr"/>
+      <c r="K33" s="19" t="inlineStr"/>
+      <c r="L33" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="M33" s="19" t="n">
         <v>6</v>
       </c>
-      <c r="N33" s="18" t="inlineStr"/>
-      <c r="O33" s="18" t="inlineStr"/>
+      <c r="N33" s="19" t="inlineStr"/>
+      <c r="O33" s="19" t="inlineStr"/>
     </row>
     <row r="34" outlineLevel="4">
-      <c r="B34" s="16" t="n"/>
-      <c r="C34" s="16" t="n"/>
-      <c r="D34" s="16" t="n"/>
-      <c r="E34" s="16" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="F34" s="16" t="n"/>
-      <c r="G34" s="18" t="n">
+      <c r="B34" s="17" t="n"/>
+      <c r="C34" s="17" t="n"/>
+      <c r="D34" s="17" t="n"/>
+      <c r="E34" s="17" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F34" s="17" t="n"/>
+      <c r="G34" s="19" t="n">
         <v>4</v>
       </c>
-      <c r="H34" s="18" t="inlineStr">
+      <c r="H34" s="19" t="inlineStr">
         <is>
           <t>HD301004 SBS 92196A108_Tritanium Socket Head Screw_WRP</t>
         </is>
       </c>
-      <c r="I34" s="18" t="inlineStr">
+      <c r="I34" s="19" t="inlineStr">
         <is>
           <t>Tritanium Socket Head Screw (HD301004 SBS 92196A108_Tritanium Socket Head Screw_WRP.SLDPRT)</t>
         </is>
       </c>
-      <c r="J34" s="18" t="inlineStr">
+      <c r="J34" s="19" t="inlineStr">
         <is>
           <t>Tritanium Socket Head Screw</t>
         </is>
       </c>
-      <c r="K34" s="18" t="inlineStr"/>
-      <c r="L34" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="M34" s="18" t="n">
+      <c r="K34" s="19" t="inlineStr"/>
+      <c r="L34" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="M34" s="19" t="n">
         <v>6</v>
       </c>
-      <c r="N34" s="18" t="inlineStr">
+      <c r="N34" s="19" t="inlineStr">
         <is>
           <t>Tritanium 18-8</t>
         </is>
       </c>
-      <c r="O34" s="18" t="inlineStr"/>
+      <c r="O34" s="19" t="inlineStr"/>
     </row>
     <row r="35" outlineLevel="4">
-      <c r="B35" s="16" t="n"/>
-      <c r="C35" s="16" t="n"/>
-      <c r="D35" s="16" t="n"/>
-      <c r="E35" s="16" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="F35" s="16" t="n"/>
-      <c r="G35" s="18" t="n">
+      <c r="B35" s="17" t="n"/>
+      <c r="C35" s="17" t="n"/>
+      <c r="D35" s="17" t="n"/>
+      <c r="E35" s="17" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F35" s="17" t="n"/>
+      <c r="G35" s="19" t="n">
         <v>4</v>
       </c>
-      <c r="H35" s="18" t="inlineStr">
+      <c r="H35" s="19" t="inlineStr">
         <is>
           <t>HD101004 EPS Tap Adjuster Rev B_WRP</t>
         </is>
       </c>
-      <c r="I35" s="18" t="inlineStr">
+      <c r="I35" s="19" t="inlineStr">
         <is>
           <t>HD101004 EPS Tap Adjuster Rev B WRP (HD101004 EPS Tap Adjuster Rev B_WRP.SLDPRT)</t>
         </is>
       </c>
-      <c r="J35" s="18" t="inlineStr"/>
-      <c r="K35" s="18" t="inlineStr"/>
-      <c r="L35" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="M35" s="18" t="n">
+      <c r="J35" s="19" t="inlineStr"/>
+      <c r="K35" s="19" t="inlineStr"/>
+      <c r="L35" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="M35" s="19" t="n">
         <v>6</v>
       </c>
-      <c r="N35" s="18" t="inlineStr"/>
-      <c r="O35" s="18" t="inlineStr"/>
+      <c r="N35" s="19" t="inlineStr"/>
+      <c r="O35" s="19" t="inlineStr"/>
     </row>
     <row r="36" outlineLevel="2">
-      <c r="B36" s="16" t="n"/>
-      <c r="C36" s="16" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="D36" s="16" t="n"/>
-      <c r="E36" s="16" t="n"/>
-      <c r="F36" s="16" t="n"/>
-      <c r="G36" s="18" t="n">
-        <v>2</v>
-      </c>
-      <c r="H36" s="18" t="inlineStr">
+      <c r="B36" s="17" t="n"/>
+      <c r="C36" s="17" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="D36" s="17" t="n"/>
+      <c r="E36" s="17" t="n"/>
+      <c r="F36" s="17" t="n"/>
+      <c r="G36" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="H36" s="19" t="inlineStr">
         <is>
           <t>FM2_WRP</t>
         </is>
       </c>
-      <c r="I36" s="18" t="inlineStr">
+      <c r="I36" s="19" t="inlineStr">
         <is>
           <t>WRP-NCC-2219 (FM2_WRP.SLDPRT)</t>
         </is>
       </c>
-      <c r="J36" s="18" t="inlineStr">
+      <c r="J36" s="19" t="inlineStr">
         <is>
           <t>FM2 FOR RCS</t>
         </is>
       </c>
-      <c r="K36" s="18" t="inlineStr"/>
-      <c r="L36" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="M36" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="N36" s="18" t="inlineStr"/>
-      <c r="O36" s="18" t="inlineStr"/>
+      <c r="K36" s="19" t="inlineStr"/>
+      <c r="L36" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="M36" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="N36" s="19" t="inlineStr"/>
+      <c r="O36" s="19" t="inlineStr"/>
     </row>
     <row r="37" outlineLevel="2">
-      <c r="B37" s="16" t="n"/>
-      <c r="C37" s="16" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="D37" s="16" t="n"/>
-      <c r="E37" s="16" t="n"/>
-      <c r="F37" s="16" t="n"/>
-      <c r="G37" s="18" t="n">
-        <v>2</v>
-      </c>
-      <c r="H37" s="18" t="inlineStr">
+      <c r="B37" s="17" t="n"/>
+      <c r="C37" s="17" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="D37" s="17" t="n"/>
+      <c r="E37" s="17" t="n"/>
+      <c r="F37" s="17" t="n"/>
+      <c r="G37" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="H37" s="19" t="inlineStr">
         <is>
           <t>NCC-FP060-00</t>
         </is>
       </c>
-      <c r="I37" s="18" t="inlineStr">
+      <c r="I37" s="19" t="inlineStr">
         <is>
           <t>Emitter - Coil9A (NCC-FP060.SLDPRT)</t>
         </is>
       </c>
-      <c r="J37" s="18" t="inlineStr">
+      <c r="J37" s="19" t="inlineStr">
         <is>
           <t>1k Coil9</t>
         </is>
       </c>
-      <c r="K37" s="18" t="inlineStr"/>
-      <c r="L37" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="M37" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="N37" s="18" t="inlineStr">
+      <c r="K37" s="19" t="inlineStr"/>
+      <c r="L37" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="M37" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="N37" s="19" t="inlineStr">
         <is>
           <t>Transparent Aluminum</t>
         </is>
       </c>
-      <c r="O37" s="18" t="inlineStr">
+      <c r="O37" s="19" t="inlineStr">
         <is>
           <t>0.01</t>
         </is>
       </c>
     </row>
     <row r="38" outlineLevel="1">
-      <c r="B38" s="16" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="C38" s="16" t="n"/>
-      <c r="D38" s="16" t="n"/>
-      <c r="E38" s="16" t="n"/>
-      <c r="F38" s="16" t="n"/>
-      <c r="G38" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="H38" s="17" t="inlineStr">
+      <c r="B38" s="17" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="C38" s="17" t="n"/>
+      <c r="D38" s="17" t="n"/>
+      <c r="E38" s="17" t="n"/>
+      <c r="F38" s="17" t="n"/>
+      <c r="G38" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="H38" s="18" t="inlineStr">
         <is>
           <t>NCC-FA019-00</t>
         </is>
       </c>
-      <c r="I38" s="17" t="inlineStr">
+      <c r="I38" s="18" t="inlineStr">
         <is>
           <t>Deflector Pinhole Blocker Assembly (NCC-FA019.SLDASM)</t>
         </is>
       </c>
-      <c r="J38" s="17" t="inlineStr">
+      <c r="J38" s="18" t="inlineStr">
         <is>
           <t>Fail into beam blocker for secondary pinhole in deflector stop</t>
         </is>
       </c>
-      <c r="K38" s="17" t="inlineStr"/>
-      <c r="L38" s="17" t="n">
-        <v>2</v>
-      </c>
-      <c r="M38" s="17" t="n">
-        <v>2</v>
-      </c>
-      <c r="N38" s="17" t="inlineStr"/>
-      <c r="O38" s="17" t="inlineStr"/>
+      <c r="K38" s="18" t="inlineStr"/>
+      <c r="L38" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="M38" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="N38" s="18" t="inlineStr"/>
+      <c r="O38" s="18" t="inlineStr"/>
     </row>
     <row r="39" outlineLevel="2">
-      <c r="B39" s="16" t="n"/>
-      <c r="C39" s="16" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="D39" s="16" t="n"/>
-      <c r="E39" s="16" t="n"/>
-      <c r="F39" s="16" t="n"/>
-      <c r="G39" s="18" t="n">
-        <v>2</v>
-      </c>
-      <c r="H39" s="18" t="inlineStr">
+      <c r="B39" s="17" t="n"/>
+      <c r="C39" s="17" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="D39" s="17" t="n"/>
+      <c r="E39" s="17" t="n"/>
+      <c r="F39" s="17" t="n"/>
+      <c r="G39" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="H39" s="19" t="inlineStr">
         <is>
           <t>deflectorActuatorFlag</t>
         </is>
       </c>
-      <c r="I39" s="18" t="inlineStr">
+      <c r="I39" s="19" t="inlineStr">
         <is>
           <t>deflectorActuatorFlag (deflectorActuatorFlag.SLDPRT)</t>
         </is>
       </c>
-      <c r="J39" s="18" t="inlineStr"/>
-      <c r="K39" s="18" t="inlineStr"/>
-      <c r="L39" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="M39" s="18" t="n">
-        <v>2</v>
-      </c>
-      <c r="N39" s="18" t="inlineStr"/>
-      <c r="O39" s="18" t="inlineStr"/>
+      <c r="J39" s="19" t="inlineStr"/>
+      <c r="K39" s="19" t="inlineStr"/>
+      <c r="L39" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="M39" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="N39" s="19" t="inlineStr"/>
+      <c r="O39" s="19" t="inlineStr"/>
     </row>
     <row r="40" outlineLevel="2">
-      <c r="B40" s="16" t="n"/>
-      <c r="C40" s="16" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="D40" s="16" t="n"/>
-      <c r="E40" s="16" t="n"/>
-      <c r="F40" s="16" t="n"/>
-      <c r="G40" s="18" t="n">
-        <v>2</v>
-      </c>
-      <c r="H40" s="18" t="inlineStr">
+      <c r="B40" s="17" t="n"/>
+      <c r="C40" s="17" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="D40" s="17" t="n"/>
+      <c r="E40" s="17" t="n"/>
+      <c r="F40" s="17" t="n"/>
+      <c r="G40" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="H40" s="19" t="inlineStr">
         <is>
           <t>92423A412_High-Strength Duranium Socket Head Screw_ENT</t>
         </is>
       </c>
-      <c r="I40" s="18" t="inlineStr">
+      <c r="I40" s="19" t="inlineStr">
         <is>
           <t>92423A412 High-Strength Duranium Socket Head Screw ENT (92423A412_High-Strength Duranium Socket Head Screw_ENT.SLDPRT)</t>
         </is>
       </c>
-      <c r="J40" s="18" t="inlineStr"/>
-      <c r="K40" s="18" t="inlineStr"/>
-      <c r="L40" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="M40" s="18" t="n">
-        <v>2</v>
-      </c>
-      <c r="N40" s="18" t="inlineStr">
+      <c r="J40" s="19" t="inlineStr"/>
+      <c r="K40" s="19" t="inlineStr"/>
+      <c r="L40" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="M40" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="N40" s="19" t="inlineStr">
         <is>
           <t>Duranium A286 Alloy</t>
         </is>
       </c>
-      <c r="O40" s="18" t="inlineStr">
+      <c r="O40" s="19" t="inlineStr">
         <is>
           <t>SW-Mass@.SLDPRT</t>
         </is>
       </c>
     </row>
     <row r="41" outlineLevel="2">
-      <c r="B41" s="16" t="n"/>
-      <c r="C41" s="16" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="D41" s="16" t="n"/>
-      <c r="E41" s="16" t="n"/>
-      <c r="F41" s="16" t="n"/>
-      <c r="G41" s="18" t="n">
-        <v>2</v>
-      </c>
-      <c r="H41" s="18" t="inlineStr">
+      <c r="B41" s="17" t="n"/>
+      <c r="C41" s="17" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="D41" s="17" t="n"/>
+      <c r="E41" s="17" t="n"/>
+      <c r="F41" s="17" t="n"/>
+      <c r="G41" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="H41" s="19" t="inlineStr">
         <is>
           <t>96246A074_Duranium Helical Insert_ENT</t>
         </is>
       </c>
-      <c r="I41" s="18" t="inlineStr">
+      <c r="I41" s="19" t="inlineStr">
         <is>
           <t>96246A074 Duranium Helical Insert ENT (96246A074_Duranium Helical Insert_ENT.SLDPRT)</t>
         </is>
       </c>
-      <c r="J41" s="18" t="inlineStr"/>
-      <c r="K41" s="18" t="inlineStr"/>
-      <c r="L41" s="18" t="n">
-        <v>2</v>
-      </c>
-      <c r="M41" s="18" t="n">
+      <c r="J41" s="19" t="inlineStr"/>
+      <c r="K41" s="19" t="inlineStr"/>
+      <c r="L41" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="M41" s="19" t="n">
         <v>4</v>
       </c>
-      <c r="N41" s="18" t="inlineStr">
+      <c r="N41" s="19" t="inlineStr">
         <is>
           <t>Nitronium 60 Duranium Alloy</t>
         </is>
       </c>
-      <c r="O41" s="18" t="inlineStr">
+      <c r="O41" s="19" t="inlineStr">
         <is>
           <t>SW-Mass@.SLDPRT</t>
         </is>
       </c>
     </row>
     <row r="42" outlineLevel="2">
-      <c r="B42" s="16" t="n"/>
-      <c r="C42" s="16" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="D42" s="16" t="n"/>
-      <c r="E42" s="16" t="n"/>
-      <c r="F42" s="16" t="n"/>
-      <c r="G42" s="18" t="n">
-        <v>2</v>
-      </c>
-      <c r="H42" s="18" t="inlineStr">
+      <c r="B42" s="17" t="n"/>
+      <c r="C42" s="17" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="D42" s="17" t="n"/>
+      <c r="E42" s="17" t="n"/>
+      <c r="F42" s="17" t="n"/>
+      <c r="G42" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="H42" s="19" t="inlineStr">
         <is>
           <t>a1439solenoid</t>
         </is>
       </c>
-      <c r="I42" s="18" t="inlineStr">
+      <c r="I42" s="19" t="inlineStr">
         <is>
           <t>Deflector Shutter (a1439solenoid.SLDPRT)</t>
         </is>
       </c>
-      <c r="J42" s="18" t="inlineStr">
+      <c r="J42" s="19" t="inlineStr">
         <is>
           <t>Modified COTS part a1320-1 shutter</t>
         </is>
       </c>
-      <c r="K42" s="18" t="inlineStr"/>
-      <c r="L42" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="M42" s="18" t="n">
-        <v>2</v>
-      </c>
-      <c r="N42" s="18" t="inlineStr"/>
-      <c r="O42" s="18" t="inlineStr">
+      <c r="K42" s="19" t="inlineStr"/>
+      <c r="L42" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="M42" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="N42" s="19" t="inlineStr"/>
+      <c r="O42" s="19" t="inlineStr">
         <is>
           <t>0.004179</t>
         </is>
       </c>
     </row>
     <row r="43" outlineLevel="2">
-      <c r="B43" s="16" t="n"/>
-      <c r="C43" s="16" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="D43" s="16" t="n"/>
-      <c r="E43" s="16" t="n"/>
-      <c r="F43" s="16" t="n"/>
-      <c r="G43" s="18" t="n">
-        <v>2</v>
-      </c>
-      <c r="H43" s="18" t="inlineStr">
+      <c r="B43" s="17" t="n"/>
+      <c r="C43" s="17" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="D43" s="17" t="n"/>
+      <c r="E43" s="17" t="n"/>
+      <c r="F43" s="17" t="n"/>
+      <c r="G43" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="H43" s="19" t="inlineStr">
         <is>
           <t>92423A461_High-Strength Duranium Socket Head Screw</t>
         </is>
       </c>
-      <c r="I43" s="18" t="inlineStr">
+      <c r="I43" s="19" t="inlineStr">
         <is>
           <t>92423A461 High-Strength Duranium Socket Head Screw (92423A461_High-Strength Duranium Socket Head Screw.SLDPRT)</t>
         </is>
       </c>
-      <c r="J43" s="18" t="inlineStr"/>
-      <c r="K43" s="18" t="inlineStr"/>
-      <c r="L43" s="18" t="n">
-        <v>3</v>
-      </c>
-      <c r="M43" s="18" t="n">
+      <c r="J43" s="19" t="inlineStr"/>
+      <c r="K43" s="19" t="inlineStr"/>
+      <c r="L43" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="M43" s="19" t="n">
         <v>6</v>
       </c>
-      <c r="N43" s="18" t="inlineStr">
+      <c r="N43" s="19" t="inlineStr">
         <is>
           <t>Duranium A286 Alloy</t>
         </is>
       </c>
-      <c r="O43" s="18" t="inlineStr"/>
+      <c r="O43" s="19" t="inlineStr"/>
     </row>
     <row r="44" outlineLevel="2">
-      <c r="B44" s="16" t="n"/>
-      <c r="C44" s="16" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="D44" s="16" t="n"/>
-      <c r="E44" s="16" t="n"/>
-      <c r="F44" s="16" t="n"/>
-      <c r="G44" s="18" t="n">
-        <v>2</v>
-      </c>
-      <c r="H44" s="18" t="inlineStr">
+      <c r="B44" s="17" t="n"/>
+      <c r="C44" s="17" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="D44" s="17" t="n"/>
+      <c r="E44" s="17" t="n"/>
+      <c r="F44" s="17" t="n"/>
+      <c r="G44" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="H44" s="19" t="inlineStr">
         <is>
           <t>NCC-FP040-00</t>
         </is>
       </c>
-      <c r="I44" s="18" t="inlineStr">
+      <c r="I44" s="19" t="inlineStr">
         <is>
           <t>EPS Bracket (NCC-FP040.SLDPRT)</t>
         </is>
       </c>
-      <c r="J44" s="18" t="inlineStr">
+      <c r="J44" s="19" t="inlineStr">
         <is>
           <t>Bracket for a1439 solenoid</t>
         </is>
       </c>
-      <c r="K44" s="18" t="inlineStr"/>
-      <c r="L44" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="M44" s="18" t="n">
-        <v>2</v>
-      </c>
-      <c r="N44" s="18" t="inlineStr">
+      <c r="K44" s="19" t="inlineStr"/>
+      <c r="L44" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="M44" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="N44" s="19" t="inlineStr">
         <is>
           <t>Tritanium-36 Plate</t>
         </is>
       </c>
-      <c r="O44" s="18" t="inlineStr"/>
+      <c r="O44" s="19" t="inlineStr"/>
     </row>
     <row r="45" outlineLevel="2">
-      <c r="B45" s="16" t="n"/>
-      <c r="C45" s="16" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="D45" s="16" t="n"/>
-      <c r="E45" s="16" t="n"/>
-      <c r="F45" s="16" t="n"/>
-      <c r="G45" s="18" t="n">
-        <v>2</v>
-      </c>
-      <c r="H45" s="18" t="inlineStr">
+      <c r="B45" s="17" t="n"/>
+      <c r="C45" s="17" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="D45" s="17" t="n"/>
+      <c r="E45" s="17" t="n"/>
+      <c r="F45" s="17" t="n"/>
+      <c r="G45" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="H45" s="19" t="inlineStr">
         <is>
           <t>92423A451_High-Strength Duranium Socket Head Screw_ENT</t>
         </is>
       </c>
-      <c r="I45" s="18" t="inlineStr">
+      <c r="I45" s="19" t="inlineStr">
         <is>
           <t>92423A451 High-Strength Duranium Socket Head Screw ENT (92423A451_High-Strength Duranium Socket Head Screw_ENT.SLDPRT)</t>
         </is>
       </c>
-      <c r="J45" s="18" t="inlineStr"/>
-      <c r="K45" s="18" t="inlineStr"/>
-      <c r="L45" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="M45" s="18" t="n">
-        <v>2</v>
-      </c>
-      <c r="N45" s="18" t="inlineStr">
+      <c r="J45" s="19" t="inlineStr"/>
+      <c r="K45" s="19" t="inlineStr"/>
+      <c r="L45" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="M45" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="N45" s="19" t="inlineStr">
         <is>
           <t>Duranium A286 Alloy</t>
         </is>
       </c>
-      <c r="O45" s="18" t="inlineStr">
+      <c r="O45" s="19" t="inlineStr">
         <is>
           <t>SW-Mass@.SLDPRT</t>
         </is>
       </c>
     </row>
     <row r="46" outlineLevel="2">
-      <c r="B46" s="16" t="n"/>
-      <c r="C46" s="16" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="D46" s="16" t="n"/>
-      <c r="E46" s="16" t="n"/>
-      <c r="F46" s="16" t="n"/>
-      <c r="G46" s="18" t="n">
-        <v>2</v>
-      </c>
-      <c r="H46" s="18" t="inlineStr">
+      <c r="B46" s="17" t="n"/>
+      <c r="C46" s="17" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="D46" s="17" t="n"/>
+      <c r="E46" s="17" t="n"/>
+      <c r="F46" s="17" t="n"/>
+      <c r="G46" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="H46" s="19" t="inlineStr">
         <is>
           <t>epsIsolator</t>
         </is>
       </c>
-      <c r="I46" s="18" t="inlineStr">
+      <c r="I46" s="19" t="inlineStr">
         <is>
           <t>epsIsolator (epsIsolator.SLDPRT)</t>
         </is>
       </c>
-      <c r="J46" s="18" t="inlineStr"/>
-      <c r="K46" s="18" t="inlineStr"/>
-      <c r="L46" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="M46" s="18" t="n">
-        <v>2</v>
-      </c>
-      <c r="N46" s="18" t="inlineStr">
+      <c r="J46" s="19" t="inlineStr"/>
+      <c r="K46" s="19" t="inlineStr"/>
+      <c r="L46" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="M46" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="N46" s="19" t="inlineStr">
         <is>
           <t>Castrodinium Epoxy Composite</t>
         </is>
       </c>
-      <c r="O46" s="18" t="inlineStr">
+      <c r="O46" s="19" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
     </row>
     <row r="47" outlineLevel="2">
-      <c r="B47" s="16" t="n"/>
-      <c r="C47" s="16" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="D47" s="16" t="n"/>
-      <c r="E47" s="16" t="n"/>
-      <c r="F47" s="16" t="n"/>
-      <c r="G47" s="18" t="n">
-        <v>2</v>
-      </c>
-      <c r="H47" s="18" t="inlineStr">
+      <c r="B47" s="17" t="n"/>
+      <c r="C47" s="17" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="D47" s="17" t="n"/>
+      <c r="E47" s="17" t="n"/>
+      <c r="F47" s="17" t="n"/>
+      <c r="G47" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="H47" s="19" t="inlineStr">
         <is>
           <t>NCC-FP033-00</t>
         </is>
       </c>
-      <c r="I47" s="18" t="inlineStr">
+      <c r="I47" s="19" t="inlineStr">
         <is>
           <t>EPS Deflector Shutter (NCC-FP033.SLDPRT)</t>
         </is>
       </c>
-      <c r="J47" s="18" t="inlineStr">
+      <c r="J47" s="19" t="inlineStr">
         <is>
           <t>Modified COTS part a1320-1_shutter</t>
         </is>
       </c>
-      <c r="K47" s="18" t="inlineStr"/>
-      <c r="L47" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="M47" s="18" t="n">
-        <v>2</v>
-      </c>
-      <c r="N47" s="18" t="inlineStr"/>
-      <c r="O47" s="18" t="inlineStr"/>
+      <c r="K47" s="19" t="inlineStr"/>
+      <c r="L47" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="M47" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="N47" s="19" t="inlineStr"/>
+      <c r="O47" s="19" t="inlineStr"/>
     </row>
     <row r="48" outlineLevel="2">
-      <c r="B48" s="16" t="n"/>
-      <c r="C48" s="16" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="D48" s="16" t="n"/>
-      <c r="E48" s="16" t="n"/>
-      <c r="F48" s="16" t="n"/>
-      <c r="G48" s="18" t="n">
-        <v>2</v>
-      </c>
-      <c r="H48" s="18" t="inlineStr">
+      <c r="B48" s="17" t="n"/>
+      <c r="C48" s="17" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="D48" s="17" t="n"/>
+      <c r="E48" s="17" t="n"/>
+      <c r="F48" s="17" t="n"/>
+      <c r="G48" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="H48" s="19" t="inlineStr">
         <is>
           <t>92423A462_High-Strength Duranium Socket Head Screw_ENT</t>
         </is>
       </c>
-      <c r="I48" s="18" t="inlineStr">
+      <c r="I48" s="19" t="inlineStr">
         <is>
           <t>92423A462 High-Strength Duranium Socket Head Screw ENT (92423A462_High-Strength Duranium Socket Head Screw_ENT.SLDPRT)</t>
         </is>
       </c>
-      <c r="J48" s="18" t="inlineStr"/>
-      <c r="K48" s="18" t="inlineStr"/>
-      <c r="L48" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="M48" s="18" t="n">
-        <v>2</v>
-      </c>
-      <c r="N48" s="18" t="inlineStr">
+      <c r="J48" s="19" t="inlineStr"/>
+      <c r="K48" s="19" t="inlineStr"/>
+      <c r="L48" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="M48" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="N48" s="19" t="inlineStr">
         <is>
           <t>Duranium A286 Alloy</t>
         </is>
       </c>
-      <c r="O48" s="18" t="inlineStr">
+      <c r="O48" s="19" t="inlineStr">
         <is>
           <t>SW-Mass@.SLDPRT</t>
         </is>
       </c>
     </row>
     <row r="49" outlineLevel="1">
-      <c r="B49" s="16" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="C49" s="16" t="n"/>
-      <c r="D49" s="16" t="n"/>
-      <c r="E49" s="16" t="n"/>
-      <c r="F49" s="16" t="n"/>
-      <c r="G49" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="H49" s="17" t="inlineStr">
+      <c r="B49" s="17" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="C49" s="17" t="n"/>
+      <c r="D49" s="17" t="n"/>
+      <c r="E49" s="17" t="n"/>
+      <c r="F49" s="17" t="n"/>
+      <c r="G49" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="H49" s="18" t="inlineStr">
         <is>
           <t>NCC-FA014-00</t>
         </is>
       </c>
-      <c r="I49" s="17" t="inlineStr">
+      <c r="I49" s="18" t="inlineStr">
         <is>
           <t>1in Cell Mounted Plasma Injector 5-DOF Mount Port With Coil (NCC-FA014.SLDASM)</t>
         </is>
       </c>
-      <c r="J49" s="17" t="inlineStr">
+      <c r="J49" s="18" t="inlineStr">
         <is>
           <t>1in Cell Mounted Plasma Injector 5-DOF Mount Port With Coil</t>
         </is>
       </c>
-      <c r="K49" s="17" t="inlineStr"/>
-      <c r="L49" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="M49" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="N49" s="17" t="inlineStr"/>
-      <c r="O49" s="17" t="inlineStr"/>
+      <c r="K49" s="18" t="inlineStr"/>
+      <c r="L49" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="M49" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="N49" s="18" t="inlineStr"/>
+      <c r="O49" s="18" t="inlineStr"/>
     </row>
     <row r="50" outlineLevel="2">
-      <c r="B50" s="16" t="n"/>
-      <c r="C50" s="16" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="D50" s="16" t="n"/>
-      <c r="E50" s="16" t="n"/>
-      <c r="F50" s="16" t="n"/>
-      <c r="G50" s="17" t="n">
-        <v>2</v>
-      </c>
-      <c r="H50" s="17" t="inlineStr">
+      <c r="B50" s="17" t="n"/>
+      <c r="C50" s="17" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="D50" s="17" t="n"/>
+      <c r="E50" s="17" t="n"/>
+      <c r="F50" s="17" t="n"/>
+      <c r="G50" s="18" t="n">
+        <v>2</v>
+      </c>
+      <c r="H50" s="18" t="inlineStr">
         <is>
           <t>NCC-FA004-00</t>
         </is>
       </c>
-      <c r="I50" s="17" t="inlineStr">
+      <c r="I50" s="18" t="inlineStr">
         <is>
           <t>Injector Mount Assembly Port No Coil (NCC-FA004.SLDASM)</t>
         </is>
       </c>
-      <c r="J50" s="17" t="inlineStr">
+      <c r="J50" s="18" t="inlineStr">
         <is>
           <t>1in Cell Mounted Plasma Injector 5-DOF Mount Port No Coil</t>
         </is>
       </c>
-      <c r="K50" s="17" t="inlineStr"/>
-      <c r="L50" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="M50" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="N50" s="17" t="inlineStr"/>
-      <c r="O50" s="17" t="inlineStr"/>
+      <c r="K50" s="18" t="inlineStr"/>
+      <c r="L50" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="M50" s="18" t="n">
+        <v>1</v>
+      </c>
+      <c r="N50" s="18" t="inlineStr"/>
+      <c r="O50" s="18" t="inlineStr"/>
     </row>
     <row r="51" outlineLevel="3">
-      <c r="B51" s="16" t="n"/>
-      <c r="C51" s="16" t="n"/>
-      <c r="D51" s="16" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="E51" s="16" t="n"/>
-      <c r="F51" s="16" t="n"/>
-      <c r="G51" s="18" t="n">
-        <v>3</v>
-      </c>
-      <c r="H51" s="18" t="inlineStr">
+      <c r="B51" s="17" t="n"/>
+      <c r="C51" s="17" t="n"/>
+      <c r="D51" s="17" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E51" s="17" t="n"/>
+      <c r="F51" s="17" t="n"/>
+      <c r="G51" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="H51" s="19" t="inlineStr">
         <is>
           <t>NCC-FP005-02</t>
         </is>
       </c>
-      <c r="I51" s="18" t="inlineStr">
+      <c r="I51" s="19" t="inlineStr">
         <is>
           <t>Injector Base Port (NCC-FP005.SLDPRT)</t>
         </is>
       </c>
-      <c r="J51" s="18" t="inlineStr">
+      <c r="J51" s="19" t="inlineStr">
         <is>
           <t>INJECTOR BASE, 1" COIL</t>
         </is>
       </c>
-      <c r="K51" s="18" t="inlineStr"/>
-      <c r="L51" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="M51" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="N51" s="18" t="inlineStr"/>
-      <c r="O51" s="18" t="inlineStr"/>
+      <c r="K51" s="19" t="inlineStr"/>
+      <c r="L51" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="M51" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="N51" s="19" t="inlineStr"/>
+      <c r="O51" s="19" t="inlineStr"/>
     </row>
     <row r="52" outlineLevel="3">
-      <c r="B52" s="16" t="n"/>
-      <c r="C52" s="16" t="n"/>
-      <c r="D52" s="16" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="E52" s="16" t="n"/>
-      <c r="F52" s="16" t="n"/>
-      <c r="G52" s="18" t="n">
-        <v>3</v>
-      </c>
-      <c r="H52" s="18" t="inlineStr">
+      <c r="B52" s="17" t="n"/>
+      <c r="C52" s="17" t="n"/>
+      <c r="D52" s="17" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E52" s="17" t="n"/>
+      <c r="F52" s="17" t="n"/>
+      <c r="G52" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="H52" s="19" t="inlineStr">
         <is>
           <t>96246A088_Duranium Helical Insert_WRP</t>
         </is>
       </c>
-      <c r="I52" s="18" t="inlineStr">
+      <c r="I52" s="19" t="inlineStr">
         <is>
           <t>Duranium Helical Insert (96246A088_Duranium Helical Insert_WRP.SLDPRT)</t>
         </is>
       </c>
-      <c r="J52" s="18" t="inlineStr">
+      <c r="J52" s="19" t="inlineStr">
         <is>
           <t>Duranium Helical Insert</t>
         </is>
       </c>
-      <c r="K52" s="18" t="inlineStr"/>
-      <c r="L52" s="18" t="n">
-        <v>2</v>
-      </c>
-      <c r="M52" s="18" t="n">
-        <v>2</v>
-      </c>
-      <c r="N52" s="18" t="inlineStr">
+      <c r="K52" s="19" t="inlineStr"/>
+      <c r="L52" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="M52" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="N52" s="19" t="inlineStr">
         <is>
           <t>Nitronium 60 Duranium Alloy</t>
         </is>
       </c>
-      <c r="O52" s="18" t="inlineStr"/>
+      <c r="O52" s="19" t="inlineStr"/>
     </row>
     <row r="53" outlineLevel="3">
-      <c r="B53" s="16" t="n"/>
-      <c r="C53" s="16" t="n"/>
-      <c r="D53" s="16" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="E53" s="16" t="n"/>
-      <c r="F53" s="16" t="n"/>
-      <c r="G53" s="18" t="n">
-        <v>3</v>
-      </c>
-      <c r="H53" s="18" t="inlineStr">
+      <c r="B53" s="17" t="n"/>
+      <c r="C53" s="17" t="n"/>
+      <c r="D53" s="17" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E53" s="17" t="n"/>
+      <c r="F53" s="17" t="n"/>
+      <c r="G53" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="H53" s="19" t="inlineStr">
         <is>
           <t>90945A715_Tritanium Fleet Spec. Washer_WRP</t>
         </is>
       </c>
-      <c r="I53" s="18" t="inlineStr">
+      <c r="I53" s="19" t="inlineStr">
         <is>
           <t>Tritanium Fleet Spec. Washer (90945A715_Tritanium Fleet Spec. Washer_WRP.SLDPRT)</t>
         </is>
       </c>
-      <c r="J53" s="18" t="inlineStr">
+      <c r="J53" s="19" t="inlineStr">
         <is>
           <t>Tritanium Fleet Spec. Washer</t>
         </is>
       </c>
-      <c r="K53" s="18" t="inlineStr"/>
-      <c r="L53" s="18" t="n">
-        <v>2</v>
-      </c>
-      <c r="M53" s="18" t="n">
-        <v>2</v>
-      </c>
-      <c r="N53" s="18" t="inlineStr">
+      <c r="K53" s="19" t="inlineStr"/>
+      <c r="L53" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="M53" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="N53" s="19" t="inlineStr">
         <is>
           <t>Tritanium 18-8</t>
         </is>
       </c>
-      <c r="O53" s="18" t="inlineStr"/>
+      <c r="O53" s="19" t="inlineStr"/>
     </row>
     <row r="54" outlineLevel="3">
-      <c r="B54" s="16" t="n"/>
-      <c r="C54" s="16" t="n"/>
-      <c r="D54" s="16" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="E54" s="16" t="n"/>
-      <c r="F54" s="16" t="n"/>
-      <c r="G54" s="18" t="n">
-        <v>3</v>
-      </c>
-      <c r="H54" s="18" t="inlineStr">
+      <c r="B54" s="17" t="n"/>
+      <c r="C54" s="17" t="n"/>
+      <c r="D54" s="17" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E54" s="17" t="n"/>
+      <c r="F54" s="17" t="n"/>
+      <c r="G54" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="H54" s="19" t="inlineStr">
         <is>
           <t>92423A458_High-Strength Duranium Socket Head Screw_WRP</t>
         </is>
       </c>
-      <c r="I54" s="18" t="inlineStr">
+      <c r="I54" s="19" t="inlineStr">
         <is>
           <t>High-Strength Duranium Socket Head Screw (92423A458_High-Strength Duranium Socket Head Screw_WRP.SLDPRT)</t>
         </is>
       </c>
-      <c r="J54" s="18" t="inlineStr">
+      <c r="J54" s="19" t="inlineStr">
         <is>
           <t>High-Strength Duranium Socket Head Screw</t>
         </is>
       </c>
-      <c r="K54" s="18" t="inlineStr"/>
-      <c r="L54" s="18" t="n">
-        <v>2</v>
-      </c>
-      <c r="M54" s="18" t="n">
-        <v>2</v>
-      </c>
-      <c r="N54" s="18" t="inlineStr">
+      <c r="K54" s="19" t="inlineStr"/>
+      <c r="L54" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="M54" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="N54" s="19" t="inlineStr">
         <is>
           <t>Duranium A286 Alloy</t>
         </is>
       </c>
-      <c r="O54" s="18" t="inlineStr"/>
+      <c r="O54" s="19" t="inlineStr"/>
     </row>
     <row r="55" outlineLevel="3">
-      <c r="B55" s="16" t="n"/>
-      <c r="C55" s="16" t="n"/>
-      <c r="D55" s="16" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="E55" s="16" t="n"/>
-      <c r="F55" s="16" t="n"/>
-      <c r="G55" s="18" t="n">
-        <v>3</v>
-      </c>
-      <c r="H55" s="18" t="inlineStr">
+      <c r="B55" s="17" t="n"/>
+      <c r="C55" s="17" t="n"/>
+      <c r="D55" s="17" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E55" s="17" t="n"/>
+      <c r="F55" s="17" t="n"/>
+      <c r="G55" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="H55" s="19" t="inlineStr">
         <is>
           <t>Custom Injector Shim_WRP</t>
         </is>
       </c>
-      <c r="I55" s="18" t="inlineStr">
+      <c r="I55" s="19" t="inlineStr">
         <is>
           <t>Custom Injector Shim WRP (Custom Injector Shim_WRP.SLDPRT)</t>
         </is>
       </c>
-      <c r="J55" s="18" t="inlineStr"/>
-      <c r="K55" s="18" t="inlineStr"/>
-      <c r="L55" s="18" t="n">
-        <v>3</v>
-      </c>
-      <c r="M55" s="18" t="n">
-        <v>3</v>
-      </c>
-      <c r="N55" s="18" t="inlineStr"/>
-      <c r="O55" s="18" t="inlineStr"/>
+      <c r="J55" s="19" t="inlineStr"/>
+      <c r="K55" s="19" t="inlineStr"/>
+      <c r="L55" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="M55" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="N55" s="19" t="inlineStr"/>
+      <c r="O55" s="19" t="inlineStr"/>
     </row>
     <row r="56" outlineLevel="3">
-      <c r="B56" s="16" t="n"/>
-      <c r="C56" s="16" t="n"/>
-      <c r="D56" s="16" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="E56" s="16" t="n"/>
-      <c r="F56" s="16" t="n"/>
-      <c r="G56" s="18" t="n">
-        <v>3</v>
-      </c>
-      <c r="H56" s="18" t="inlineStr">
+      <c r="B56" s="17" t="n"/>
+      <c r="C56" s="17" t="n"/>
+      <c r="D56" s="17" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E56" s="17" t="n"/>
+      <c r="F56" s="17" t="n"/>
+      <c r="G56" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="H56" s="19" t="inlineStr">
         <is>
           <t>NCC-FP006-02</t>
         </is>
       </c>
-      <c r="I56" s="18" t="inlineStr">
+      <c r="I56" s="19" t="inlineStr">
         <is>
           <t>1in Injector Stage Port (NCC-FP006.SLDPRT)</t>
         </is>
       </c>
-      <c r="J56" s="18" t="inlineStr">
+      <c r="J56" s="19" t="inlineStr">
         <is>
           <t>INJECTOR STAGE, 1" COIL</t>
         </is>
       </c>
-      <c r="K56" s="18" t="inlineStr"/>
-      <c r="L56" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="M56" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="N56" s="18" t="inlineStr"/>
-      <c r="O56" s="18" t="inlineStr"/>
+      <c r="K56" s="19" t="inlineStr"/>
+      <c r="L56" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="M56" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="N56" s="19" t="inlineStr"/>
+      <c r="O56" s="19" t="inlineStr"/>
     </row>
     <row r="57" outlineLevel="3">
-      <c r="B57" s="16" t="n"/>
-      <c r="C57" s="16" t="n"/>
-      <c r="D57" s="16" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="E57" s="16" t="n"/>
-      <c r="F57" s="16" t="n"/>
-      <c r="G57" s="18" t="n">
-        <v>3</v>
-      </c>
-      <c r="H57" s="18" t="inlineStr">
+      <c r="B57" s="17" t="n"/>
+      <c r="C57" s="17" t="n"/>
+      <c r="D57" s="17" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E57" s="17" t="n"/>
+      <c r="F57" s="17" t="n"/>
+      <c r="G57" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="H57" s="19" t="inlineStr">
         <is>
           <t>90945A725_Tritanium Fleet Spec. Washer_WRP</t>
         </is>
       </c>
-      <c r="I57" s="18" t="inlineStr">
+      <c r="I57" s="19" t="inlineStr">
         <is>
           <t>Tritanium Fleet Spec. Washer (90945A725_Tritanium Fleet Spec. Washer_WRP.SLDPRT)</t>
         </is>
       </c>
-      <c r="J57" s="18" t="inlineStr">
+      <c r="J57" s="19" t="inlineStr">
         <is>
           <t>Tritanium Fleet Spec. Washer</t>
         </is>
       </c>
-      <c r="K57" s="18" t="inlineStr"/>
-      <c r="L57" s="18" t="n">
-        <v>3</v>
-      </c>
-      <c r="M57" s="18" t="n">
-        <v>3</v>
-      </c>
-      <c r="N57" s="18" t="inlineStr">
+      <c r="K57" s="19" t="inlineStr"/>
+      <c r="L57" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="M57" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="N57" s="19" t="inlineStr">
         <is>
           <t>Tritanium 18-8</t>
         </is>
       </c>
-      <c r="O57" s="18" t="inlineStr"/>
+      <c r="O57" s="19" t="inlineStr"/>
     </row>
     <row r="58" outlineLevel="3">
-      <c r="B58" s="16" t="n"/>
-      <c r="C58" s="16" t="n"/>
-      <c r="D58" s="16" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="E58" s="16" t="n"/>
-      <c r="F58" s="16" t="n"/>
-      <c r="G58" s="18" t="n">
-        <v>3</v>
-      </c>
-      <c r="H58" s="18" t="inlineStr">
+      <c r="B58" s="17" t="n"/>
+      <c r="C58" s="17" t="n"/>
+      <c r="D58" s="17" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E58" s="17" t="n"/>
+      <c r="F58" s="17" t="n"/>
+      <c r="G58" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="H58" s="19" t="inlineStr">
         <is>
           <t>96246A046_Duranium Helical Insert_WRP</t>
         </is>
       </c>
-      <c r="I58" s="18" t="inlineStr">
+      <c r="I58" s="19" t="inlineStr">
         <is>
           <t>Duranium Helical Insert (96246A046_Duranium Helical Insert_WRP.SLDPRT)</t>
         </is>
       </c>
-      <c r="J58" s="18" t="inlineStr">
+      <c r="J58" s="19" t="inlineStr">
         <is>
           <t>Duranium Helical Insert</t>
         </is>
       </c>
-      <c r="K58" s="18" t="inlineStr"/>
-      <c r="L58" s="18" t="n">
+      <c r="K58" s="19" t="inlineStr"/>
+      <c r="L58" s="19" t="n">
         <v>7</v>
       </c>
-      <c r="M58" s="18" t="n">
+      <c r="M58" s="19" t="n">
         <v>7</v>
       </c>
-      <c r="N58" s="18" t="inlineStr">
+      <c r="N58" s="19" t="inlineStr">
         <is>
           <t>Nitronium 60 Duranium Alloy</t>
         </is>
       </c>
-      <c r="O58" s="18" t="inlineStr"/>
+      <c r="O58" s="19" t="inlineStr"/>
     </row>
     <row r="59" outlineLevel="3">
-      <c r="B59" s="16" t="n"/>
-      <c r="C59" s="16" t="n"/>
-      <c r="D59" s="16" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="E59" s="16" t="n"/>
-      <c r="F59" s="16" t="n"/>
-      <c r="G59" s="18" t="n">
-        <v>3</v>
-      </c>
-      <c r="H59" s="18" t="inlineStr">
+      <c r="B59" s="17" t="n"/>
+      <c r="C59" s="17" t="n"/>
+      <c r="D59" s="17" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E59" s="17" t="n"/>
+      <c r="F59" s="17" t="n"/>
+      <c r="G59" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="H59" s="19" t="inlineStr">
         <is>
           <t>NCC-FP007-00</t>
         </is>
       </c>
-      <c r="I59" s="18" t="inlineStr">
+      <c r="I59" s="19" t="inlineStr">
         <is>
           <t>Coil Glue Bond (NCC-FP007.SLDPRT)</t>
         </is>
       </c>
-      <c r="J59" s="18" t="inlineStr">
+      <c r="J59" s="19" t="inlineStr">
         <is>
           <t>Sinlge 2216 bond for 1in coil.</t>
         </is>
       </c>
-      <c r="K59" s="18" t="inlineStr"/>
-      <c r="L59" s="18" t="n">
-        <v>3</v>
-      </c>
-      <c r="M59" s="18" t="n">
-        <v>3</v>
-      </c>
-      <c r="N59" s="18" t="inlineStr"/>
-      <c r="O59" s="18" t="inlineStr"/>
+      <c r="K59" s="19" t="inlineStr"/>
+      <c r="L59" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="M59" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="N59" s="19" t="inlineStr"/>
+      <c r="O59" s="19" t="inlineStr"/>
     </row>
     <row r="60" outlineLevel="3">
-      <c r="B60" s="16" t="n"/>
-      <c r="C60" s="16" t="n"/>
-      <c r="D60" s="16" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="E60" s="16" t="n"/>
-      <c r="F60" s="16" t="n"/>
-      <c r="G60" s="18" t="n">
-        <v>3</v>
-      </c>
-      <c r="H60" s="18" t="inlineStr">
+      <c r="B60" s="17" t="n"/>
+      <c r="C60" s="17" t="n"/>
+      <c r="D60" s="17" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E60" s="17" t="n"/>
+      <c r="F60" s="17" t="n"/>
+      <c r="G60" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="H60" s="19" t="inlineStr">
         <is>
           <t>NCC-FP004-B</t>
         </is>
       </c>
-      <c r="I60" s="18" t="inlineStr">
+      <c r="I60" s="19" t="inlineStr">
         <is>
           <t>1in Injector Radial Cell (NCC-FP004.SLDPRT)</t>
         </is>
       </c>
-      <c r="J60" s="18" t="inlineStr">
+      <c r="J60" s="19" t="inlineStr">
         <is>
           <t>Radial Cell of Injector 3DOF or 5DOF Coil Mount</t>
         </is>
       </c>
-      <c r="K60" s="18" t="inlineStr"/>
-      <c r="L60" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="M60" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="N60" s="18" t="inlineStr">
+      <c r="K60" s="19" t="inlineStr"/>
+      <c r="L60" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="M60" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="N60" s="19" t="inlineStr">
         <is>
           <t>Tritanium-36 Plate</t>
         </is>
       </c>
-      <c r="O60" s="18" t="inlineStr">
+      <c r="O60" s="19" t="inlineStr">
         <is>
           <t>0.064</t>
         </is>
       </c>
     </row>
     <row r="61" outlineLevel="3">
-      <c r="B61" s="16" t="n"/>
-      <c r="C61" s="16" t="n"/>
-      <c r="D61" s="16" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="E61" s="16" t="n"/>
-      <c r="F61" s="16" t="n"/>
-      <c r="G61" s="18" t="n">
-        <v>3</v>
-      </c>
-      <c r="H61" s="18" t="inlineStr">
+      <c r="B61" s="17" t="n"/>
+      <c r="C61" s="17" t="n"/>
+      <c r="D61" s="17" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E61" s="17" t="n"/>
+      <c r="F61" s="17" t="n"/>
+      <c r="G61" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="H61" s="19" t="inlineStr">
         <is>
           <t>92423A491_High-Strength Duranium Socket Head Screw_WRP</t>
         </is>
       </c>
-      <c r="I61" s="18" t="inlineStr">
+      <c r="I61" s="19" t="inlineStr">
         <is>
           <t>High-Strength Duranium Socket Head Screw (92423A491_High-Strength Duranium Socket Head Screw_WRP.SLDPRT)</t>
         </is>
       </c>
-      <c r="J61" s="18" t="inlineStr">
+      <c r="J61" s="19" t="inlineStr">
         <is>
           <t>High-Strength Duranium Socket Head Screw</t>
         </is>
       </c>
-      <c r="K61" s="18" t="inlineStr"/>
-      <c r="L61" s="18" t="n">
-        <v>3</v>
-      </c>
-      <c r="M61" s="18" t="n">
-        <v>3</v>
-      </c>
-      <c r="N61" s="18" t="inlineStr">
+      <c r="K61" s="19" t="inlineStr"/>
+      <c r="L61" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="M61" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="N61" s="19" t="inlineStr">
         <is>
           <t>Duranium A286 Alloy</t>
         </is>
       </c>
-      <c r="O61" s="18" t="inlineStr"/>
+      <c r="O61" s="19" t="inlineStr"/>
     </row>
     <row r="62" outlineLevel="3">
-      <c r="B62" s="16" t="n"/>
-      <c r="C62" s="16" t="n"/>
-      <c r="D62" s="16" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="E62" s="16" t="n"/>
-      <c r="F62" s="16" t="n"/>
-      <c r="G62" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="H62" s="17" t="inlineStr">
+      <c r="B62" s="17" t="n"/>
+      <c r="C62" s="17" t="n"/>
+      <c r="D62" s="17" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E62" s="17" t="n"/>
+      <c r="F62" s="17" t="n"/>
+      <c r="G62" s="18" t="n">
+        <v>3</v>
+      </c>
+      <c r="H62" s="18" t="inlineStr">
         <is>
           <t>AK000007S_WRP</t>
         </is>
       </c>
-      <c r="I62" s="17" t="inlineStr">
+      <c r="I62" s="18" t="inlineStr">
         <is>
           <t>AK000007S WRP (AK000007S_WRP.SLDASM)</t>
         </is>
       </c>
-      <c r="J62" s="17" t="inlineStr"/>
-      <c r="K62" s="17" t="inlineStr"/>
-      <c r="L62" s="17" t="n">
+      <c r="J62" s="18" t="inlineStr"/>
+      <c r="K62" s="18" t="inlineStr"/>
+      <c r="L62" s="18" t="n">
         <v>6</v>
       </c>
-      <c r="M62" s="17" t="n">
+      <c r="M62" s="18" t="n">
         <v>6</v>
       </c>
-      <c r="N62" s="17" t="inlineStr"/>
-      <c r="O62" s="17" t="inlineStr"/>
+      <c r="N62" s="18" t="inlineStr"/>
+      <c r="O62" s="18" t="inlineStr"/>
     </row>
     <row r="63" outlineLevel="4">
-      <c r="B63" s="16" t="n"/>
-      <c r="C63" s="16" t="n"/>
-      <c r="D63" s="16" t="n"/>
-      <c r="E63" s="16" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="F63" s="16" t="n"/>
-      <c r="G63" s="18" t="n">
+      <c r="B63" s="17" t="n"/>
+      <c r="C63" s="17" t="n"/>
+      <c r="D63" s="17" t="n"/>
+      <c r="E63" s="17" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F63" s="17" t="n"/>
+      <c r="G63" s="19" t="n">
         <v>4</v>
       </c>
-      <c r="H63" s="18" t="inlineStr">
+      <c r="H63" s="19" t="inlineStr">
         <is>
           <t>AK020004 EPS Tap Rev A_WRP</t>
         </is>
       </c>
-      <c r="I63" s="18" t="inlineStr">
+      <c r="I63" s="19" t="inlineStr">
         <is>
           <t>AK020004 EPS Tap Rev A WRP (AK020004 EPS Tap Rev A_WRP.SLDPRT)</t>
         </is>
       </c>
-      <c r="J63" s="18" t="inlineStr"/>
-      <c r="K63" s="18" t="inlineStr"/>
-      <c r="L63" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="M63" s="18" t="n">
+      <c r="J63" s="19" t="inlineStr"/>
+      <c r="K63" s="19" t="inlineStr"/>
+      <c r="L63" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="M63" s="19" t="n">
         <v>6</v>
       </c>
-      <c r="N63" s="18" t="inlineStr"/>
-      <c r="O63" s="18" t="inlineStr"/>
+      <c r="N63" s="19" t="inlineStr"/>
+      <c r="O63" s="19" t="inlineStr"/>
     </row>
     <row r="64" outlineLevel="4">
-      <c r="B64" s="16" t="n"/>
-      <c r="C64" s="16" t="n"/>
-      <c r="D64" s="16" t="n"/>
-      <c r="E64" s="16" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="F64" s="16" t="n"/>
-      <c r="G64" s="18" t="n">
+      <c r="B64" s="17" t="n"/>
+      <c r="C64" s="17" t="n"/>
+      <c r="D64" s="17" t="n"/>
+      <c r="E64" s="17" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F64" s="17" t="n"/>
+      <c r="G64" s="19" t="n">
         <v>4</v>
       </c>
-      <c r="H64" s="18" t="inlineStr">
+      <c r="H64" s="19" t="inlineStr">
         <is>
           <t>HD301004 SBS 92196A108_Tritanium Socket Head Screw_WRP</t>
         </is>
       </c>
-      <c r="I64" s="18" t="inlineStr">
+      <c r="I64" s="19" t="inlineStr">
         <is>
           <t>Tritanium Socket Head Screw (HD301004 SBS 92196A108_Tritanium Socket Head Screw_WRP.SLDPRT)</t>
         </is>
       </c>
-      <c r="J64" s="18" t="inlineStr">
+      <c r="J64" s="19" t="inlineStr">
         <is>
           <t>Tritanium Socket Head Screw</t>
         </is>
       </c>
-      <c r="K64" s="18" t="inlineStr"/>
-      <c r="L64" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="M64" s="18" t="n">
+      <c r="K64" s="19" t="inlineStr"/>
+      <c r="L64" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="M64" s="19" t="n">
         <v>6</v>
       </c>
-      <c r="N64" s="18" t="inlineStr">
+      <c r="N64" s="19" t="inlineStr">
         <is>
           <t>Tritanium 18-8</t>
         </is>
       </c>
-      <c r="O64" s="18" t="inlineStr"/>
+      <c r="O64" s="19" t="inlineStr"/>
     </row>
     <row r="65" outlineLevel="4">
-      <c r="B65" s="16" t="n"/>
-      <c r="C65" s="16" t="n"/>
-      <c r="D65" s="16" t="n"/>
-      <c r="E65" s="16" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="F65" s="16" t="n"/>
-      <c r="G65" s="18" t="n">
+      <c r="B65" s="17" t="n"/>
+      <c r="C65" s="17" t="n"/>
+      <c r="D65" s="17" t="n"/>
+      <c r="E65" s="17" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F65" s="17" t="n"/>
+      <c r="G65" s="19" t="n">
         <v>4</v>
       </c>
-      <c r="H65" s="18" t="inlineStr">
+      <c r="H65" s="19" t="inlineStr">
         <is>
           <t>HD101004 EPS Tap Adjuster Rev B_WRP</t>
         </is>
       </c>
-      <c r="I65" s="18" t="inlineStr">
+      <c r="I65" s="19" t="inlineStr">
         <is>
           <t>HD101004 EPS Tap Adjuster Rev B WRP (HD101004 EPS Tap Adjuster Rev B_WRP.SLDPRT)</t>
         </is>
       </c>
-      <c r="J65" s="18" t="inlineStr"/>
-      <c r="K65" s="18" t="inlineStr"/>
-      <c r="L65" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="M65" s="18" t="n">
+      <c r="J65" s="19" t="inlineStr"/>
+      <c r="K65" s="19" t="inlineStr"/>
+      <c r="L65" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="M65" s="19" t="n">
         <v>6</v>
       </c>
-      <c r="N65" s="18" t="inlineStr"/>
-      <c r="O65" s="18" t="inlineStr"/>
+      <c r="N65" s="19" t="inlineStr"/>
+      <c r="O65" s="19" t="inlineStr"/>
     </row>
     <row r="66" outlineLevel="2">
-      <c r="B66" s="16" t="n"/>
-      <c r="C66" s="16" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="D66" s="16" t="n"/>
-      <c r="E66" s="16" t="n"/>
-      <c r="F66" s="16" t="n"/>
-      <c r="G66" s="18" t="n">
-        <v>2</v>
-      </c>
-      <c r="H66" s="18" t="inlineStr">
+      <c r="B66" s="17" t="n"/>
+      <c r="C66" s="17" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="D66" s="17" t="n"/>
+      <c r="E66" s="17" t="n"/>
+      <c r="F66" s="17" t="n"/>
+      <c r="G66" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="H66" s="19" t="inlineStr">
         <is>
           <t>NCC-FP053-00</t>
         </is>
       </c>
-      <c r="I66" s="18" t="inlineStr">
+      <c r="I66" s="19" t="inlineStr">
         <is>
           <t>Emitter - Coil2 (NCC-FP053.SLDPRT)</t>
         </is>
       </c>
-      <c r="J66" s="18" t="inlineStr">
+      <c r="J66" s="19" t="inlineStr">
         <is>
           <t>Fore Coil2</t>
         </is>
       </c>
-      <c r="K66" s="18" t="inlineStr"/>
-      <c r="L66" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="M66" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="N66" s="18" t="inlineStr">
+      <c r="K66" s="19" t="inlineStr"/>
+      <c r="L66" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="M66" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="N66" s="19" t="inlineStr">
         <is>
           <t>Transparent Aluminum</t>
         </is>
       </c>
-      <c r="O66" s="18" t="inlineStr">
+      <c r="O66" s="19" t="inlineStr">
         <is>
           <t>0.01</t>
         </is>
@@ -2734,7 +2746,7 @@
     </row>
   </sheetData>
   <autoFilter ref="G17:O66"/>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="B10:G10"/>
     <mergeCell ref="B16:F16"/>
     <mergeCell ref="L16:M16"/>
@@ -2742,6 +2754,7 @@
     <mergeCell ref="B2:O5"/>
     <mergeCell ref="B12:G12"/>
     <mergeCell ref="B13:G13"/>
+    <mergeCell ref="B14:O14"/>
     <mergeCell ref="B7:G7"/>
     <mergeCell ref="B11:G11"/>
     <mergeCell ref="B6:G6"/>

--- a/examples/NCC-1701_pdmout_BOM.xlsx
+++ b/examples/NCC-1701_pdmout_BOM.xlsx
@@ -19,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -41,6 +41,10 @@
       <name val="Aptos Narrow"/>
       <b val="1"/>
       <sz val="14"/>
+    </font>
+    <font>
+      <name val="Aptos Narrow"/>
+      <sz val="10"/>
     </font>
     <font>
       <name val="Aptos Narrow"/>
@@ -174,7 +178,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -189,6 +193,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -198,11 +203,11 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -648,6 +653,13 @@
         </is>
       </c>
     </row>
+    <row r="8">
+      <c r="B8" s="11" t="inlineStr">
+        <is>
+          <t>Source: examples/NCC-1701_pdmout.csv</t>
+        </is>
+      </c>
+    </row>
     <row r="9">
       <c r="B9" s="10" t="inlineStr">
         <is>
@@ -684,130 +696,130 @@
       </c>
     </row>
     <row r="14">
-      <c r="B14" s="11" t="inlineStr">
-        <is>
-          <t>Source BOM: examples/NCC-1701_pdmout.csv · Config: bomgen.toml · bomgen: 0.1.0 · Python: 3.11.15 · openpyxl: 3.1.5 · Generated: 2026-07-20 05:46</t>
+      <c r="B14" s="12" t="inlineStr">
+        <is>
+          <t>Source BOM: examples/NCC-1701_pdmout.csv · Config: bomgen.toml · bomgen: 0.1.0 · Python: 3.11.15 · openpyxl: 3.1.5 · Generated: 2026-07-22 06:05</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="B16" s="12" t="inlineStr">
+      <c r="B16" s="13" t="inlineStr">
         <is>
           <t>Assembly Level</t>
         </is>
       </c>
-      <c r="C16" s="13" t="n"/>
-      <c r="D16" s="13" t="n"/>
-      <c r="E16" s="13" t="n"/>
-      <c r="F16" s="13" t="n"/>
-      <c r="G16" s="13" t="n"/>
-      <c r="H16" s="13" t="n"/>
-      <c r="I16" s="13" t="n"/>
-      <c r="J16" s="13" t="n"/>
-      <c r="K16" s="13" t="n"/>
-      <c r="L16" s="14" t="inlineStr">
+      <c r="C16" s="14" t="n"/>
+      <c r="D16" s="14" t="n"/>
+      <c r="E16" s="14" t="n"/>
+      <c r="F16" s="14" t="n"/>
+      <c r="G16" s="14" t="n"/>
+      <c r="H16" s="14" t="n"/>
+      <c r="I16" s="14" t="n"/>
+      <c r="J16" s="14" t="n"/>
+      <c r="K16" s="14" t="n"/>
+      <c r="L16" s="15" t="inlineStr">
         <is>
           <t>Quantity Required</t>
         </is>
       </c>
-      <c r="M16" s="13" t="n"/>
-      <c r="N16" s="13" t="n"/>
-      <c r="O16" s="13" t="n"/>
+      <c r="M16" s="14" t="n"/>
+      <c r="N16" s="14" t="n"/>
+      <c r="O16" s="14" t="n"/>
     </row>
     <row r="17">
-      <c r="B17" s="15" t="inlineStr">
+      <c r="B17" s="16" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="C17" s="15" t="inlineStr">
+      <c r="C17" s="16" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D17" s="15" t="inlineStr">
+      <c r="D17" s="16" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E17" s="15" t="inlineStr">
+      <c r="E17" s="16" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="F17" s="15" t="inlineStr">
+      <c r="F17" s="16" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="G17" s="14" t="inlineStr">
+      <c r="G17" s="15" t="inlineStr">
         <is>
           <t>Level</t>
         </is>
       </c>
-      <c r="H17" s="14" t="inlineStr">
+      <c r="H17" s="15" t="inlineStr">
         <is>
           <t>Abbreviated Part Number</t>
         </is>
       </c>
-      <c r="I17" s="14" t="inlineStr">
+      <c r="I17" s="15" t="inlineStr">
         <is>
           <t>Part Name</t>
         </is>
       </c>
-      <c r="J17" s="14" t="inlineStr">
+      <c r="J17" s="15" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
-      <c r="K17" s="14" t="inlineStr">
+      <c r="K17" s="15" t="inlineStr">
         <is>
           <t>COTS</t>
         </is>
       </c>
-      <c r="L17" s="14" t="inlineStr">
+      <c r="L17" s="15" t="inlineStr">
         <is>
           <t>Qty (Assembly)</t>
         </is>
       </c>
-      <c r="M17" s="14" t="inlineStr">
+      <c r="M17" s="15" t="inlineStr">
         <is>
           <t>Qty (Total)</t>
         </is>
       </c>
-      <c r="N17" s="14" t="inlineStr">
+      <c r="N17" s="15" t="inlineStr">
         <is>
           <t>Material</t>
         </is>
       </c>
-      <c r="O17" s="14" t="inlineStr">
+      <c r="O17" s="15" t="inlineStr">
         <is>
           <t>Mass</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="B18" s="16" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="C18" s="16" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="D18" s="16" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="E18" s="16" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="F18" s="16" t="inlineStr">
+      <c r="B18" s="17" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="C18" s="17" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="D18" s="17" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E18" s="17" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F18" s="17" t="inlineStr">
         <is>
           <t>X</t>
         </is>
@@ -841,1904 +853,1904 @@
       <c r="O18" s="10" t="inlineStr"/>
     </row>
     <row r="19" outlineLevel="1">
-      <c r="B19" s="17" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="C19" s="17" t="n"/>
-      <c r="D19" s="17" t="n"/>
-      <c r="E19" s="17" t="n"/>
-      <c r="F19" s="17" t="n"/>
-      <c r="G19" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="H19" s="18" t="inlineStr">
+      <c r="B19" s="18" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="C19" s="18" t="n"/>
+      <c r="D19" s="18" t="n"/>
+      <c r="E19" s="18" t="n"/>
+      <c r="F19" s="18" t="n"/>
+      <c r="G19" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="H19" s="19" t="inlineStr">
         <is>
           <t>NCC-FA014-00</t>
         </is>
       </c>
-      <c r="I19" s="18" t="inlineStr">
+      <c r="I19" s="19" t="inlineStr">
         <is>
           <t>1in Cell Mounted Plasma Injector 5-DOF Mount Port With Coil (NCC-FA014.SLDASM)</t>
         </is>
       </c>
-      <c r="J19" s="18" t="inlineStr">
+      <c r="J19" s="19" t="inlineStr">
         <is>
           <t>1in Cell Mounted Plasma Injector 5-DOF Mount Port With Coil</t>
         </is>
       </c>
-      <c r="K19" s="18" t="inlineStr"/>
-      <c r="L19" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="M19" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="N19" s="18" t="inlineStr"/>
-      <c r="O19" s="18" t="inlineStr"/>
+      <c r="K19" s="19" t="inlineStr"/>
+      <c r="L19" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="M19" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="N19" s="19" t="inlineStr"/>
+      <c r="O19" s="19" t="inlineStr"/>
     </row>
     <row r="20" outlineLevel="2">
-      <c r="B20" s="17" t="n"/>
-      <c r="C20" s="17" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="D20" s="17" t="n"/>
-      <c r="E20" s="17" t="n"/>
-      <c r="F20" s="17" t="n"/>
-      <c r="G20" s="18" t="n">
-        <v>2</v>
-      </c>
-      <c r="H20" s="18" t="inlineStr">
+      <c r="B20" s="18" t="n"/>
+      <c r="C20" s="18" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="D20" s="18" t="n"/>
+      <c r="E20" s="18" t="n"/>
+      <c r="F20" s="18" t="n"/>
+      <c r="G20" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="H20" s="19" t="inlineStr">
         <is>
           <t>NCC-FA004-00</t>
         </is>
       </c>
-      <c r="I20" s="18" t="inlineStr">
+      <c r="I20" s="19" t="inlineStr">
         <is>
           <t>Injector Mount Assembly Port No Coil (NCC-FA004.SLDASM)</t>
         </is>
       </c>
-      <c r="J20" s="18" t="inlineStr">
+      <c r="J20" s="19" t="inlineStr">
         <is>
           <t>1in Cell Mounted Plasma Injector 5-DOF Mount Port No Coil</t>
         </is>
       </c>
-      <c r="K20" s="18" t="inlineStr"/>
-      <c r="L20" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="M20" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="N20" s="18" t="inlineStr"/>
-      <c r="O20" s="18" t="inlineStr"/>
+      <c r="K20" s="19" t="inlineStr"/>
+      <c r="L20" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="M20" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="N20" s="19" t="inlineStr"/>
+      <c r="O20" s="19" t="inlineStr"/>
     </row>
     <row r="21" outlineLevel="3">
-      <c r="B21" s="17" t="n"/>
-      <c r="C21" s="17" t="n"/>
-      <c r="D21" s="17" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="E21" s="17" t="n"/>
-      <c r="F21" s="17" t="n"/>
-      <c r="G21" s="19" t="n">
-        <v>3</v>
-      </c>
-      <c r="H21" s="19" t="inlineStr">
+      <c r="B21" s="18" t="n"/>
+      <c r="C21" s="18" t="n"/>
+      <c r="D21" s="18" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E21" s="18" t="n"/>
+      <c r="F21" s="18" t="n"/>
+      <c r="G21" s="20" t="n">
+        <v>3</v>
+      </c>
+      <c r="H21" s="20" t="inlineStr">
         <is>
           <t>NCC-FP005-02</t>
         </is>
       </c>
-      <c r="I21" s="19" t="inlineStr">
+      <c r="I21" s="20" t="inlineStr">
         <is>
           <t>Injector Base Port (NCC-FP005.SLDPRT)</t>
         </is>
       </c>
-      <c r="J21" s="19" t="inlineStr">
+      <c r="J21" s="20" t="inlineStr">
         <is>
           <t>INJECTOR BASE, 1" COIL</t>
         </is>
       </c>
-      <c r="K21" s="19" t="inlineStr"/>
-      <c r="L21" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="M21" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="N21" s="19" t="inlineStr"/>
-      <c r="O21" s="19" t="inlineStr"/>
+      <c r="K21" s="20" t="inlineStr"/>
+      <c r="L21" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="M21" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="N21" s="20" t="inlineStr"/>
+      <c r="O21" s="20" t="inlineStr"/>
     </row>
     <row r="22" outlineLevel="3">
-      <c r="B22" s="17" t="n"/>
-      <c r="C22" s="17" t="n"/>
-      <c r="D22" s="17" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="E22" s="17" t="n"/>
-      <c r="F22" s="17" t="n"/>
-      <c r="G22" s="19" t="n">
-        <v>3</v>
-      </c>
-      <c r="H22" s="19" t="inlineStr">
+      <c r="B22" s="18" t="n"/>
+      <c r="C22" s="18" t="n"/>
+      <c r="D22" s="18" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E22" s="18" t="n"/>
+      <c r="F22" s="18" t="n"/>
+      <c r="G22" s="20" t="n">
+        <v>3</v>
+      </c>
+      <c r="H22" s="20" t="inlineStr">
         <is>
           <t>96246A088_Duranium Helical Insert_WRP</t>
         </is>
       </c>
-      <c r="I22" s="19" t="inlineStr">
+      <c r="I22" s="20" t="inlineStr">
         <is>
           <t>Duranium Helical Insert (96246A088_Duranium Helical Insert_WRP.SLDPRT)</t>
         </is>
       </c>
-      <c r="J22" s="19" t="inlineStr">
+      <c r="J22" s="20" t="inlineStr">
         <is>
           <t>Duranium Helical Insert</t>
         </is>
       </c>
-      <c r="K22" s="19" t="inlineStr"/>
-      <c r="L22" s="19" t="n">
-        <v>2</v>
-      </c>
-      <c r="M22" s="19" t="n">
-        <v>2</v>
-      </c>
-      <c r="N22" s="19" t="inlineStr">
+      <c r="K22" s="20" t="inlineStr"/>
+      <c r="L22" s="20" t="n">
+        <v>2</v>
+      </c>
+      <c r="M22" s="20" t="n">
+        <v>2</v>
+      </c>
+      <c r="N22" s="20" t="inlineStr">
         <is>
           <t>Nitronium 60 Duranium Alloy</t>
         </is>
       </c>
-      <c r="O22" s="19" t="inlineStr"/>
+      <c r="O22" s="20" t="inlineStr"/>
     </row>
     <row r="23" outlineLevel="3">
-      <c r="B23" s="17" t="n"/>
-      <c r="C23" s="17" t="n"/>
-      <c r="D23" s="17" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="E23" s="17" t="n"/>
-      <c r="F23" s="17" t="n"/>
-      <c r="G23" s="19" t="n">
-        <v>3</v>
-      </c>
-      <c r="H23" s="19" t="inlineStr">
+      <c r="B23" s="18" t="n"/>
+      <c r="C23" s="18" t="n"/>
+      <c r="D23" s="18" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E23" s="18" t="n"/>
+      <c r="F23" s="18" t="n"/>
+      <c r="G23" s="20" t="n">
+        <v>3</v>
+      </c>
+      <c r="H23" s="20" t="inlineStr">
         <is>
           <t>90945A715_Tritanium Fleet Spec. Washer_WRP</t>
         </is>
       </c>
-      <c r="I23" s="19" t="inlineStr">
+      <c r="I23" s="20" t="inlineStr">
         <is>
           <t>Tritanium Fleet Spec. Washer (90945A715_Tritanium Fleet Spec. Washer_WRP.SLDPRT)</t>
         </is>
       </c>
-      <c r="J23" s="19" t="inlineStr">
+      <c r="J23" s="20" t="inlineStr">
         <is>
           <t>Tritanium Fleet Spec. Washer</t>
         </is>
       </c>
-      <c r="K23" s="19" t="inlineStr"/>
-      <c r="L23" s="19" t="n">
-        <v>2</v>
-      </c>
-      <c r="M23" s="19" t="n">
-        <v>2</v>
-      </c>
-      <c r="N23" s="19" t="inlineStr">
+      <c r="K23" s="20" t="inlineStr"/>
+      <c r="L23" s="20" t="n">
+        <v>2</v>
+      </c>
+      <c r="M23" s="20" t="n">
+        <v>2</v>
+      </c>
+      <c r="N23" s="20" t="inlineStr">
         <is>
           <t>Tritanium 18-8</t>
         </is>
       </c>
-      <c r="O23" s="19" t="inlineStr"/>
+      <c r="O23" s="20" t="inlineStr"/>
     </row>
     <row r="24" outlineLevel="3">
-      <c r="B24" s="17" t="n"/>
-      <c r="C24" s="17" t="n"/>
-      <c r="D24" s="17" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="E24" s="17" t="n"/>
-      <c r="F24" s="17" t="n"/>
-      <c r="G24" s="19" t="n">
-        <v>3</v>
-      </c>
-      <c r="H24" s="19" t="inlineStr">
+      <c r="B24" s="18" t="n"/>
+      <c r="C24" s="18" t="n"/>
+      <c r="D24" s="18" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E24" s="18" t="n"/>
+      <c r="F24" s="18" t="n"/>
+      <c r="G24" s="20" t="n">
+        <v>3</v>
+      </c>
+      <c r="H24" s="20" t="inlineStr">
         <is>
           <t>92423A458_High-Strength Duranium Socket Head Screw_WRP</t>
         </is>
       </c>
-      <c r="I24" s="19" t="inlineStr">
+      <c r="I24" s="20" t="inlineStr">
         <is>
           <t>High-Strength Duranium Socket Head Screw (92423A458_High-Strength Duranium Socket Head Screw_WRP.SLDPRT)</t>
         </is>
       </c>
-      <c r="J24" s="19" t="inlineStr">
+      <c r="J24" s="20" t="inlineStr">
         <is>
           <t>High-Strength Duranium Socket Head Screw</t>
         </is>
       </c>
-      <c r="K24" s="19" t="inlineStr"/>
-      <c r="L24" s="19" t="n">
-        <v>2</v>
-      </c>
-      <c r="M24" s="19" t="n">
-        <v>2</v>
-      </c>
-      <c r="N24" s="19" t="inlineStr">
+      <c r="K24" s="20" t="inlineStr"/>
+      <c r="L24" s="20" t="n">
+        <v>2</v>
+      </c>
+      <c r="M24" s="20" t="n">
+        <v>2</v>
+      </c>
+      <c r="N24" s="20" t="inlineStr">
         <is>
           <t>Duranium A286 Alloy</t>
         </is>
       </c>
-      <c r="O24" s="19" t="inlineStr"/>
+      <c r="O24" s="20" t="inlineStr"/>
     </row>
     <row r="25" outlineLevel="3">
-      <c r="B25" s="17" t="n"/>
-      <c r="C25" s="17" t="n"/>
-      <c r="D25" s="17" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="E25" s="17" t="n"/>
-      <c r="F25" s="17" t="n"/>
-      <c r="G25" s="19" t="n">
-        <v>3</v>
-      </c>
-      <c r="H25" s="19" t="inlineStr">
+      <c r="B25" s="18" t="n"/>
+      <c r="C25" s="18" t="n"/>
+      <c r="D25" s="18" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E25" s="18" t="n"/>
+      <c r="F25" s="18" t="n"/>
+      <c r="G25" s="20" t="n">
+        <v>3</v>
+      </c>
+      <c r="H25" s="20" t="inlineStr">
         <is>
           <t>Custom Injector Shim_WRP</t>
         </is>
       </c>
-      <c r="I25" s="19" t="inlineStr">
+      <c r="I25" s="20" t="inlineStr">
         <is>
           <t>Custom Injector Shim WRP (Custom Injector Shim_WRP.SLDPRT)</t>
         </is>
       </c>
-      <c r="J25" s="19" t="inlineStr"/>
-      <c r="K25" s="19" t="inlineStr"/>
-      <c r="L25" s="19" t="n">
-        <v>3</v>
-      </c>
-      <c r="M25" s="19" t="n">
-        <v>3</v>
-      </c>
-      <c r="N25" s="19" t="inlineStr"/>
-      <c r="O25" s="19" t="inlineStr"/>
+      <c r="J25" s="20" t="inlineStr"/>
+      <c r="K25" s="20" t="inlineStr"/>
+      <c r="L25" s="20" t="n">
+        <v>3</v>
+      </c>
+      <c r="M25" s="20" t="n">
+        <v>3</v>
+      </c>
+      <c r="N25" s="20" t="inlineStr"/>
+      <c r="O25" s="20" t="inlineStr"/>
     </row>
     <row r="26" outlineLevel="3">
-      <c r="B26" s="17" t="n"/>
-      <c r="C26" s="17" t="n"/>
-      <c r="D26" s="17" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="E26" s="17" t="n"/>
-      <c r="F26" s="17" t="n"/>
-      <c r="G26" s="19" t="n">
-        <v>3</v>
-      </c>
-      <c r="H26" s="19" t="inlineStr">
+      <c r="B26" s="18" t="n"/>
+      <c r="C26" s="18" t="n"/>
+      <c r="D26" s="18" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E26" s="18" t="n"/>
+      <c r="F26" s="18" t="n"/>
+      <c r="G26" s="20" t="n">
+        <v>3</v>
+      </c>
+      <c r="H26" s="20" t="inlineStr">
         <is>
           <t>NCC-FP006-02</t>
         </is>
       </c>
-      <c r="I26" s="19" t="inlineStr">
+      <c r="I26" s="20" t="inlineStr">
         <is>
           <t>1in Injector Stage Port (NCC-FP006.SLDPRT)</t>
         </is>
       </c>
-      <c r="J26" s="19" t="inlineStr">
+      <c r="J26" s="20" t="inlineStr">
         <is>
           <t>INJECTOR STAGE, 1" COIL</t>
         </is>
       </c>
-      <c r="K26" s="19" t="inlineStr"/>
-      <c r="L26" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="M26" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="N26" s="19" t="inlineStr"/>
-      <c r="O26" s="19" t="inlineStr"/>
+      <c r="K26" s="20" t="inlineStr"/>
+      <c r="L26" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="M26" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="N26" s="20" t="inlineStr"/>
+      <c r="O26" s="20" t="inlineStr"/>
     </row>
     <row r="27" outlineLevel="3">
-      <c r="B27" s="17" t="n"/>
-      <c r="C27" s="17" t="n"/>
-      <c r="D27" s="17" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="E27" s="17" t="n"/>
-      <c r="F27" s="17" t="n"/>
-      <c r="G27" s="19" t="n">
-        <v>3</v>
-      </c>
-      <c r="H27" s="19" t="inlineStr">
+      <c r="B27" s="18" t="n"/>
+      <c r="C27" s="18" t="n"/>
+      <c r="D27" s="18" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E27" s="18" t="n"/>
+      <c r="F27" s="18" t="n"/>
+      <c r="G27" s="20" t="n">
+        <v>3</v>
+      </c>
+      <c r="H27" s="20" t="inlineStr">
         <is>
           <t>90945A725_Tritanium Fleet Spec. Washer_WRP</t>
         </is>
       </c>
-      <c r="I27" s="19" t="inlineStr">
+      <c r="I27" s="20" t="inlineStr">
         <is>
           <t>Tritanium Fleet Spec. Washer (90945A725_Tritanium Fleet Spec. Washer_WRP.SLDPRT)</t>
         </is>
       </c>
-      <c r="J27" s="19" t="inlineStr">
+      <c r="J27" s="20" t="inlineStr">
         <is>
           <t>Tritanium Fleet Spec. Washer</t>
         </is>
       </c>
-      <c r="K27" s="19" t="inlineStr"/>
-      <c r="L27" s="19" t="n">
-        <v>3</v>
-      </c>
-      <c r="M27" s="19" t="n">
-        <v>3</v>
-      </c>
-      <c r="N27" s="19" t="inlineStr">
+      <c r="K27" s="20" t="inlineStr"/>
+      <c r="L27" s="20" t="n">
+        <v>3</v>
+      </c>
+      <c r="M27" s="20" t="n">
+        <v>3</v>
+      </c>
+      <c r="N27" s="20" t="inlineStr">
         <is>
           <t>Tritanium 18-8</t>
         </is>
       </c>
-      <c r="O27" s="19" t="inlineStr"/>
+      <c r="O27" s="20" t="inlineStr"/>
     </row>
     <row r="28" outlineLevel="3">
-      <c r="B28" s="17" t="n"/>
-      <c r="C28" s="17" t="n"/>
-      <c r="D28" s="17" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="E28" s="17" t="n"/>
-      <c r="F28" s="17" t="n"/>
-      <c r="G28" s="19" t="n">
-        <v>3</v>
-      </c>
-      <c r="H28" s="19" t="inlineStr">
+      <c r="B28" s="18" t="n"/>
+      <c r="C28" s="18" t="n"/>
+      <c r="D28" s="18" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E28" s="18" t="n"/>
+      <c r="F28" s="18" t="n"/>
+      <c r="G28" s="20" t="n">
+        <v>3</v>
+      </c>
+      <c r="H28" s="20" t="inlineStr">
         <is>
           <t>96246A046_Duranium Helical Insert_WRP</t>
         </is>
       </c>
-      <c r="I28" s="19" t="inlineStr">
+      <c r="I28" s="20" t="inlineStr">
         <is>
           <t>Duranium Helical Insert (96246A046_Duranium Helical Insert_WRP.SLDPRT)</t>
         </is>
       </c>
-      <c r="J28" s="19" t="inlineStr">
+      <c r="J28" s="20" t="inlineStr">
         <is>
           <t>Duranium Helical Insert</t>
         </is>
       </c>
-      <c r="K28" s="19" t="inlineStr"/>
-      <c r="L28" s="19" t="n">
+      <c r="K28" s="20" t="inlineStr"/>
+      <c r="L28" s="20" t="n">
         <v>7</v>
       </c>
-      <c r="M28" s="19" t="n">
+      <c r="M28" s="20" t="n">
         <v>7</v>
       </c>
-      <c r="N28" s="19" t="inlineStr">
+      <c r="N28" s="20" t="inlineStr">
         <is>
           <t>Nitronium 60 Duranium Alloy</t>
         </is>
       </c>
-      <c r="O28" s="19" t="inlineStr"/>
+      <c r="O28" s="20" t="inlineStr"/>
     </row>
     <row r="29" outlineLevel="3">
-      <c r="B29" s="17" t="n"/>
-      <c r="C29" s="17" t="n"/>
-      <c r="D29" s="17" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="E29" s="17" t="n"/>
-      <c r="F29" s="17" t="n"/>
-      <c r="G29" s="19" t="n">
-        <v>3</v>
-      </c>
-      <c r="H29" s="19" t="inlineStr">
+      <c r="B29" s="18" t="n"/>
+      <c r="C29" s="18" t="n"/>
+      <c r="D29" s="18" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E29" s="18" t="n"/>
+      <c r="F29" s="18" t="n"/>
+      <c r="G29" s="20" t="n">
+        <v>3</v>
+      </c>
+      <c r="H29" s="20" t="inlineStr">
         <is>
           <t>NCC-FP007-00</t>
         </is>
       </c>
-      <c r="I29" s="19" t="inlineStr">
+      <c r="I29" s="20" t="inlineStr">
         <is>
           <t>Coil Glue Bond (NCC-FP007.SLDPRT)</t>
         </is>
       </c>
-      <c r="J29" s="19" t="inlineStr">
+      <c r="J29" s="20" t="inlineStr">
         <is>
           <t>Sinlge 2216 bond for 1in coil.</t>
         </is>
       </c>
-      <c r="K29" s="19" t="inlineStr"/>
-      <c r="L29" s="19" t="n">
-        <v>3</v>
-      </c>
-      <c r="M29" s="19" t="n">
-        <v>3</v>
-      </c>
-      <c r="N29" s="19" t="inlineStr"/>
-      <c r="O29" s="19" t="inlineStr"/>
+      <c r="K29" s="20" t="inlineStr"/>
+      <c r="L29" s="20" t="n">
+        <v>3</v>
+      </c>
+      <c r="M29" s="20" t="n">
+        <v>3</v>
+      </c>
+      <c r="N29" s="20" t="inlineStr"/>
+      <c r="O29" s="20" t="inlineStr"/>
     </row>
     <row r="30" outlineLevel="3">
-      <c r="B30" s="17" t="n"/>
-      <c r="C30" s="17" t="n"/>
-      <c r="D30" s="17" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="E30" s="17" t="n"/>
-      <c r="F30" s="17" t="n"/>
-      <c r="G30" s="19" t="n">
-        <v>3</v>
-      </c>
-      <c r="H30" s="19" t="inlineStr">
+      <c r="B30" s="18" t="n"/>
+      <c r="C30" s="18" t="n"/>
+      <c r="D30" s="18" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E30" s="18" t="n"/>
+      <c r="F30" s="18" t="n"/>
+      <c r="G30" s="20" t="n">
+        <v>3</v>
+      </c>
+      <c r="H30" s="20" t="inlineStr">
         <is>
           <t>NCC-FP004-B</t>
         </is>
       </c>
-      <c r="I30" s="19" t="inlineStr">
+      <c r="I30" s="20" t="inlineStr">
         <is>
           <t>1in Injector Radial Cell (NCC-FP004.SLDPRT)</t>
         </is>
       </c>
-      <c r="J30" s="19" t="inlineStr">
+      <c r="J30" s="20" t="inlineStr">
         <is>
           <t>Radial Cell of Injector 3DOF or 5DOF Coil Mount</t>
         </is>
       </c>
-      <c r="K30" s="19" t="inlineStr"/>
-      <c r="L30" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="M30" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="N30" s="19" t="inlineStr">
+      <c r="K30" s="20" t="inlineStr"/>
+      <c r="L30" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="M30" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="N30" s="20" t="inlineStr">
         <is>
           <t>Tritanium-36 Plate</t>
         </is>
       </c>
-      <c r="O30" s="19" t="inlineStr">
+      <c r="O30" s="20" t="inlineStr">
         <is>
           <t>0.064</t>
         </is>
       </c>
     </row>
     <row r="31" outlineLevel="3">
-      <c r="B31" s="17" t="n"/>
-      <c r="C31" s="17" t="n"/>
-      <c r="D31" s="17" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="E31" s="17" t="n"/>
-      <c r="F31" s="17" t="n"/>
-      <c r="G31" s="19" t="n">
-        <v>3</v>
-      </c>
-      <c r="H31" s="19" t="inlineStr">
+      <c r="B31" s="18" t="n"/>
+      <c r="C31" s="18" t="n"/>
+      <c r="D31" s="18" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E31" s="18" t="n"/>
+      <c r="F31" s="18" t="n"/>
+      <c r="G31" s="20" t="n">
+        <v>3</v>
+      </c>
+      <c r="H31" s="20" t="inlineStr">
         <is>
           <t>92423A491_High-Strength Duranium Socket Head Screw_WRP</t>
         </is>
       </c>
-      <c r="I31" s="19" t="inlineStr">
+      <c r="I31" s="20" t="inlineStr">
         <is>
           <t>High-Strength Duranium Socket Head Screw (92423A491_High-Strength Duranium Socket Head Screw_WRP.SLDPRT)</t>
         </is>
       </c>
-      <c r="J31" s="19" t="inlineStr">
+      <c r="J31" s="20" t="inlineStr">
         <is>
           <t>High-Strength Duranium Socket Head Screw</t>
         </is>
       </c>
-      <c r="K31" s="19" t="inlineStr"/>
-      <c r="L31" s="19" t="n">
-        <v>3</v>
-      </c>
-      <c r="M31" s="19" t="n">
-        <v>3</v>
-      </c>
-      <c r="N31" s="19" t="inlineStr">
+      <c r="K31" s="20" t="inlineStr"/>
+      <c r="L31" s="20" t="n">
+        <v>3</v>
+      </c>
+      <c r="M31" s="20" t="n">
+        <v>3</v>
+      </c>
+      <c r="N31" s="20" t="inlineStr">
         <is>
           <t>Duranium A286 Alloy</t>
         </is>
       </c>
-      <c r="O31" s="19" t="inlineStr"/>
+      <c r="O31" s="20" t="inlineStr"/>
     </row>
     <row r="32" outlineLevel="3">
-      <c r="B32" s="17" t="n"/>
-      <c r="C32" s="17" t="n"/>
-      <c r="D32" s="17" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="E32" s="17" t="n"/>
-      <c r="F32" s="17" t="n"/>
-      <c r="G32" s="18" t="n">
-        <v>3</v>
-      </c>
-      <c r="H32" s="18" t="inlineStr">
+      <c r="B32" s="18" t="n"/>
+      <c r="C32" s="18" t="n"/>
+      <c r="D32" s="18" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E32" s="18" t="n"/>
+      <c r="F32" s="18" t="n"/>
+      <c r="G32" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="H32" s="19" t="inlineStr">
         <is>
           <t>AK000007S_WRP</t>
         </is>
       </c>
-      <c r="I32" s="18" t="inlineStr">
+      <c r="I32" s="19" t="inlineStr">
         <is>
           <t>AK000007S WRP (AK000007S_WRP.SLDASM)</t>
         </is>
       </c>
-      <c r="J32" s="18" t="inlineStr"/>
-      <c r="K32" s="18" t="inlineStr"/>
-      <c r="L32" s="18" t="n">
+      <c r="J32" s="19" t="inlineStr"/>
+      <c r="K32" s="19" t="inlineStr"/>
+      <c r="L32" s="19" t="n">
         <v>6</v>
       </c>
-      <c r="M32" s="18" t="n">
+      <c r="M32" s="19" t="n">
         <v>6</v>
       </c>
-      <c r="N32" s="18" t="inlineStr"/>
-      <c r="O32" s="18" t="inlineStr"/>
+      <c r="N32" s="19" t="inlineStr"/>
+      <c r="O32" s="19" t="inlineStr"/>
     </row>
     <row r="33" outlineLevel="4">
-      <c r="B33" s="17" t="n"/>
-      <c r="C33" s="17" t="n"/>
-      <c r="D33" s="17" t="n"/>
-      <c r="E33" s="17" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="F33" s="17" t="n"/>
-      <c r="G33" s="19" t="n">
+      <c r="B33" s="18" t="n"/>
+      <c r="C33" s="18" t="n"/>
+      <c r="D33" s="18" t="n"/>
+      <c r="E33" s="18" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F33" s="18" t="n"/>
+      <c r="G33" s="20" t="n">
         <v>4</v>
       </c>
-      <c r="H33" s="19" t="inlineStr">
+      <c r="H33" s="20" t="inlineStr">
         <is>
           <t>AK020004 EPS Tap Rev A_WRP</t>
         </is>
       </c>
-      <c r="I33" s="19" t="inlineStr">
+      <c r="I33" s="20" t="inlineStr">
         <is>
           <t>AK020004 EPS Tap Rev A WRP (AK020004 EPS Tap Rev A_WRP.SLDPRT)</t>
         </is>
       </c>
-      <c r="J33" s="19" t="inlineStr"/>
-      <c r="K33" s="19" t="inlineStr"/>
-      <c r="L33" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="M33" s="19" t="n">
+      <c r="J33" s="20" t="inlineStr"/>
+      <c r="K33" s="20" t="inlineStr"/>
+      <c r="L33" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="M33" s="20" t="n">
         <v>6</v>
       </c>
-      <c r="N33" s="19" t="inlineStr"/>
-      <c r="O33" s="19" t="inlineStr"/>
+      <c r="N33" s="20" t="inlineStr"/>
+      <c r="O33" s="20" t="inlineStr"/>
     </row>
     <row r="34" outlineLevel="4">
-      <c r="B34" s="17" t="n"/>
-      <c r="C34" s="17" t="n"/>
-      <c r="D34" s="17" t="n"/>
-      <c r="E34" s="17" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="F34" s="17" t="n"/>
-      <c r="G34" s="19" t="n">
+      <c r="B34" s="18" t="n"/>
+      <c r="C34" s="18" t="n"/>
+      <c r="D34" s="18" t="n"/>
+      <c r="E34" s="18" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F34" s="18" t="n"/>
+      <c r="G34" s="20" t="n">
         <v>4</v>
       </c>
-      <c r="H34" s="19" t="inlineStr">
+      <c r="H34" s="20" t="inlineStr">
         <is>
           <t>HD301004 SBS 92196A108_Tritanium Socket Head Screw_WRP</t>
         </is>
       </c>
-      <c r="I34" s="19" t="inlineStr">
+      <c r="I34" s="20" t="inlineStr">
         <is>
           <t>Tritanium Socket Head Screw (HD301004 SBS 92196A108_Tritanium Socket Head Screw_WRP.SLDPRT)</t>
         </is>
       </c>
-      <c r="J34" s="19" t="inlineStr">
+      <c r="J34" s="20" t="inlineStr">
         <is>
           <t>Tritanium Socket Head Screw</t>
         </is>
       </c>
-      <c r="K34" s="19" t="inlineStr"/>
-      <c r="L34" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="M34" s="19" t="n">
+      <c r="K34" s="20" t="inlineStr"/>
+      <c r="L34" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="M34" s="20" t="n">
         <v>6</v>
       </c>
-      <c r="N34" s="19" t="inlineStr">
+      <c r="N34" s="20" t="inlineStr">
         <is>
           <t>Tritanium 18-8</t>
         </is>
       </c>
-      <c r="O34" s="19" t="inlineStr"/>
+      <c r="O34" s="20" t="inlineStr"/>
     </row>
     <row r="35" outlineLevel="4">
-      <c r="B35" s="17" t="n"/>
-      <c r="C35" s="17" t="n"/>
-      <c r="D35" s="17" t="n"/>
-      <c r="E35" s="17" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="F35" s="17" t="n"/>
-      <c r="G35" s="19" t="n">
+      <c r="B35" s="18" t="n"/>
+      <c r="C35" s="18" t="n"/>
+      <c r="D35" s="18" t="n"/>
+      <c r="E35" s="18" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F35" s="18" t="n"/>
+      <c r="G35" s="20" t="n">
         <v>4</v>
       </c>
-      <c r="H35" s="19" t="inlineStr">
+      <c r="H35" s="20" t="inlineStr">
         <is>
           <t>HD101004 EPS Tap Adjuster Rev B_WRP</t>
         </is>
       </c>
-      <c r="I35" s="19" t="inlineStr">
+      <c r="I35" s="20" t="inlineStr">
         <is>
           <t>HD101004 EPS Tap Adjuster Rev B WRP (HD101004 EPS Tap Adjuster Rev B_WRP.SLDPRT)</t>
         </is>
       </c>
-      <c r="J35" s="19" t="inlineStr"/>
-      <c r="K35" s="19" t="inlineStr"/>
-      <c r="L35" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="M35" s="19" t="n">
+      <c r="J35" s="20" t="inlineStr"/>
+      <c r="K35" s="20" t="inlineStr"/>
+      <c r="L35" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="M35" s="20" t="n">
         <v>6</v>
       </c>
-      <c r="N35" s="19" t="inlineStr"/>
-      <c r="O35" s="19" t="inlineStr"/>
+      <c r="N35" s="20" t="inlineStr"/>
+      <c r="O35" s="20" t="inlineStr"/>
     </row>
     <row r="36" outlineLevel="2">
-      <c r="B36" s="17" t="n"/>
-      <c r="C36" s="17" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="D36" s="17" t="n"/>
-      <c r="E36" s="17" t="n"/>
-      <c r="F36" s="17" t="n"/>
-      <c r="G36" s="19" t="n">
-        <v>2</v>
-      </c>
-      <c r="H36" s="19" t="inlineStr">
+      <c r="B36" s="18" t="n"/>
+      <c r="C36" s="18" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="D36" s="18" t="n"/>
+      <c r="E36" s="18" t="n"/>
+      <c r="F36" s="18" t="n"/>
+      <c r="G36" s="20" t="n">
+        <v>2</v>
+      </c>
+      <c r="H36" s="20" t="inlineStr">
         <is>
           <t>FM2_WRP</t>
         </is>
       </c>
-      <c r="I36" s="19" t="inlineStr">
+      <c r="I36" s="20" t="inlineStr">
         <is>
           <t>WRP-NCC-2219 (FM2_WRP.SLDPRT)</t>
         </is>
       </c>
-      <c r="J36" s="19" t="inlineStr">
+      <c r="J36" s="20" t="inlineStr">
         <is>
           <t>FM2 FOR RCS</t>
         </is>
       </c>
-      <c r="K36" s="19" t="inlineStr"/>
-      <c r="L36" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="M36" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="N36" s="19" t="inlineStr"/>
-      <c r="O36" s="19" t="inlineStr"/>
+      <c r="K36" s="20" t="inlineStr"/>
+      <c r="L36" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="M36" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="N36" s="20" t="inlineStr"/>
+      <c r="O36" s="20" t="inlineStr"/>
     </row>
     <row r="37" outlineLevel="2">
-      <c r="B37" s="17" t="n"/>
-      <c r="C37" s="17" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="D37" s="17" t="n"/>
-      <c r="E37" s="17" t="n"/>
-      <c r="F37" s="17" t="n"/>
-      <c r="G37" s="19" t="n">
-        <v>2</v>
-      </c>
-      <c r="H37" s="19" t="inlineStr">
+      <c r="B37" s="18" t="n"/>
+      <c r="C37" s="18" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="D37" s="18" t="n"/>
+      <c r="E37" s="18" t="n"/>
+      <c r="F37" s="18" t="n"/>
+      <c r="G37" s="20" t="n">
+        <v>2</v>
+      </c>
+      <c r="H37" s="20" t="inlineStr">
         <is>
           <t>NCC-FP060-00</t>
         </is>
       </c>
-      <c r="I37" s="19" t="inlineStr">
+      <c r="I37" s="20" t="inlineStr">
         <is>
           <t>Emitter - Coil9A (NCC-FP060.SLDPRT)</t>
         </is>
       </c>
-      <c r="J37" s="19" t="inlineStr">
+      <c r="J37" s="20" t="inlineStr">
         <is>
           <t>1k Coil9</t>
         </is>
       </c>
-      <c r="K37" s="19" t="inlineStr"/>
-      <c r="L37" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="M37" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="N37" s="19" t="inlineStr">
+      <c r="K37" s="20" t="inlineStr"/>
+      <c r="L37" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="M37" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="N37" s="20" t="inlineStr">
         <is>
           <t>Transparent Aluminum</t>
         </is>
       </c>
-      <c r="O37" s="19" t="inlineStr">
+      <c r="O37" s="20" t="inlineStr">
         <is>
           <t>0.01</t>
         </is>
       </c>
     </row>
     <row r="38" outlineLevel="1">
-      <c r="B38" s="17" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="C38" s="17" t="n"/>
-      <c r="D38" s="17" t="n"/>
-      <c r="E38" s="17" t="n"/>
-      <c r="F38" s="17" t="n"/>
-      <c r="G38" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="H38" s="18" t="inlineStr">
+      <c r="B38" s="18" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="C38" s="18" t="n"/>
+      <c r="D38" s="18" t="n"/>
+      <c r="E38" s="18" t="n"/>
+      <c r="F38" s="18" t="n"/>
+      <c r="G38" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="H38" s="19" t="inlineStr">
         <is>
           <t>NCC-FA019-00</t>
         </is>
       </c>
-      <c r="I38" s="18" t="inlineStr">
+      <c r="I38" s="19" t="inlineStr">
         <is>
           <t>Deflector Pinhole Blocker Assembly (NCC-FA019.SLDASM)</t>
         </is>
       </c>
-      <c r="J38" s="18" t="inlineStr">
+      <c r="J38" s="19" t="inlineStr">
         <is>
           <t>Fail into beam blocker for secondary pinhole in deflector stop</t>
         </is>
       </c>
-      <c r="K38" s="18" t="inlineStr"/>
-      <c r="L38" s="18" t="n">
-        <v>2</v>
-      </c>
-      <c r="M38" s="18" t="n">
-        <v>2</v>
-      </c>
-      <c r="N38" s="18" t="inlineStr"/>
-      <c r="O38" s="18" t="inlineStr"/>
+      <c r="K38" s="19" t="inlineStr"/>
+      <c r="L38" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="M38" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="N38" s="19" t="inlineStr"/>
+      <c r="O38" s="19" t="inlineStr"/>
     </row>
     <row r="39" outlineLevel="2">
-      <c r="B39" s="17" t="n"/>
-      <c r="C39" s="17" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="D39" s="17" t="n"/>
-      <c r="E39" s="17" t="n"/>
-      <c r="F39" s="17" t="n"/>
-      <c r="G39" s="19" t="n">
-        <v>2</v>
-      </c>
-      <c r="H39" s="19" t="inlineStr">
+      <c r="B39" s="18" t="n"/>
+      <c r="C39" s="18" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="D39" s="18" t="n"/>
+      <c r="E39" s="18" t="n"/>
+      <c r="F39" s="18" t="n"/>
+      <c r="G39" s="20" t="n">
+        <v>2</v>
+      </c>
+      <c r="H39" s="20" t="inlineStr">
         <is>
           <t>deflectorActuatorFlag</t>
         </is>
       </c>
-      <c r="I39" s="19" t="inlineStr">
+      <c r="I39" s="20" t="inlineStr">
         <is>
           <t>deflectorActuatorFlag (deflectorActuatorFlag.SLDPRT)</t>
         </is>
       </c>
-      <c r="J39" s="19" t="inlineStr"/>
-      <c r="K39" s="19" t="inlineStr"/>
-      <c r="L39" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="M39" s="19" t="n">
-        <v>2</v>
-      </c>
-      <c r="N39" s="19" t="inlineStr"/>
-      <c r="O39" s="19" t="inlineStr"/>
+      <c r="J39" s="20" t="inlineStr"/>
+      <c r="K39" s="20" t="inlineStr"/>
+      <c r="L39" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="M39" s="20" t="n">
+        <v>2</v>
+      </c>
+      <c r="N39" s="20" t="inlineStr"/>
+      <c r="O39" s="20" t="inlineStr"/>
     </row>
     <row r="40" outlineLevel="2">
-      <c r="B40" s="17" t="n"/>
-      <c r="C40" s="17" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="D40" s="17" t="n"/>
-      <c r="E40" s="17" t="n"/>
-      <c r="F40" s="17" t="n"/>
-      <c r="G40" s="19" t="n">
-        <v>2</v>
-      </c>
-      <c r="H40" s="19" t="inlineStr">
+      <c r="B40" s="18" t="n"/>
+      <c r="C40" s="18" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="D40" s="18" t="n"/>
+      <c r="E40" s="18" t="n"/>
+      <c r="F40" s="18" t="n"/>
+      <c r="G40" s="20" t="n">
+        <v>2</v>
+      </c>
+      <c r="H40" s="20" t="inlineStr">
         <is>
           <t>92423A412_High-Strength Duranium Socket Head Screw_ENT</t>
         </is>
       </c>
-      <c r="I40" s="19" t="inlineStr">
+      <c r="I40" s="20" t="inlineStr">
         <is>
           <t>92423A412 High-Strength Duranium Socket Head Screw ENT (92423A412_High-Strength Duranium Socket Head Screw_ENT.SLDPRT)</t>
         </is>
       </c>
-      <c r="J40" s="19" t="inlineStr"/>
-      <c r="K40" s="19" t="inlineStr"/>
-      <c r="L40" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="M40" s="19" t="n">
-        <v>2</v>
-      </c>
-      <c r="N40" s="19" t="inlineStr">
+      <c r="J40" s="20" t="inlineStr"/>
+      <c r="K40" s="20" t="inlineStr"/>
+      <c r="L40" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="M40" s="20" t="n">
+        <v>2</v>
+      </c>
+      <c r="N40" s="20" t="inlineStr">
         <is>
           <t>Duranium A286 Alloy</t>
         </is>
       </c>
-      <c r="O40" s="19" t="inlineStr">
+      <c r="O40" s="20" t="inlineStr">
         <is>
           <t>SW-Mass@.SLDPRT</t>
         </is>
       </c>
     </row>
     <row r="41" outlineLevel="2">
-      <c r="B41" s="17" t="n"/>
-      <c r="C41" s="17" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="D41" s="17" t="n"/>
-      <c r="E41" s="17" t="n"/>
-      <c r="F41" s="17" t="n"/>
-      <c r="G41" s="19" t="n">
-        <v>2</v>
-      </c>
-      <c r="H41" s="19" t="inlineStr">
+      <c r="B41" s="18" t="n"/>
+      <c r="C41" s="18" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="D41" s="18" t="n"/>
+      <c r="E41" s="18" t="n"/>
+      <c r="F41" s="18" t="n"/>
+      <c r="G41" s="20" t="n">
+        <v>2</v>
+      </c>
+      <c r="H41" s="20" t="inlineStr">
         <is>
           <t>96246A074_Duranium Helical Insert_ENT</t>
         </is>
       </c>
-      <c r="I41" s="19" t="inlineStr">
+      <c r="I41" s="20" t="inlineStr">
         <is>
           <t>96246A074 Duranium Helical Insert ENT (96246A074_Duranium Helical Insert_ENT.SLDPRT)</t>
         </is>
       </c>
-      <c r="J41" s="19" t="inlineStr"/>
-      <c r="K41" s="19" t="inlineStr"/>
-      <c r="L41" s="19" t="n">
-        <v>2</v>
-      </c>
-      <c r="M41" s="19" t="n">
+      <c r="J41" s="20" t="inlineStr"/>
+      <c r="K41" s="20" t="inlineStr"/>
+      <c r="L41" s="20" t="n">
+        <v>2</v>
+      </c>
+      <c r="M41" s="20" t="n">
         <v>4</v>
       </c>
-      <c r="N41" s="19" t="inlineStr">
+      <c r="N41" s="20" t="inlineStr">
         <is>
           <t>Nitronium 60 Duranium Alloy</t>
         </is>
       </c>
-      <c r="O41" s="19" t="inlineStr">
+      <c r="O41" s="20" t="inlineStr">
         <is>
           <t>SW-Mass@.SLDPRT</t>
         </is>
       </c>
     </row>
     <row r="42" outlineLevel="2">
-      <c r="B42" s="17" t="n"/>
-      <c r="C42" s="17" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="D42" s="17" t="n"/>
-      <c r="E42" s="17" t="n"/>
-      <c r="F42" s="17" t="n"/>
-      <c r="G42" s="19" t="n">
-        <v>2</v>
-      </c>
-      <c r="H42" s="19" t="inlineStr">
+      <c r="B42" s="18" t="n"/>
+      <c r="C42" s="18" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="D42" s="18" t="n"/>
+      <c r="E42" s="18" t="n"/>
+      <c r="F42" s="18" t="n"/>
+      <c r="G42" s="20" t="n">
+        <v>2</v>
+      </c>
+      <c r="H42" s="20" t="inlineStr">
         <is>
           <t>a1439solenoid</t>
         </is>
       </c>
-      <c r="I42" s="19" t="inlineStr">
+      <c r="I42" s="20" t="inlineStr">
         <is>
           <t>Deflector Shutter (a1439solenoid.SLDPRT)</t>
         </is>
       </c>
-      <c r="J42" s="19" t="inlineStr">
+      <c r="J42" s="20" t="inlineStr">
         <is>
           <t>Modified COTS part a1320-1 shutter</t>
         </is>
       </c>
-      <c r="K42" s="19" t="inlineStr"/>
-      <c r="L42" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="M42" s="19" t="n">
-        <v>2</v>
-      </c>
-      <c r="N42" s="19" t="inlineStr"/>
-      <c r="O42" s="19" t="inlineStr">
+      <c r="K42" s="20" t="inlineStr"/>
+      <c r="L42" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="M42" s="20" t="n">
+        <v>2</v>
+      </c>
+      <c r="N42" s="20" t="inlineStr"/>
+      <c r="O42" s="20" t="inlineStr">
         <is>
           <t>0.004179</t>
         </is>
       </c>
     </row>
     <row r="43" outlineLevel="2">
-      <c r="B43" s="17" t="n"/>
-      <c r="C43" s="17" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="D43" s="17" t="n"/>
-      <c r="E43" s="17" t="n"/>
-      <c r="F43" s="17" t="n"/>
-      <c r="G43" s="19" t="n">
-        <v>2</v>
-      </c>
-      <c r="H43" s="19" t="inlineStr">
+      <c r="B43" s="18" t="n"/>
+      <c r="C43" s="18" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="D43" s="18" t="n"/>
+      <c r="E43" s="18" t="n"/>
+      <c r="F43" s="18" t="n"/>
+      <c r="G43" s="20" t="n">
+        <v>2</v>
+      </c>
+      <c r="H43" s="20" t="inlineStr">
         <is>
           <t>92423A461_High-Strength Duranium Socket Head Screw</t>
         </is>
       </c>
-      <c r="I43" s="19" t="inlineStr">
+      <c r="I43" s="20" t="inlineStr">
         <is>
           <t>92423A461 High-Strength Duranium Socket Head Screw (92423A461_High-Strength Duranium Socket Head Screw.SLDPRT)</t>
         </is>
       </c>
-      <c r="J43" s="19" t="inlineStr"/>
-      <c r="K43" s="19" t="inlineStr"/>
-      <c r="L43" s="19" t="n">
-        <v>3</v>
-      </c>
-      <c r="M43" s="19" t="n">
+      <c r="J43" s="20" t="inlineStr"/>
+      <c r="K43" s="20" t="inlineStr"/>
+      <c r="L43" s="20" t="n">
+        <v>3</v>
+      </c>
+      <c r="M43" s="20" t="n">
         <v>6</v>
       </c>
-      <c r="N43" s="19" t="inlineStr">
+      <c r="N43" s="20" t="inlineStr">
         <is>
           <t>Duranium A286 Alloy</t>
         </is>
       </c>
-      <c r="O43" s="19" t="inlineStr"/>
+      <c r="O43" s="20" t="inlineStr"/>
     </row>
     <row r="44" outlineLevel="2">
-      <c r="B44" s="17" t="n"/>
-      <c r="C44" s="17" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="D44" s="17" t="n"/>
-      <c r="E44" s="17" t="n"/>
-      <c r="F44" s="17" t="n"/>
-      <c r="G44" s="19" t="n">
-        <v>2</v>
-      </c>
-      <c r="H44" s="19" t="inlineStr">
+      <c r="B44" s="18" t="n"/>
+      <c r="C44" s="18" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="D44" s="18" t="n"/>
+      <c r="E44" s="18" t="n"/>
+      <c r="F44" s="18" t="n"/>
+      <c r="G44" s="20" t="n">
+        <v>2</v>
+      </c>
+      <c r="H44" s="20" t="inlineStr">
         <is>
           <t>NCC-FP040-00</t>
         </is>
       </c>
-      <c r="I44" s="19" t="inlineStr">
+      <c r="I44" s="20" t="inlineStr">
         <is>
           <t>EPS Bracket (NCC-FP040.SLDPRT)</t>
         </is>
       </c>
-      <c r="J44" s="19" t="inlineStr">
+      <c r="J44" s="20" t="inlineStr">
         <is>
           <t>Bracket for a1439 solenoid</t>
         </is>
       </c>
-      <c r="K44" s="19" t="inlineStr"/>
-      <c r="L44" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="M44" s="19" t="n">
-        <v>2</v>
-      </c>
-      <c r="N44" s="19" t="inlineStr">
+      <c r="K44" s="20" t="inlineStr"/>
+      <c r="L44" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="M44" s="20" t="n">
+        <v>2</v>
+      </c>
+      <c r="N44" s="20" t="inlineStr">
         <is>
           <t>Tritanium-36 Plate</t>
         </is>
       </c>
-      <c r="O44" s="19" t="inlineStr"/>
+      <c r="O44" s="20" t="inlineStr"/>
     </row>
     <row r="45" outlineLevel="2">
-      <c r="B45" s="17" t="n"/>
-      <c r="C45" s="17" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="D45" s="17" t="n"/>
-      <c r="E45" s="17" t="n"/>
-      <c r="F45" s="17" t="n"/>
-      <c r="G45" s="19" t="n">
-        <v>2</v>
-      </c>
-      <c r="H45" s="19" t="inlineStr">
+      <c r="B45" s="18" t="n"/>
+      <c r="C45" s="18" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="D45" s="18" t="n"/>
+      <c r="E45" s="18" t="n"/>
+      <c r="F45" s="18" t="n"/>
+      <c r="G45" s="20" t="n">
+        <v>2</v>
+      </c>
+      <c r="H45" s="20" t="inlineStr">
         <is>
           <t>92423A451_High-Strength Duranium Socket Head Screw_ENT</t>
         </is>
       </c>
-      <c r="I45" s="19" t="inlineStr">
+      <c r="I45" s="20" t="inlineStr">
         <is>
           <t>92423A451 High-Strength Duranium Socket Head Screw ENT (92423A451_High-Strength Duranium Socket Head Screw_ENT.SLDPRT)</t>
         </is>
       </c>
-      <c r="J45" s="19" t="inlineStr"/>
-      <c r="K45" s="19" t="inlineStr"/>
-      <c r="L45" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="M45" s="19" t="n">
-        <v>2</v>
-      </c>
-      <c r="N45" s="19" t="inlineStr">
+      <c r="J45" s="20" t="inlineStr"/>
+      <c r="K45" s="20" t="inlineStr"/>
+      <c r="L45" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="M45" s="20" t="n">
+        <v>2</v>
+      </c>
+      <c r="N45" s="20" t="inlineStr">
         <is>
           <t>Duranium A286 Alloy</t>
         </is>
       </c>
-      <c r="O45" s="19" t="inlineStr">
+      <c r="O45" s="20" t="inlineStr">
         <is>
           <t>SW-Mass@.SLDPRT</t>
         </is>
       </c>
     </row>
     <row r="46" outlineLevel="2">
-      <c r="B46" s="17" t="n"/>
-      <c r="C46" s="17" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="D46" s="17" t="n"/>
-      <c r="E46" s="17" t="n"/>
-      <c r="F46" s="17" t="n"/>
-      <c r="G46" s="19" t="n">
-        <v>2</v>
-      </c>
-      <c r="H46" s="19" t="inlineStr">
+      <c r="B46" s="18" t="n"/>
+      <c r="C46" s="18" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="D46" s="18" t="n"/>
+      <c r="E46" s="18" t="n"/>
+      <c r="F46" s="18" t="n"/>
+      <c r="G46" s="20" t="n">
+        <v>2</v>
+      </c>
+      <c r="H46" s="20" t="inlineStr">
         <is>
           <t>epsIsolator</t>
         </is>
       </c>
-      <c r="I46" s="19" t="inlineStr">
+      <c r="I46" s="20" t="inlineStr">
         <is>
           <t>epsIsolator (epsIsolator.SLDPRT)</t>
         </is>
       </c>
-      <c r="J46" s="19" t="inlineStr"/>
-      <c r="K46" s="19" t="inlineStr"/>
-      <c r="L46" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="M46" s="19" t="n">
-        <v>2</v>
-      </c>
-      <c r="N46" s="19" t="inlineStr">
+      <c r="J46" s="20" t="inlineStr"/>
+      <c r="K46" s="20" t="inlineStr"/>
+      <c r="L46" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="M46" s="20" t="n">
+        <v>2</v>
+      </c>
+      <c r="N46" s="20" t="inlineStr">
         <is>
           <t>Castrodinium Epoxy Composite</t>
         </is>
       </c>
-      <c r="O46" s="19" t="inlineStr">
+      <c r="O46" s="20" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
     </row>
     <row r="47" outlineLevel="2">
-      <c r="B47" s="17" t="n"/>
-      <c r="C47" s="17" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="D47" s="17" t="n"/>
-      <c r="E47" s="17" t="n"/>
-      <c r="F47" s="17" t="n"/>
-      <c r="G47" s="19" t="n">
-        <v>2</v>
-      </c>
-      <c r="H47" s="19" t="inlineStr">
+      <c r="B47" s="18" t="n"/>
+      <c r="C47" s="18" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="D47" s="18" t="n"/>
+      <c r="E47" s="18" t="n"/>
+      <c r="F47" s="18" t="n"/>
+      <c r="G47" s="20" t="n">
+        <v>2</v>
+      </c>
+      <c r="H47" s="20" t="inlineStr">
         <is>
           <t>NCC-FP033-00</t>
         </is>
       </c>
-      <c r="I47" s="19" t="inlineStr">
+      <c r="I47" s="20" t="inlineStr">
         <is>
           <t>EPS Deflector Shutter (NCC-FP033.SLDPRT)</t>
         </is>
       </c>
-      <c r="J47" s="19" t="inlineStr">
+      <c r="J47" s="20" t="inlineStr">
         <is>
           <t>Modified COTS part a1320-1_shutter</t>
         </is>
       </c>
-      <c r="K47" s="19" t="inlineStr"/>
-      <c r="L47" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="M47" s="19" t="n">
-        <v>2</v>
-      </c>
-      <c r="N47" s="19" t="inlineStr"/>
-      <c r="O47" s="19" t="inlineStr"/>
+      <c r="K47" s="20" t="inlineStr"/>
+      <c r="L47" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="M47" s="20" t="n">
+        <v>2</v>
+      </c>
+      <c r="N47" s="20" t="inlineStr"/>
+      <c r="O47" s="20" t="inlineStr"/>
     </row>
     <row r="48" outlineLevel="2">
-      <c r="B48" s="17" t="n"/>
-      <c r="C48" s="17" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="D48" s="17" t="n"/>
-      <c r="E48" s="17" t="n"/>
-      <c r="F48" s="17" t="n"/>
-      <c r="G48" s="19" t="n">
-        <v>2</v>
-      </c>
-      <c r="H48" s="19" t="inlineStr">
+      <c r="B48" s="18" t="n"/>
+      <c r="C48" s="18" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="D48" s="18" t="n"/>
+      <c r="E48" s="18" t="n"/>
+      <c r="F48" s="18" t="n"/>
+      <c r="G48" s="20" t="n">
+        <v>2</v>
+      </c>
+      <c r="H48" s="20" t="inlineStr">
         <is>
           <t>92423A462_High-Strength Duranium Socket Head Screw_ENT</t>
         </is>
       </c>
-      <c r="I48" s="19" t="inlineStr">
+      <c r="I48" s="20" t="inlineStr">
         <is>
           <t>92423A462 High-Strength Duranium Socket Head Screw ENT (92423A462_High-Strength Duranium Socket Head Screw_ENT.SLDPRT)</t>
         </is>
       </c>
-      <c r="J48" s="19" t="inlineStr"/>
-      <c r="K48" s="19" t="inlineStr"/>
-      <c r="L48" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="M48" s="19" t="n">
-        <v>2</v>
-      </c>
-      <c r="N48" s="19" t="inlineStr">
+      <c r="J48" s="20" t="inlineStr"/>
+      <c r="K48" s="20" t="inlineStr"/>
+      <c r="L48" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="M48" s="20" t="n">
+        <v>2</v>
+      </c>
+      <c r="N48" s="20" t="inlineStr">
         <is>
           <t>Duranium A286 Alloy</t>
         </is>
       </c>
-      <c r="O48" s="19" t="inlineStr">
+      <c r="O48" s="20" t="inlineStr">
         <is>
           <t>SW-Mass@.SLDPRT</t>
         </is>
       </c>
     </row>
     <row r="49" outlineLevel="1">
-      <c r="B49" s="17" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="C49" s="17" t="n"/>
-      <c r="D49" s="17" t="n"/>
-      <c r="E49" s="17" t="n"/>
-      <c r="F49" s="17" t="n"/>
-      <c r="G49" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="H49" s="18" t="inlineStr">
+      <c r="B49" s="18" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="C49" s="18" t="n"/>
+      <c r="D49" s="18" t="n"/>
+      <c r="E49" s="18" t="n"/>
+      <c r="F49" s="18" t="n"/>
+      <c r="G49" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="H49" s="19" t="inlineStr">
         <is>
           <t>NCC-FA014-00</t>
         </is>
       </c>
-      <c r="I49" s="18" t="inlineStr">
+      <c r="I49" s="19" t="inlineStr">
         <is>
           <t>1in Cell Mounted Plasma Injector 5-DOF Mount Port With Coil (NCC-FA014.SLDASM)</t>
         </is>
       </c>
-      <c r="J49" s="18" t="inlineStr">
+      <c r="J49" s="19" t="inlineStr">
         <is>
           <t>1in Cell Mounted Plasma Injector 5-DOF Mount Port With Coil</t>
         </is>
       </c>
-      <c r="K49" s="18" t="inlineStr"/>
-      <c r="L49" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="M49" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="N49" s="18" t="inlineStr"/>
-      <c r="O49" s="18" t="inlineStr"/>
+      <c r="K49" s="19" t="inlineStr"/>
+      <c r="L49" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="M49" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="N49" s="19" t="inlineStr"/>
+      <c r="O49" s="19" t="inlineStr"/>
     </row>
     <row r="50" outlineLevel="2">
-      <c r="B50" s="17" t="n"/>
-      <c r="C50" s="17" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="D50" s="17" t="n"/>
-      <c r="E50" s="17" t="n"/>
-      <c r="F50" s="17" t="n"/>
-      <c r="G50" s="18" t="n">
-        <v>2</v>
-      </c>
-      <c r="H50" s="18" t="inlineStr">
+      <c r="B50" s="18" t="n"/>
+      <c r="C50" s="18" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="D50" s="18" t="n"/>
+      <c r="E50" s="18" t="n"/>
+      <c r="F50" s="18" t="n"/>
+      <c r="G50" s="19" t="n">
+        <v>2</v>
+      </c>
+      <c r="H50" s="19" t="inlineStr">
         <is>
           <t>NCC-FA004-00</t>
         </is>
       </c>
-      <c r="I50" s="18" t="inlineStr">
+      <c r="I50" s="19" t="inlineStr">
         <is>
           <t>Injector Mount Assembly Port No Coil (NCC-FA004.SLDASM)</t>
         </is>
       </c>
-      <c r="J50" s="18" t="inlineStr">
+      <c r="J50" s="19" t="inlineStr">
         <is>
           <t>1in Cell Mounted Plasma Injector 5-DOF Mount Port No Coil</t>
         </is>
       </c>
-      <c r="K50" s="18" t="inlineStr"/>
-      <c r="L50" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="M50" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="N50" s="18" t="inlineStr"/>
-      <c r="O50" s="18" t="inlineStr"/>
+      <c r="K50" s="19" t="inlineStr"/>
+      <c r="L50" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="M50" s="19" t="n">
+        <v>1</v>
+      </c>
+      <c r="N50" s="19" t="inlineStr"/>
+      <c r="O50" s="19" t="inlineStr"/>
     </row>
     <row r="51" outlineLevel="3">
-      <c r="B51" s="17" t="n"/>
-      <c r="C51" s="17" t="n"/>
-      <c r="D51" s="17" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="E51" s="17" t="n"/>
-      <c r="F51" s="17" t="n"/>
-      <c r="G51" s="19" t="n">
-        <v>3</v>
-      </c>
-      <c r="H51" s="19" t="inlineStr">
+      <c r="B51" s="18" t="n"/>
+      <c r="C51" s="18" t="n"/>
+      <c r="D51" s="18" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E51" s="18" t="n"/>
+      <c r="F51" s="18" t="n"/>
+      <c r="G51" s="20" t="n">
+        <v>3</v>
+      </c>
+      <c r="H51" s="20" t="inlineStr">
         <is>
           <t>NCC-FP005-02</t>
         </is>
       </c>
-      <c r="I51" s="19" t="inlineStr">
+      <c r="I51" s="20" t="inlineStr">
         <is>
           <t>Injector Base Port (NCC-FP005.SLDPRT)</t>
         </is>
       </c>
-      <c r="J51" s="19" t="inlineStr">
+      <c r="J51" s="20" t="inlineStr">
         <is>
           <t>INJECTOR BASE, 1" COIL</t>
         </is>
       </c>
-      <c r="K51" s="19" t="inlineStr"/>
-      <c r="L51" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="M51" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="N51" s="19" t="inlineStr"/>
-      <c r="O51" s="19" t="inlineStr"/>
+      <c r="K51" s="20" t="inlineStr"/>
+      <c r="L51" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="M51" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="N51" s="20" t="inlineStr"/>
+      <c r="O51" s="20" t="inlineStr"/>
     </row>
     <row r="52" outlineLevel="3">
-      <c r="B52" s="17" t="n"/>
-      <c r="C52" s="17" t="n"/>
-      <c r="D52" s="17" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="E52" s="17" t="n"/>
-      <c r="F52" s="17" t="n"/>
-      <c r="G52" s="19" t="n">
-        <v>3</v>
-      </c>
-      <c r="H52" s="19" t="inlineStr">
+      <c r="B52" s="18" t="n"/>
+      <c r="C52" s="18" t="n"/>
+      <c r="D52" s="18" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E52" s="18" t="n"/>
+      <c r="F52" s="18" t="n"/>
+      <c r="G52" s="20" t="n">
+        <v>3</v>
+      </c>
+      <c r="H52" s="20" t="inlineStr">
         <is>
           <t>96246A088_Duranium Helical Insert_WRP</t>
         </is>
       </c>
-      <c r="I52" s="19" t="inlineStr">
+      <c r="I52" s="20" t="inlineStr">
         <is>
           <t>Duranium Helical Insert (96246A088_Duranium Helical Insert_WRP.SLDPRT)</t>
         </is>
       </c>
-      <c r="J52" s="19" t="inlineStr">
+      <c r="J52" s="20" t="inlineStr">
         <is>
           <t>Duranium Helical Insert</t>
         </is>
       </c>
-      <c r="K52" s="19" t="inlineStr"/>
-      <c r="L52" s="19" t="n">
-        <v>2</v>
-      </c>
-      <c r="M52" s="19" t="n">
-        <v>2</v>
-      </c>
-      <c r="N52" s="19" t="inlineStr">
+      <c r="K52" s="20" t="inlineStr"/>
+      <c r="L52" s="20" t="n">
+        <v>2</v>
+      </c>
+      <c r="M52" s="20" t="n">
+        <v>2</v>
+      </c>
+      <c r="N52" s="20" t="inlineStr">
         <is>
           <t>Nitronium 60 Duranium Alloy</t>
         </is>
       </c>
-      <c r="O52" s="19" t="inlineStr"/>
+      <c r="O52" s="20" t="inlineStr"/>
     </row>
     <row r="53" outlineLevel="3">
-      <c r="B53" s="17" t="n"/>
-      <c r="C53" s="17" t="n"/>
-      <c r="D53" s="17" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="E53" s="17" t="n"/>
-      <c r="F53" s="17" t="n"/>
-      <c r="G53" s="19" t="n">
-        <v>3</v>
-      </c>
-      <c r="H53" s="19" t="inlineStr">
+      <c r="B53" s="18" t="n"/>
+      <c r="C53" s="18" t="n"/>
+      <c r="D53" s="18" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E53" s="18" t="n"/>
+      <c r="F53" s="18" t="n"/>
+      <c r="G53" s="20" t="n">
+        <v>3</v>
+      </c>
+      <c r="H53" s="20" t="inlineStr">
         <is>
           <t>90945A715_Tritanium Fleet Spec. Washer_WRP</t>
         </is>
       </c>
-      <c r="I53" s="19" t="inlineStr">
+      <c r="I53" s="20" t="inlineStr">
         <is>
           <t>Tritanium Fleet Spec. Washer (90945A715_Tritanium Fleet Spec. Washer_WRP.SLDPRT)</t>
         </is>
       </c>
-      <c r="J53" s="19" t="inlineStr">
+      <c r="J53" s="20" t="inlineStr">
         <is>
           <t>Tritanium Fleet Spec. Washer</t>
         </is>
       </c>
-      <c r="K53" s="19" t="inlineStr"/>
-      <c r="L53" s="19" t="n">
-        <v>2</v>
-      </c>
-      <c r="M53" s="19" t="n">
-        <v>2</v>
-      </c>
-      <c r="N53" s="19" t="inlineStr">
+      <c r="K53" s="20" t="inlineStr"/>
+      <c r="L53" s="20" t="n">
+        <v>2</v>
+      </c>
+      <c r="M53" s="20" t="n">
+        <v>2</v>
+      </c>
+      <c r="N53" s="20" t="inlineStr">
         <is>
           <t>Tritanium 18-8</t>
         </is>
       </c>
-      <c r="O53" s="19" t="inlineStr"/>
+      <c r="O53" s="20" t="inlineStr"/>
     </row>
     <row r="54" outlineLevel="3">
-      <c r="B54" s="17" t="n"/>
-      <c r="C54" s="17" t="n"/>
-      <c r="D54" s="17" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="E54" s="17" t="n"/>
-      <c r="F54" s="17" t="n"/>
-      <c r="G54" s="19" t="n">
-        <v>3</v>
-      </c>
-      <c r="H54" s="19" t="inlineStr">
+      <c r="B54" s="18" t="n"/>
+      <c r="C54" s="18" t="n"/>
+      <c r="D54" s="18" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E54" s="18" t="n"/>
+      <c r="F54" s="18" t="n"/>
+      <c r="G54" s="20" t="n">
+        <v>3</v>
+      </c>
+      <c r="H54" s="20" t="inlineStr">
         <is>
           <t>92423A458_High-Strength Duranium Socket Head Screw_WRP</t>
         </is>
       </c>
-      <c r="I54" s="19" t="inlineStr">
+      <c r="I54" s="20" t="inlineStr">
         <is>
           <t>High-Strength Duranium Socket Head Screw (92423A458_High-Strength Duranium Socket Head Screw_WRP.SLDPRT)</t>
         </is>
       </c>
-      <c r="J54" s="19" t="inlineStr">
+      <c r="J54" s="20" t="inlineStr">
         <is>
           <t>High-Strength Duranium Socket Head Screw</t>
         </is>
       </c>
-      <c r="K54" s="19" t="inlineStr"/>
-      <c r="L54" s="19" t="n">
-        <v>2</v>
-      </c>
-      <c r="M54" s="19" t="n">
-        <v>2</v>
-      </c>
-      <c r="N54" s="19" t="inlineStr">
+      <c r="K54" s="20" t="inlineStr"/>
+      <c r="L54" s="20" t="n">
+        <v>2</v>
+      </c>
+      <c r="M54" s="20" t="n">
+        <v>2</v>
+      </c>
+      <c r="N54" s="20" t="inlineStr">
         <is>
           <t>Duranium A286 Alloy</t>
         </is>
       </c>
-      <c r="O54" s="19" t="inlineStr"/>
+      <c r="O54" s="20" t="inlineStr"/>
     </row>
     <row r="55" outlineLevel="3">
-      <c r="B55" s="17" t="n"/>
-      <c r="C55" s="17" t="n"/>
-      <c r="D55" s="17" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="E55" s="17" t="n"/>
-      <c r="F55" s="17" t="n"/>
-      <c r="G55" s="19" t="n">
-        <v>3</v>
-      </c>
-      <c r="H55" s="19" t="inlineStr">
+      <c r="B55" s="18" t="n"/>
+      <c r="C55" s="18" t="n"/>
+      <c r="D55" s="18" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E55" s="18" t="n"/>
+      <c r="F55" s="18" t="n"/>
+      <c r="G55" s="20" t="n">
+        <v>3</v>
+      </c>
+      <c r="H55" s="20" t="inlineStr">
         <is>
           <t>Custom Injector Shim_WRP</t>
         </is>
       </c>
-      <c r="I55" s="19" t="inlineStr">
+      <c r="I55" s="20" t="inlineStr">
         <is>
           <t>Custom Injector Shim WRP (Custom Injector Shim_WRP.SLDPRT)</t>
         </is>
       </c>
-      <c r="J55" s="19" t="inlineStr"/>
-      <c r="K55" s="19" t="inlineStr"/>
-      <c r="L55" s="19" t="n">
-        <v>3</v>
-      </c>
-      <c r="M55" s="19" t="n">
-        <v>3</v>
-      </c>
-      <c r="N55" s="19" t="inlineStr"/>
-      <c r="O55" s="19" t="inlineStr"/>
+      <c r="J55" s="20" t="inlineStr"/>
+      <c r="K55" s="20" t="inlineStr"/>
+      <c r="L55" s="20" t="n">
+        <v>3</v>
+      </c>
+      <c r="M55" s="20" t="n">
+        <v>3</v>
+      </c>
+      <c r="N55" s="20" t="inlineStr"/>
+      <c r="O55" s="20" t="inlineStr"/>
     </row>
     <row r="56" outlineLevel="3">
-      <c r="B56" s="17" t="n"/>
-      <c r="C56" s="17" t="n"/>
-      <c r="D56" s="17" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="E56" s="17" t="n"/>
-      <c r="F56" s="17" t="n"/>
-      <c r="G56" s="19" t="n">
-        <v>3</v>
-      </c>
-      <c r="H56" s="19" t="inlineStr">
+      <c r="B56" s="18" t="n"/>
+      <c r="C56" s="18" t="n"/>
+      <c r="D56" s="18" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E56" s="18" t="n"/>
+      <c r="F56" s="18" t="n"/>
+      <c r="G56" s="20" t="n">
+        <v>3</v>
+      </c>
+      <c r="H56" s="20" t="inlineStr">
         <is>
           <t>NCC-FP006-02</t>
         </is>
       </c>
-      <c r="I56" s="19" t="inlineStr">
+      <c r="I56" s="20" t="inlineStr">
         <is>
           <t>1in Injector Stage Port (NCC-FP006.SLDPRT)</t>
         </is>
       </c>
-      <c r="J56" s="19" t="inlineStr">
+      <c r="J56" s="20" t="inlineStr">
         <is>
           <t>INJECTOR STAGE, 1" COIL</t>
         </is>
       </c>
-      <c r="K56" s="19" t="inlineStr"/>
-      <c r="L56" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="M56" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="N56" s="19" t="inlineStr"/>
-      <c r="O56" s="19" t="inlineStr"/>
+      <c r="K56" s="20" t="inlineStr"/>
+      <c r="L56" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="M56" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="N56" s="20" t="inlineStr"/>
+      <c r="O56" s="20" t="inlineStr"/>
     </row>
     <row r="57" outlineLevel="3">
-      <c r="B57" s="17" t="n"/>
-      <c r="C57" s="17" t="n"/>
-      <c r="D57" s="17" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="E57" s="17" t="n"/>
-      <c r="F57" s="17" t="n"/>
-      <c r="G57" s="19" t="n">
-        <v>3</v>
-      </c>
-      <c r="H57" s="19" t="inlineStr">
+      <c r="B57" s="18" t="n"/>
+      <c r="C57" s="18" t="n"/>
+      <c r="D57" s="18" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E57" s="18" t="n"/>
+      <c r="F57" s="18" t="n"/>
+      <c r="G57" s="20" t="n">
+        <v>3</v>
+      </c>
+      <c r="H57" s="20" t="inlineStr">
         <is>
           <t>90945A725_Tritanium Fleet Spec. Washer_WRP</t>
         </is>
       </c>
-      <c r="I57" s="19" t="inlineStr">
+      <c r="I57" s="20" t="inlineStr">
         <is>
           <t>Tritanium Fleet Spec. Washer (90945A725_Tritanium Fleet Spec. Washer_WRP.SLDPRT)</t>
         </is>
       </c>
-      <c r="J57" s="19" t="inlineStr">
+      <c r="J57" s="20" t="inlineStr">
         <is>
           <t>Tritanium Fleet Spec. Washer</t>
         </is>
       </c>
-      <c r="K57" s="19" t="inlineStr"/>
-      <c r="L57" s="19" t="n">
-        <v>3</v>
-      </c>
-      <c r="M57" s="19" t="n">
-        <v>3</v>
-      </c>
-      <c r="N57" s="19" t="inlineStr">
+      <c r="K57" s="20" t="inlineStr"/>
+      <c r="L57" s="20" t="n">
+        <v>3</v>
+      </c>
+      <c r="M57" s="20" t="n">
+        <v>3</v>
+      </c>
+      <c r="N57" s="20" t="inlineStr">
         <is>
           <t>Tritanium 18-8</t>
         </is>
       </c>
-      <c r="O57" s="19" t="inlineStr"/>
+      <c r="O57" s="20" t="inlineStr"/>
     </row>
     <row r="58" outlineLevel="3">
-      <c r="B58" s="17" t="n"/>
-      <c r="C58" s="17" t="n"/>
-      <c r="D58" s="17" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="E58" s="17" t="n"/>
-      <c r="F58" s="17" t="n"/>
-      <c r="G58" s="19" t="n">
-        <v>3</v>
-      </c>
-      <c r="H58" s="19" t="inlineStr">
+      <c r="B58" s="18" t="n"/>
+      <c r="C58" s="18" t="n"/>
+      <c r="D58" s="18" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E58" s="18" t="n"/>
+      <c r="F58" s="18" t="n"/>
+      <c r="G58" s="20" t="n">
+        <v>3</v>
+      </c>
+      <c r="H58" s="20" t="inlineStr">
         <is>
           <t>96246A046_Duranium Helical Insert_WRP</t>
         </is>
       </c>
-      <c r="I58" s="19" t="inlineStr">
+      <c r="I58" s="20" t="inlineStr">
         <is>
           <t>Duranium Helical Insert (96246A046_Duranium Helical Insert_WRP.SLDPRT)</t>
         </is>
       </c>
-      <c r="J58" s="19" t="inlineStr">
+      <c r="J58" s="20" t="inlineStr">
         <is>
           <t>Duranium Helical Insert</t>
         </is>
       </c>
-      <c r="K58" s="19" t="inlineStr"/>
-      <c r="L58" s="19" t="n">
+      <c r="K58" s="20" t="inlineStr"/>
+      <c r="L58" s="20" t="n">
         <v>7</v>
       </c>
-      <c r="M58" s="19" t="n">
+      <c r="M58" s="20" t="n">
         <v>7</v>
       </c>
-      <c r="N58" s="19" t="inlineStr">
+      <c r="N58" s="20" t="inlineStr">
         <is>
           <t>Nitronium 60 Duranium Alloy</t>
         </is>
       </c>
-      <c r="O58" s="19" t="inlineStr"/>
+      <c r="O58" s="20" t="inlineStr"/>
     </row>
     <row r="59" outlineLevel="3">
-      <c r="B59" s="17" t="n"/>
-      <c r="C59" s="17" t="n"/>
-      <c r="D59" s="17" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="E59" s="17" t="n"/>
-      <c r="F59" s="17" t="n"/>
-      <c r="G59" s="19" t="n">
-        <v>3</v>
-      </c>
-      <c r="H59" s="19" t="inlineStr">
+      <c r="B59" s="18" t="n"/>
+      <c r="C59" s="18" t="n"/>
+      <c r="D59" s="18" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E59" s="18" t="n"/>
+      <c r="F59" s="18" t="n"/>
+      <c r="G59" s="20" t="n">
+        <v>3</v>
+      </c>
+      <c r="H59" s="20" t="inlineStr">
         <is>
           <t>NCC-FP007-00</t>
         </is>
       </c>
-      <c r="I59" s="19" t="inlineStr">
+      <c r="I59" s="20" t="inlineStr">
         <is>
           <t>Coil Glue Bond (NCC-FP007.SLDPRT)</t>
         </is>
       </c>
-      <c r="J59" s="19" t="inlineStr">
+      <c r="J59" s="20" t="inlineStr">
         <is>
           <t>Sinlge 2216 bond for 1in coil.</t>
         </is>
       </c>
-      <c r="K59" s="19" t="inlineStr"/>
-      <c r="L59" s="19" t="n">
-        <v>3</v>
-      </c>
-      <c r="M59" s="19" t="n">
-        <v>3</v>
-      </c>
-      <c r="N59" s="19" t="inlineStr"/>
-      <c r="O59" s="19" t="inlineStr"/>
+      <c r="K59" s="20" t="inlineStr"/>
+      <c r="L59" s="20" t="n">
+        <v>3</v>
+      </c>
+      <c r="M59" s="20" t="n">
+        <v>3</v>
+      </c>
+      <c r="N59" s="20" t="inlineStr"/>
+      <c r="O59" s="20" t="inlineStr"/>
     </row>
     <row r="60" outlineLevel="3">
-      <c r="B60" s="17" t="n"/>
-      <c r="C60" s="17" t="n"/>
-      <c r="D60" s="17" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="E60" s="17" t="n"/>
-      <c r="F60" s="17" t="n"/>
-      <c r="G60" s="19" t="n">
-        <v>3</v>
-      </c>
-      <c r="H60" s="19" t="inlineStr">
+      <c r="B60" s="18" t="n"/>
+      <c r="C60" s="18" t="n"/>
+      <c r="D60" s="18" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E60" s="18" t="n"/>
+      <c r="F60" s="18" t="n"/>
+      <c r="G60" s="20" t="n">
+        <v>3</v>
+      </c>
+      <c r="H60" s="20" t="inlineStr">
         <is>
           <t>NCC-FP004-B</t>
         </is>
       </c>
-      <c r="I60" s="19" t="inlineStr">
+      <c r="I60" s="20" t="inlineStr">
         <is>
           <t>1in Injector Radial Cell (NCC-FP004.SLDPRT)</t>
         </is>
       </c>
-      <c r="J60" s="19" t="inlineStr">
+      <c r="J60" s="20" t="inlineStr">
         <is>
           <t>Radial Cell of Injector 3DOF or 5DOF Coil Mount</t>
         </is>
       </c>
-      <c r="K60" s="19" t="inlineStr"/>
-      <c r="L60" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="M60" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="N60" s="19" t="inlineStr">
+      <c r="K60" s="20" t="inlineStr"/>
+      <c r="L60" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="M60" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="N60" s="20" t="inlineStr">
         <is>
           <t>Tritanium-36 Plate</t>
         </is>
       </c>
-      <c r="O60" s="19" t="inlineStr">
+      <c r="O60" s="20" t="inlineStr">
         <is>
           <t>0.064</t>
         </is>
       </c>
     </row>
     <row r="61" outlineLevel="3">
-      <c r="B61" s="17" t="n"/>
-      <c r="C61" s="17" t="n"/>
-      <c r="D61" s="17" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="E61" s="17" t="n"/>
-      <c r="F61" s="17" t="n"/>
-      <c r="G61" s="19" t="n">
-        <v>3</v>
-      </c>
-      <c r="H61" s="19" t="inlineStr">
+      <c r="B61" s="18" t="n"/>
+      <c r="C61" s="18" t="n"/>
+      <c r="D61" s="18" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E61" s="18" t="n"/>
+      <c r="F61" s="18" t="n"/>
+      <c r="G61" s="20" t="n">
+        <v>3</v>
+      </c>
+      <c r="H61" s="20" t="inlineStr">
         <is>
           <t>92423A491_High-Strength Duranium Socket Head Screw_WRP</t>
         </is>
       </c>
-      <c r="I61" s="19" t="inlineStr">
+      <c r="I61" s="20" t="inlineStr">
         <is>
           <t>High-Strength Duranium Socket Head Screw (92423A491_High-Strength Duranium Socket Head Screw_WRP.SLDPRT)</t>
         </is>
       </c>
-      <c r="J61" s="19" t="inlineStr">
+      <c r="J61" s="20" t="inlineStr">
         <is>
           <t>High-Strength Duranium Socket Head Screw</t>
         </is>
       </c>
-      <c r="K61" s="19" t="inlineStr"/>
-      <c r="L61" s="19" t="n">
-        <v>3</v>
-      </c>
-      <c r="M61" s="19" t="n">
-        <v>3</v>
-      </c>
-      <c r="N61" s="19" t="inlineStr">
+      <c r="K61" s="20" t="inlineStr"/>
+      <c r="L61" s="20" t="n">
+        <v>3</v>
+      </c>
+      <c r="M61" s="20" t="n">
+        <v>3</v>
+      </c>
+      <c r="N61" s="20" t="inlineStr">
         <is>
           <t>Duranium A286 Alloy</t>
         </is>
       </c>
-      <c r="O61" s="19" t="inlineStr"/>
+      <c r="O61" s="20" t="inlineStr"/>
     </row>
     <row r="62" outlineLevel="3">
-      <c r="B62" s="17" t="n"/>
-      <c r="C62" s="17" t="n"/>
-      <c r="D62" s="17" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="E62" s="17" t="n"/>
-      <c r="F62" s="17" t="n"/>
-      <c r="G62" s="18" t="n">
-        <v>3</v>
-      </c>
-      <c r="H62" s="18" t="inlineStr">
+      <c r="B62" s="18" t="n"/>
+      <c r="C62" s="18" t="n"/>
+      <c r="D62" s="18" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="E62" s="18" t="n"/>
+      <c r="F62" s="18" t="n"/>
+      <c r="G62" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="H62" s="19" t="inlineStr">
         <is>
           <t>AK000007S_WRP</t>
         </is>
       </c>
-      <c r="I62" s="18" t="inlineStr">
+      <c r="I62" s="19" t="inlineStr">
         <is>
           <t>AK000007S WRP (AK000007S_WRP.SLDASM)</t>
         </is>
       </c>
-      <c r="J62" s="18" t="inlineStr"/>
-      <c r="K62" s="18" t="inlineStr"/>
-      <c r="L62" s="18" t="n">
+      <c r="J62" s="19" t="inlineStr"/>
+      <c r="K62" s="19" t="inlineStr"/>
+      <c r="L62" s="19" t="n">
         <v>6</v>
       </c>
-      <c r="M62" s="18" t="n">
+      <c r="M62" s="19" t="n">
         <v>6</v>
       </c>
-      <c r="N62" s="18" t="inlineStr"/>
-      <c r="O62" s="18" t="inlineStr"/>
+      <c r="N62" s="19" t="inlineStr"/>
+      <c r="O62" s="19" t="inlineStr"/>
     </row>
     <row r="63" outlineLevel="4">
-      <c r="B63" s="17" t="n"/>
-      <c r="C63" s="17" t="n"/>
-      <c r="D63" s="17" t="n"/>
-      <c r="E63" s="17" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="F63" s="17" t="n"/>
-      <c r="G63" s="19" t="n">
+      <c r="B63" s="18" t="n"/>
+      <c r="C63" s="18" t="n"/>
+      <c r="D63" s="18" t="n"/>
+      <c r="E63" s="18" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F63" s="18" t="n"/>
+      <c r="G63" s="20" t="n">
         <v>4</v>
       </c>
-      <c r="H63" s="19" t="inlineStr">
+      <c r="H63" s="20" t="inlineStr">
         <is>
           <t>AK020004 EPS Tap Rev A_WRP</t>
         </is>
       </c>
-      <c r="I63" s="19" t="inlineStr">
+      <c r="I63" s="20" t="inlineStr">
         <is>
           <t>AK020004 EPS Tap Rev A WRP (AK020004 EPS Tap Rev A_WRP.SLDPRT)</t>
         </is>
       </c>
-      <c r="J63" s="19" t="inlineStr"/>
-      <c r="K63" s="19" t="inlineStr"/>
-      <c r="L63" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="M63" s="19" t="n">
+      <c r="J63" s="20" t="inlineStr"/>
+      <c r="K63" s="20" t="inlineStr"/>
+      <c r="L63" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="M63" s="20" t="n">
         <v>6</v>
       </c>
-      <c r="N63" s="19" t="inlineStr"/>
-      <c r="O63" s="19" t="inlineStr"/>
+      <c r="N63" s="20" t="inlineStr"/>
+      <c r="O63" s="20" t="inlineStr"/>
     </row>
     <row r="64" outlineLevel="4">
-      <c r="B64" s="17" t="n"/>
-      <c r="C64" s="17" t="n"/>
-      <c r="D64" s="17" t="n"/>
-      <c r="E64" s="17" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="F64" s="17" t="n"/>
-      <c r="G64" s="19" t="n">
+      <c r="B64" s="18" t="n"/>
+      <c r="C64" s="18" t="n"/>
+      <c r="D64" s="18" t="n"/>
+      <c r="E64" s="18" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F64" s="18" t="n"/>
+      <c r="G64" s="20" t="n">
         <v>4</v>
       </c>
-      <c r="H64" s="19" t="inlineStr">
+      <c r="H64" s="20" t="inlineStr">
         <is>
           <t>HD301004 SBS 92196A108_Tritanium Socket Head Screw_WRP</t>
         </is>
       </c>
-      <c r="I64" s="19" t="inlineStr">
+      <c r="I64" s="20" t="inlineStr">
         <is>
           <t>Tritanium Socket Head Screw (HD301004 SBS 92196A108_Tritanium Socket Head Screw_WRP.SLDPRT)</t>
         </is>
       </c>
-      <c r="J64" s="19" t="inlineStr">
+      <c r="J64" s="20" t="inlineStr">
         <is>
           <t>Tritanium Socket Head Screw</t>
         </is>
       </c>
-      <c r="K64" s="19" t="inlineStr"/>
-      <c r="L64" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="M64" s="19" t="n">
+      <c r="K64" s="20" t="inlineStr"/>
+      <c r="L64" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="M64" s="20" t="n">
         <v>6</v>
       </c>
-      <c r="N64" s="19" t="inlineStr">
+      <c r="N64" s="20" t="inlineStr">
         <is>
           <t>Tritanium 18-8</t>
         </is>
       </c>
-      <c r="O64" s="19" t="inlineStr"/>
+      <c r="O64" s="20" t="inlineStr"/>
     </row>
     <row r="65" outlineLevel="4">
-      <c r="B65" s="17" t="n"/>
-      <c r="C65" s="17" t="n"/>
-      <c r="D65" s="17" t="n"/>
-      <c r="E65" s="17" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="F65" s="17" t="n"/>
-      <c r="G65" s="19" t="n">
+      <c r="B65" s="18" t="n"/>
+      <c r="C65" s="18" t="n"/>
+      <c r="D65" s="18" t="n"/>
+      <c r="E65" s="18" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="F65" s="18" t="n"/>
+      <c r="G65" s="20" t="n">
         <v>4</v>
       </c>
-      <c r="H65" s="19" t="inlineStr">
+      <c r="H65" s="20" t="inlineStr">
         <is>
           <t>HD101004 EPS Tap Adjuster Rev B_WRP</t>
         </is>
       </c>
-      <c r="I65" s="19" t="inlineStr">
+      <c r="I65" s="20" t="inlineStr">
         <is>
           <t>HD101004 EPS Tap Adjuster Rev B WRP (HD101004 EPS Tap Adjuster Rev B_WRP.SLDPRT)</t>
         </is>
       </c>
-      <c r="J65" s="19" t="inlineStr"/>
-      <c r="K65" s="19" t="inlineStr"/>
-      <c r="L65" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="M65" s="19" t="n">
+      <c r="J65" s="20" t="inlineStr"/>
+      <c r="K65" s="20" t="inlineStr"/>
+      <c r="L65" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="M65" s="20" t="n">
         <v>6</v>
       </c>
-      <c r="N65" s="19" t="inlineStr"/>
-      <c r="O65" s="19" t="inlineStr"/>
+      <c r="N65" s="20" t="inlineStr"/>
+      <c r="O65" s="20" t="inlineStr"/>
     </row>
     <row r="66" outlineLevel="2">
-      <c r="B66" s="17" t="n"/>
-      <c r="C66" s="17" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="D66" s="17" t="n"/>
-      <c r="E66" s="17" t="n"/>
-      <c r="F66" s="17" t="n"/>
-      <c r="G66" s="19" t="n">
-        <v>2</v>
-      </c>
-      <c r="H66" s="19" t="inlineStr">
+      <c r="B66" s="18" t="n"/>
+      <c r="C66" s="18" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="D66" s="18" t="n"/>
+      <c r="E66" s="18" t="n"/>
+      <c r="F66" s="18" t="n"/>
+      <c r="G66" s="20" t="n">
+        <v>2</v>
+      </c>
+      <c r="H66" s="20" t="inlineStr">
         <is>
           <t>NCC-FP053-00</t>
         </is>
       </c>
-      <c r="I66" s="19" t="inlineStr">
+      <c r="I66" s="20" t="inlineStr">
         <is>
           <t>Emitter - Coil2 (NCC-FP053.SLDPRT)</t>
         </is>
       </c>
-      <c r="J66" s="19" t="inlineStr">
+      <c r="J66" s="20" t="inlineStr">
         <is>
           <t>Fore Coil2</t>
         </is>
       </c>
-      <c r="K66" s="19" t="inlineStr"/>
-      <c r="L66" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="M66" s="19" t="n">
-        <v>1</v>
-      </c>
-      <c r="N66" s="19" t="inlineStr">
+      <c r="K66" s="20" t="inlineStr"/>
+      <c r="L66" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="M66" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="N66" s="20" t="inlineStr">
         <is>
           <t>Transparent Aluminum</t>
         </is>
       </c>
-      <c r="O66" s="19" t="inlineStr">
+      <c r="O66" s="20" t="inlineStr">
         <is>
           <t>0.01</t>
         </is>
@@ -2746,11 +2758,12 @@
     </row>
   </sheetData>
   <autoFilter ref="G17:O66"/>
-  <mergeCells count="11">
+  <mergeCells count="12">
     <mergeCell ref="B10:G10"/>
     <mergeCell ref="B16:F16"/>
     <mergeCell ref="L16:M16"/>
     <mergeCell ref="B9:G9"/>
+    <mergeCell ref="B8:G8"/>
     <mergeCell ref="B2:O5"/>
     <mergeCell ref="B12:G12"/>
     <mergeCell ref="B13:G13"/>
